--- a/ReportesTrades/Tabla_Maestra_Trades.xlsx
+++ b/ReportesTrades/Tabla_Maestra_Trades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Documents\NinjaTrader 8\bin\Custom\ReportesTrades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AADB11E3-CA46-42D0-8835-B62AC0B251A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2801731-89DD-4AF9-9005-397EACE20C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FE1A4C1F-7078-4DBA-A673-2A739DE03A3E}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{ED65FE19-A058-430B-85C9-6EBD53BB409C}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Trades" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="59">
   <si>
     <t>ArchivoOrigen</t>
   </si>
@@ -117,7 +117,7 @@
     <t>Bars</t>
   </si>
   <si>
-    <t>NTMatrix10212026.xlsx</t>
+    <t>NTMatrix10202026.xlsx</t>
   </si>
   <si>
     <t>ES 12-26</t>
@@ -132,19 +132,19 @@
     <t>Long</t>
   </si>
   <si>
-    <t>MatrixLong_Extreme</t>
-  </si>
-  <si>
-    <t>Profit target</t>
-  </si>
-  <si>
-    <t>MatrixLong_Inner</t>
+    <t>MatrixLong_Surfer</t>
   </si>
   <si>
     <t>Stop loss</t>
   </si>
   <si>
     <t>Short</t>
+  </si>
+  <si>
+    <t>MatrixShort_Zona1</t>
+  </si>
+  <si>
+    <t>Profit target</t>
   </si>
   <si>
     <t>MatrixShort_Surfer</t>
@@ -156,28 +156,43 @@
     <t>MatrixLong_Zona1</t>
   </si>
   <si>
-    <t>MatrixLong_Surfer</t>
+    <t>MatrixShort_Inner</t>
   </si>
   <si>
-    <t>MatrixShort_Zona1</t>
+    <t>Close position</t>
   </si>
   <si>
-    <t>MatrixShort_Inner</t>
+    <t>MatrixLong_Inner</t>
+  </si>
+  <si>
+    <t>StopReverse_CierreLargo</t>
+  </si>
+  <si>
+    <t>SL_BandaOpuesta_Surfer</t>
+  </si>
+  <si>
+    <t>MatrixShort_Extreme</t>
+  </si>
+  <si>
+    <t>NTMatrix10212026.xlsx</t>
+  </si>
+  <si>
+    <t>MatrixLong_Extreme</t>
   </si>
   <si>
     <t>NTMatrix10222026.xlsx</t>
   </si>
   <si>
-    <t>MatrixShort_Extreme</t>
-  </si>
-  <si>
-    <t>Close position</t>
-  </si>
-  <si>
-    <t>NTSniperSurfer10212026.xlsx</t>
+    <t>NTSniperSurfer10202026.xlsx</t>
   </si>
   <si>
     <t>Tick610_SniperSurferES</t>
+  </si>
+  <si>
+    <t>SniperSurfer_Long</t>
+  </si>
+  <si>
+    <t>SniperZona1_Short</t>
   </si>
   <si>
     <t>SniperSurfer_Short</t>
@@ -186,10 +201,7 @@
     <t>SniperZona1_Long</t>
   </si>
   <si>
-    <t>SniperSurfer_Long</t>
-  </si>
-  <si>
-    <t>SniperZona1_Short</t>
+    <t>NTSniperSurfer10212026.xlsx</t>
   </si>
   <si>
     <t>NTSniperSurfer10222026.xlsx</t>
@@ -590,8 +602,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7B192-A18C-43AB-BADA-900D7B38E587}">
-  <dimension ref="A1:Y60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6BE70E0-9802-43AC-9B06-E3B4656B0DCB}">
+  <dimension ref="A1:Y83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -698,7 +710,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -719,16 +731,16 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>7774.5</v>
+        <v>7733</v>
       </c>
       <c r="J2">
-        <v>7776</v>
+        <v>7732.75</v>
       </c>
       <c r="K2" s="3">
-        <v>46316.413194444445</v>
+        <v>46315.411111111112</v>
       </c>
       <c r="L2" s="3">
-        <v>46316.413194444445</v>
+        <v>46315.413194444445</v>
       </c>
       <c r="M2" t="s">
         <v>30</v>
@@ -737,10 +749,10 @@
         <v>31</v>
       </c>
       <c r="O2" s="4">
-        <v>70.64</v>
+        <v>-16.86</v>
       </c>
       <c r="P2" s="4">
-        <v>70.64</v>
+        <v>-16.86</v>
       </c>
       <c r="Q2" s="4">
         <v>4.3600000000000003</v>
@@ -758,16 +770,16 @@
         <v>0</v>
       </c>
       <c r="V2" s="4">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="W2" s="4">
-        <v>87.5</v>
+        <v>237.5</v>
       </c>
       <c r="X2" s="4">
-        <v>16.86</v>
+        <v>254.36</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -775,7 +787,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -790,34 +802,34 @@
         <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>7775</v>
+        <v>7778.5</v>
       </c>
       <c r="J3">
-        <v>7771</v>
+        <v>7775.75</v>
       </c>
       <c r="K3" s="3">
-        <v>46316.418055555558</v>
+        <v>46315.460416666669</v>
       </c>
       <c r="L3" s="3">
-        <v>46316.419444444444</v>
+        <v>46315.465277777781</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="4">
-        <v>-204.36</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P3" s="4">
-        <v>-133.72</v>
+        <v>116.28</v>
       </c>
       <c r="Q3" s="4">
         <v>4.3600000000000003</v>
@@ -838,13 +850,13 @@
         <v>200</v>
       </c>
       <c r="W3" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="X3" s="4">
-        <v>304.36</v>
+        <v>16.86</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -852,7 +864,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -867,22 +879,22 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>7759.75</v>
+        <v>7772.75</v>
       </c>
       <c r="J4">
-        <v>7755.5</v>
+        <v>7755.75</v>
       </c>
       <c r="K4" s="3">
-        <v>46316.420138888891</v>
+        <v>46315.46597222222</v>
       </c>
       <c r="L4" s="3">
-        <v>46316.423611111109</v>
+        <v>46315.467361111114</v>
       </c>
       <c r="M4" t="s">
         <v>35</v>
@@ -891,10 +903,10 @@
         <v>36</v>
       </c>
       <c r="O4" s="4">
-        <v>208.14</v>
+        <v>845.64</v>
       </c>
       <c r="P4" s="4">
-        <v>74.42</v>
+        <v>961.92</v>
       </c>
       <c r="Q4" s="4">
         <v>4.3600000000000003</v>
@@ -915,13 +927,13 @@
         <v>150</v>
       </c>
       <c r="W4" s="4">
-        <v>250</v>
+        <v>862.5</v>
       </c>
       <c r="X4" s="4">
-        <v>41.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -929,7 +941,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -950,28 +962,28 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>7762.25</v>
+        <v>7763</v>
       </c>
       <c r="J5">
-        <v>7765</v>
+        <v>7766</v>
       </c>
       <c r="K5" s="3">
-        <v>46316.436111111114</v>
+        <v>46315.487500000003</v>
       </c>
       <c r="L5" s="3">
-        <v>46316.438194444447</v>
+        <v>46315.487500000003</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O5" s="4">
-        <v>133.13999999999999</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P5" s="4">
-        <v>207.56</v>
+        <v>1107.56</v>
       </c>
       <c r="Q5" s="4">
         <v>4.3600000000000003</v>
@@ -989,16 +1001,16 @@
         <v>0</v>
       </c>
       <c r="V5" s="4">
-        <v>162.5</v>
+        <v>37.5</v>
       </c>
       <c r="W5" s="4">
         <v>150</v>
       </c>
       <c r="X5" s="4">
-        <v>16.86</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1006,7 +1018,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1021,34 +1033,34 @@
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>7774.25</v>
+        <v>7759.25</v>
       </c>
       <c r="J6">
-        <v>7777.25</v>
+        <v>7762.25</v>
       </c>
       <c r="K6" s="3">
-        <v>46316.449305555558</v>
+        <v>46315.489583333336</v>
       </c>
       <c r="L6" s="3">
-        <v>46316.45208333333</v>
+        <v>46315.491666666669</v>
       </c>
       <c r="M6" t="s">
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O6" s="4">
-        <v>145.63999999999999</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P6" s="4">
-        <v>353.2</v>
+        <v>953.2</v>
       </c>
       <c r="Q6" s="4">
         <v>4.3600000000000003</v>
@@ -1066,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="V6" s="4">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="W6" s="4">
-        <v>250</v>
+        <v>112.5</v>
       </c>
       <c r="X6" s="4">
-        <v>104.36</v>
+        <v>266.86</v>
       </c>
       <c r="Y6">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1083,7 +1095,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1098,34 +1110,34 @@
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>7788.5</v>
+        <v>7762.25</v>
       </c>
       <c r="J7">
-        <v>7791.75</v>
+        <v>7758.25</v>
       </c>
       <c r="K7" s="3">
-        <v>46316.518750000003</v>
+        <v>46315.491666666669</v>
       </c>
       <c r="L7" s="3">
-        <v>46316.526388888888</v>
+        <v>46315.493750000001</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O7" s="4">
-        <v>-166.86</v>
+        <v>-204.36</v>
       </c>
       <c r="P7" s="4">
-        <v>186.34</v>
+        <v>748.84</v>
       </c>
       <c r="Q7" s="4">
         <v>4.3600000000000003</v>
@@ -1143,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="V7" s="4">
-        <v>175</v>
+        <v>212.5</v>
       </c>
       <c r="W7" s="4">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="X7" s="4">
-        <v>216.86</v>
+        <v>241.86</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1160,7 +1172,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1181,28 +1193,28 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>7799.5</v>
+        <v>7763.25</v>
       </c>
       <c r="J8">
-        <v>7798.75</v>
+        <v>7767.25</v>
       </c>
       <c r="K8" s="3">
-        <v>46316.527083333334</v>
+        <v>46315.495833333334</v>
       </c>
       <c r="L8" s="3">
-        <v>46316.527777777781</v>
+        <v>46315.495833333334</v>
       </c>
       <c r="M8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O8" s="4">
-        <v>-41.86</v>
+        <v>195.64</v>
       </c>
       <c r="P8" s="4">
-        <v>144.47999999999999</v>
+        <v>944.48</v>
       </c>
       <c r="Q8" s="4">
         <v>4.3600000000000003</v>
@@ -1220,16 +1232,16 @@
         <v>0</v>
       </c>
       <c r="V8" s="4">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="W8" s="4">
-        <v>350</v>
+        <v>212.5</v>
       </c>
       <c r="X8" s="4">
-        <v>391.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y8">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -1237,7 +1249,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1252,34 +1264,34 @@
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>7805</v>
+        <v>7764.25</v>
       </c>
       <c r="J9">
-        <v>7802.5</v>
+        <v>7761.25</v>
       </c>
       <c r="K9" s="3">
-        <v>46316.615972222222</v>
+        <v>46315.504166666666</v>
       </c>
       <c r="L9" s="3">
-        <v>46316.616666666669</v>
+        <v>46315.506944444445</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O9" s="4">
-        <v>120.64</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P9" s="4">
-        <v>265.12</v>
+        <v>790.12</v>
       </c>
       <c r="Q9" s="4">
         <v>4.3600000000000003</v>
@@ -1297,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="V9" s="4">
+        <v>150</v>
+      </c>
+      <c r="W9" s="4">
         <v>100</v>
       </c>
-      <c r="W9" s="4">
-        <v>162.5</v>
-      </c>
       <c r="X9" s="4">
-        <v>41.86</v>
+        <v>254.36</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -1314,7 +1326,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1329,34 +1341,34 @@
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>7798.75</v>
+        <v>7754</v>
       </c>
       <c r="J10">
-        <v>7797.5</v>
+        <v>7758.75</v>
       </c>
       <c r="K10" s="3">
-        <v>46316.617361111108</v>
+        <v>46315.512499999997</v>
       </c>
       <c r="L10" s="3">
-        <v>46316.619444444441</v>
+        <v>46315.518750000003</v>
       </c>
       <c r="M10" t="s">
         <v>35</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O10" s="4">
-        <v>58.14</v>
+        <v>-241.86</v>
       </c>
       <c r="P10" s="4">
-        <v>323.26</v>
+        <v>548.26</v>
       </c>
       <c r="Q10" s="4">
         <v>4.3600000000000003</v>
@@ -1374,16 +1386,16 @@
         <v>0</v>
       </c>
       <c r="V10" s="4">
-        <v>137.5</v>
+        <v>262.5</v>
       </c>
       <c r="W10" s="4">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="X10" s="4">
-        <v>191.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y10">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -1391,7 +1403,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1412,28 +1424,28 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>7786.5</v>
+        <v>7762</v>
       </c>
       <c r="J11">
-        <v>7789.25</v>
+        <v>7758.75</v>
       </c>
       <c r="K11" s="3">
-        <v>46316.636111111111</v>
+        <v>46315.533333333333</v>
       </c>
       <c r="L11" s="3">
-        <v>46316.636805555558</v>
+        <v>46315.536111111112</v>
       </c>
       <c r="M11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N11" t="s">
         <v>31</v>
       </c>
       <c r="O11" s="4">
-        <v>133.13999999999999</v>
+        <v>-166.86</v>
       </c>
       <c r="P11" s="4">
-        <v>456.4</v>
+        <v>381.4</v>
       </c>
       <c r="Q11" s="4">
         <v>4.3600000000000003</v>
@@ -1451,16 +1463,16 @@
         <v>0</v>
       </c>
       <c r="V11" s="4">
-        <v>25</v>
+        <v>187.5</v>
       </c>
       <c r="W11" s="4">
-        <v>137.5</v>
+        <v>75</v>
       </c>
       <c r="X11" s="4">
-        <v>4.3600000000000003</v>
+        <v>241.86</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -1468,7 +1480,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1483,34 +1495,34 @@
         <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>7784.5</v>
+        <v>7766.25</v>
       </c>
       <c r="J12">
-        <v>7786</v>
+        <v>7762.25</v>
       </c>
       <c r="K12" s="3">
-        <v>46316.637499999997</v>
+        <v>46315.5625</v>
       </c>
       <c r="L12" s="3">
-        <v>46316.638194444444</v>
+        <v>46315.581250000003</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O12" s="4">
-        <v>-79.36</v>
+        <v>-204.36</v>
       </c>
       <c r="P12" s="4">
-        <v>377.04</v>
+        <v>177.04</v>
       </c>
       <c r="Q12" s="4">
         <v>4.3600000000000003</v>
@@ -1528,27 +1540,27 @@
         <v>0</v>
       </c>
       <c r="V12" s="4">
+        <v>275</v>
+      </c>
+      <c r="W12" s="4">
         <v>112.5</v>
       </c>
-      <c r="W12" s="4">
-        <v>12.5</v>
-      </c>
       <c r="X12" s="4">
-        <v>91.86</v>
+        <v>316.86</v>
       </c>
       <c r="Y12">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -1560,60 +1572,72 @@
         <v>28</v>
       </c>
       <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>7761.25</v>
+      </c>
+      <c r="J13">
+        <v>7758.75</v>
+      </c>
+      <c r="K13" s="3">
+        <v>46315.6</v>
+      </c>
+      <c r="L13" s="3">
+        <v>46315.600694444445</v>
+      </c>
+      <c r="M13" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" t="s">
         <v>34</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>7735</v>
-      </c>
-      <c r="J13">
-        <v>7739</v>
-      </c>
-      <c r="K13" s="3">
-        <v>46317.416666666664</v>
-      </c>
-      <c r="L13" s="3">
-        <v>46317.416666666664</v>
-      </c>
-      <c r="M13" t="s">
-        <v>42</v>
-      </c>
-      <c r="N13" t="s">
-        <v>33</v>
-      </c>
       <c r="O13" s="4">
-        <v>-204.36</v>
+        <v>120.64</v>
       </c>
       <c r="P13" s="4">
-        <v>-204.36</v>
+        <v>297.68</v>
       </c>
       <c r="Q13" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
       <c r="V13" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W13" s="4">
-        <v>62.5</v>
+        <v>137.5</v>
       </c>
       <c r="X13" s="4">
-        <v>266.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -1625,60 +1649,72 @@
         <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>7735.75</v>
+        <v>7754.5</v>
       </c>
       <c r="J14">
-        <v>7733</v>
+        <v>7753.25</v>
       </c>
       <c r="K14" s="3">
-        <v>46317.420138888891</v>
+        <v>46315.60833333333</v>
       </c>
       <c r="L14" s="3">
-        <v>46317.42083333333</v>
+        <v>46315.614583333336</v>
       </c>
       <c r="M14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N14" t="s">
         <v>31</v>
       </c>
       <c r="O14" s="4">
-        <v>133.13999999999999</v>
+        <v>58.14</v>
       </c>
       <c r="P14" s="4">
-        <v>-71.22</v>
+        <v>355.82</v>
       </c>
       <c r="Q14" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
       <c r="V14" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="W14" s="4">
-        <v>137.5</v>
+        <v>287.5</v>
       </c>
       <c r="X14" s="4">
-        <v>4.3600000000000003</v>
+        <v>229.36</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -1690,60 +1726,72 @@
         <v>28</v>
       </c>
       <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>7755.75</v>
+      </c>
+      <c r="J15">
+        <v>7756</v>
+      </c>
+      <c r="K15" s="3">
+        <v>46315.622916666667</v>
+      </c>
+      <c r="L15" s="3">
+        <v>46315.630555555559</v>
+      </c>
+      <c r="M15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" t="s">
         <v>34</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>7727.25</v>
-      </c>
-      <c r="J15">
-        <v>7718.5</v>
-      </c>
-      <c r="K15" s="3">
-        <v>46317.422222222223</v>
-      </c>
-      <c r="L15" s="3">
-        <v>46317.427083333336</v>
-      </c>
-      <c r="M15" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" t="s">
-        <v>36</v>
-      </c>
       <c r="O15" s="4">
-        <v>433.14</v>
+        <v>-16.86</v>
       </c>
       <c r="P15" s="4">
-        <v>361.92</v>
+        <v>338.96</v>
       </c>
       <c r="Q15" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
       <c r="V15" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="W15" s="4">
-        <v>462.5</v>
+        <v>12.5</v>
       </c>
       <c r="X15" s="4">
         <v>29.36</v>
       </c>
       <c r="Y15">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
@@ -1755,60 +1803,72 @@
         <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>7695</v>
+        <v>7750.25</v>
       </c>
       <c r="J16">
-        <v>7689.75</v>
+        <v>7751</v>
       </c>
       <c r="K16" s="3">
-        <v>46317.454861111109</v>
+        <v>46315.63958333333</v>
       </c>
       <c r="L16" s="3">
-        <v>46317.454861111109</v>
+        <v>46315.643055555556</v>
       </c>
       <c r="M16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O16" s="4">
-        <v>-266.86</v>
+        <v>-41.86</v>
       </c>
       <c r="P16" s="4">
-        <v>95.06</v>
+        <v>297.10000000000002</v>
       </c>
       <c r="Q16" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
       <c r="V16" s="4">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="W16" s="4">
-        <v>75</v>
+        <v>187.5</v>
       </c>
       <c r="X16" s="4">
-        <v>341.86</v>
+        <v>229.36</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -1820,60 +1880,72 @@
         <v>28</v>
       </c>
       <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>7774.5</v>
+      </c>
+      <c r="J17">
+        <v>7776</v>
+      </c>
+      <c r="K17" s="3">
+        <v>46316.413194444445</v>
+      </c>
+      <c r="L17" s="3">
+        <v>46316.413194444445</v>
+      </c>
+      <c r="M17" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" t="s">
         <v>34</v>
       </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>7689.5</v>
-      </c>
-      <c r="J17">
-        <v>7694</v>
-      </c>
-      <c r="K17" s="3">
-        <v>46317.454861111109</v>
-      </c>
-      <c r="L17" s="3">
-        <v>46317.457638888889</v>
-      </c>
-      <c r="M17" t="s">
-        <v>40</v>
-      </c>
-      <c r="N17" t="s">
-        <v>33</v>
-      </c>
       <c r="O17" s="4">
-        <v>-229.36</v>
+        <v>70.64</v>
       </c>
       <c r="P17" s="4">
-        <v>-134.30000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="Q17" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
       <c r="V17" s="4">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="W17" s="4">
         <v>87.5</v>
       </c>
       <c r="X17" s="4">
-        <v>316.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y17">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1885,60 +1957,72 @@
         <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>7692.25</v>
+        <v>7775</v>
       </c>
       <c r="J18">
-        <v>7696.25</v>
+        <v>7771</v>
       </c>
       <c r="K18" s="3">
-        <v>46317.460416666669</v>
+        <v>46316.418055555558</v>
       </c>
       <c r="L18" s="3">
-        <v>46317.467361111114</v>
+        <v>46316.419444444444</v>
       </c>
       <c r="M18" t="s">
         <v>40</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O18" s="4">
         <v>-204.36</v>
       </c>
       <c r="P18" s="4">
-        <v>-338.66</v>
+        <v>-133.72</v>
       </c>
       <c r="Q18" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
       <c r="V18" s="4">
-        <v>212.5</v>
+        <v>200</v>
       </c>
       <c r="W18" s="4">
-        <v>162.5</v>
+        <v>100</v>
       </c>
       <c r="X18" s="4">
-        <v>366.86</v>
+        <v>304.36</v>
       </c>
       <c r="Y18">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B19" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1950,60 +2034,72 @@
         <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>7691</v>
+        <v>7759.75</v>
       </c>
       <c r="J19">
-        <v>7696.25</v>
+        <v>7755.5</v>
       </c>
       <c r="K19" s="3">
-        <v>46317.468055555553</v>
+        <v>46316.420138888891</v>
       </c>
       <c r="L19" s="3">
-        <v>46317.470138888886</v>
+        <v>46316.423611111109</v>
       </c>
       <c r="M19" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O19" s="4">
-        <v>-266.86</v>
+        <v>208.14</v>
       </c>
       <c r="P19" s="4">
-        <v>-605.52</v>
+        <v>74.42</v>
       </c>
       <c r="Q19" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
       <c r="V19" s="4">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="W19" s="4">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="X19" s="4">
-        <v>316.86</v>
+        <v>41.86</v>
       </c>
       <c r="Y19">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
@@ -2021,54 +2117,66 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>7700.75</v>
+        <v>7762.25</v>
       </c>
       <c r="J20">
-        <v>7712</v>
+        <v>7765</v>
       </c>
       <c r="K20" s="3">
-        <v>46317.470833333333</v>
+        <v>46316.436111111114</v>
       </c>
       <c r="L20" s="3">
-        <v>46317.474999999999</v>
+        <v>46316.438194444447</v>
       </c>
       <c r="M20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O20" s="4">
-        <v>558.14</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P20" s="4">
-        <v>-47.38</v>
+        <v>207.56</v>
       </c>
       <c r="Q20" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R20" s="4">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0</v>
+      </c>
       <c r="V20" s="4">
-        <v>100</v>
+        <v>162.5</v>
       </c>
       <c r="W20" s="4">
-        <v>587.5</v>
+        <v>150</v>
       </c>
       <c r="X20" s="4">
-        <v>29.36</v>
+        <v>16.86</v>
       </c>
       <c r="Y20">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
@@ -2086,54 +2194,66 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>7700.75</v>
+        <v>7774.25</v>
       </c>
       <c r="J21">
-        <v>7697.25</v>
+        <v>7777.25</v>
       </c>
       <c r="K21" s="3">
-        <v>46317.482638888891</v>
+        <v>46316.449305555558</v>
       </c>
       <c r="L21" s="3">
-        <v>46317.484722222223</v>
+        <v>46316.45208333333</v>
       </c>
       <c r="M21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N21" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="O21" s="4">
-        <v>-179.36</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P21" s="4">
-        <v>-226.74</v>
+        <v>353.2</v>
       </c>
       <c r="Q21" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R21" s="4">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
       <c r="V21" s="4">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="W21" s="4">
-        <v>87.5</v>
+        <v>250</v>
       </c>
       <c r="X21" s="4">
-        <v>266.86</v>
+        <v>104.36</v>
       </c>
       <c r="Y21">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -2145,60 +2265,72 @@
         <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>7697.25</v>
+        <v>7788.5</v>
       </c>
       <c r="J22">
-        <v>7692.75</v>
+        <v>7791.75</v>
       </c>
       <c r="K22" s="3">
-        <v>46317.484722222223</v>
+        <v>46316.518750000003</v>
       </c>
       <c r="L22" s="3">
-        <v>46317.486111111109</v>
+        <v>46316.526388888888</v>
       </c>
       <c r="M22" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N22" t="s">
         <v>31</v>
       </c>
       <c r="O22" s="4">
-        <v>220.64</v>
+        <v>-166.86</v>
       </c>
       <c r="P22" s="4">
-        <v>-6.1</v>
+        <v>186.34</v>
       </c>
       <c r="Q22" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0</v>
+      </c>
       <c r="V22" s="4">
-        <v>162.5</v>
+        <v>175</v>
       </c>
       <c r="W22" s="4">
-        <v>425</v>
+        <v>50</v>
       </c>
       <c r="X22" s="4">
-        <v>204.36</v>
+        <v>216.86</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -2216,54 +2348,66 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>7701.5</v>
+        <v>7799.5</v>
       </c>
       <c r="J23">
-        <v>7696.25</v>
+        <v>7798.75</v>
       </c>
       <c r="K23" s="3">
-        <v>46317.488194444442</v>
+        <v>46316.527083333334</v>
       </c>
       <c r="L23" s="3">
-        <v>46317.489583333336</v>
+        <v>46316.527777777781</v>
       </c>
       <c r="M23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N23" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="O23" s="4">
-        <v>-266.86</v>
+        <v>-41.86</v>
       </c>
       <c r="P23" s="4">
-        <v>-272.95999999999998</v>
+        <v>144.47999999999999</v>
       </c>
       <c r="Q23" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R23" s="4">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4">
+        <v>0</v>
+      </c>
+      <c r="U23" s="4">
+        <v>0</v>
+      </c>
       <c r="V23" s="4">
-        <v>287.5</v>
+        <v>37.5</v>
       </c>
       <c r="W23" s="4">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X23" s="4">
-        <v>266.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -2275,60 +2419,72 @@
         <v>28</v>
       </c>
       <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>7805</v>
+      </c>
+      <c r="J24">
+        <v>7802.5</v>
+      </c>
+      <c r="K24" s="3">
+        <v>46316.615972222222</v>
+      </c>
+      <c r="L24" s="3">
+        <v>46316.616666666669</v>
+      </c>
+      <c r="M24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" t="s">
         <v>34</v>
       </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>7696.25</v>
-      </c>
-      <c r="J24">
-        <v>7701.25</v>
-      </c>
-      <c r="K24" s="3">
-        <v>46317.489583333336</v>
-      </c>
-      <c r="L24" s="3">
-        <v>46317.493055555555</v>
-      </c>
-      <c r="M24" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" t="s">
-        <v>33</v>
-      </c>
       <c r="O24" s="4">
-        <v>-254.36</v>
+        <v>120.64</v>
       </c>
       <c r="P24" s="4">
-        <v>-527.32000000000005</v>
+        <v>265.12</v>
       </c>
       <c r="Q24" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R24" s="4">
+        <v>0</v>
+      </c>
+      <c r="S24" s="4">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0</v>
+      </c>
       <c r="V24" s="4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="W24" s="4">
-        <v>37.5</v>
+        <v>162.5</v>
       </c>
       <c r="X24" s="4">
-        <v>291.86</v>
+        <v>41.86</v>
       </c>
       <c r="Y24">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
@@ -2340,60 +2496,72 @@
         <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>7711</v>
+        <v>7798.75</v>
       </c>
       <c r="J25">
-        <v>7716.75</v>
+        <v>7797.5</v>
       </c>
       <c r="K25" s="3">
-        <v>46317.49722222222</v>
+        <v>46316.617361111108</v>
       </c>
       <c r="L25" s="3">
-        <v>46317.5</v>
+        <v>46316.619444444441</v>
       </c>
       <c r="M25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O25" s="4">
-        <v>283.14</v>
+        <v>58.14</v>
       </c>
       <c r="P25" s="4">
-        <v>-244.18</v>
+        <v>323.26</v>
       </c>
       <c r="Q25" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R25" s="4">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0</v>
+      </c>
       <c r="V25" s="4">
-        <v>62.5</v>
+        <v>137.5</v>
       </c>
       <c r="W25" s="4">
-        <v>312.5</v>
+        <v>250</v>
       </c>
       <c r="X25" s="4">
-        <v>29.36</v>
+        <v>191.86</v>
       </c>
       <c r="Y25">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -2405,60 +2573,72 @@
         <v>28</v>
       </c>
       <c r="G26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>7786.5</v>
+      </c>
+      <c r="J26">
+        <v>7789.25</v>
+      </c>
+      <c r="K26" s="3">
+        <v>46316.636111111111</v>
+      </c>
+      <c r="L26" s="3">
+        <v>46316.636805555558</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
         <v>34</v>
       </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>7711.5</v>
-      </c>
-      <c r="J26">
-        <v>7709</v>
-      </c>
-      <c r="K26" s="3">
-        <v>46317.522222222222</v>
-      </c>
-      <c r="L26" s="3">
-        <v>46317.522916666669</v>
-      </c>
-      <c r="M26" t="s">
-        <v>39</v>
-      </c>
-      <c r="N26" t="s">
-        <v>31</v>
-      </c>
       <c r="O26" s="4">
-        <v>120.64</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P26" s="4">
-        <v>-123.54</v>
+        <v>456.4</v>
       </c>
       <c r="Q26" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R26" s="4">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0</v>
+      </c>
       <c r="V26" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="W26" s="4">
         <v>137.5</v>
       </c>
       <c r="X26" s="4">
-        <v>16.86</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -2470,60 +2650,72 @@
         <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>7701</v>
+        <v>7784.5</v>
       </c>
       <c r="J27">
-        <v>7698.25</v>
+        <v>7786</v>
       </c>
       <c r="K27" s="3">
-        <v>46317.527083333334</v>
+        <v>46316.637499999997</v>
       </c>
       <c r="L27" s="3">
-        <v>46317.530555555553</v>
+        <v>46316.638194444444</v>
       </c>
       <c r="M27" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N27" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O27" s="4">
-        <v>133.13999999999999</v>
+        <v>-79.36</v>
       </c>
       <c r="P27" s="4">
-        <v>9.6</v>
+        <v>377.04</v>
       </c>
       <c r="Q27" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R27" s="4">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0</v>
+      </c>
       <c r="V27" s="4">
-        <v>50</v>
+        <v>112.5</v>
       </c>
       <c r="W27" s="4">
-        <v>237.5</v>
+        <v>12.5</v>
       </c>
       <c r="X27" s="4">
-        <v>104.36</v>
+        <v>91.86</v>
       </c>
       <c r="Y27">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2">
         <v>46317</v>
       </c>
       <c r="C28">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -2535,60 +2727,60 @@
         <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>7702.25</v>
+        <v>7735</v>
       </c>
       <c r="J28">
-        <v>7697.5</v>
+        <v>7739</v>
       </c>
       <c r="K28" s="3">
-        <v>46317.540277777778</v>
+        <v>46317.416666666664</v>
       </c>
       <c r="L28" s="3">
-        <v>46317.543055555558</v>
+        <v>46317.416666666664</v>
       </c>
       <c r="M28" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O28" s="4">
-        <v>-241.86</v>
+        <v>-204.36</v>
       </c>
       <c r="P28" s="4">
-        <v>-232.26</v>
+        <v>-204.36</v>
       </c>
       <c r="Q28" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V28" s="4">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="W28" s="4">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="X28" s="4">
-        <v>329.36</v>
+        <v>266.86</v>
       </c>
       <c r="Y28">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B29" s="2">
         <v>46317</v>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -2600,60 +2792,60 @@
         <v>28</v>
       </c>
       <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>7735.75</v>
+      </c>
+      <c r="J29">
+        <v>7733</v>
+      </c>
+      <c r="K29" s="3">
+        <v>46317.420138888891</v>
+      </c>
+      <c r="L29" s="3">
+        <v>46317.42083333333</v>
+      </c>
+      <c r="M29" t="s">
+        <v>38</v>
+      </c>
+      <c r="N29" t="s">
         <v>34</v>
       </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>7690</v>
-      </c>
-      <c r="J29">
-        <v>7693</v>
-      </c>
-      <c r="K29" s="3">
-        <v>46317.547222222223</v>
-      </c>
-      <c r="L29" s="3">
-        <v>46317.551388888889</v>
-      </c>
-      <c r="M29" t="s">
-        <v>35</v>
-      </c>
-      <c r="N29" t="s">
-        <v>36</v>
-      </c>
       <c r="O29" s="4">
-        <v>-154.36000000000001</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P29" s="4">
-        <v>-386.62</v>
+        <v>-71.22</v>
       </c>
       <c r="Q29" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V29" s="4">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="W29" s="4">
-        <v>175</v>
+        <v>137.5</v>
       </c>
       <c r="X29" s="4">
-        <v>329.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y29">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B30" s="2">
         <v>46317</v>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D30" t="s">
         <v>26</v>
@@ -2665,60 +2857,60 @@
         <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>7695.5</v>
+        <v>7727.25</v>
       </c>
       <c r="J30">
-        <v>7698.75</v>
+        <v>7718.5</v>
       </c>
       <c r="K30" s="3">
-        <v>46317.558333333334</v>
+        <v>46317.422222222223</v>
       </c>
       <c r="L30" s="3">
-        <v>46317.561111111114</v>
+        <v>46317.427083333336</v>
       </c>
       <c r="M30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O30" s="4">
-        <v>-166.86</v>
+        <v>433.14</v>
       </c>
       <c r="P30" s="4">
-        <v>-553.48</v>
+        <v>361.92</v>
       </c>
       <c r="Q30" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V30" s="4">
-        <v>162.5</v>
+        <v>100</v>
       </c>
       <c r="W30" s="4">
-        <v>150</v>
+        <v>462.5</v>
       </c>
       <c r="X30" s="4">
-        <v>316.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y30">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2">
         <v>46317</v>
       </c>
       <c r="C31">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -2736,54 +2928,54 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>7698.25</v>
+        <v>7695</v>
       </c>
       <c r="J31">
-        <v>7702.5</v>
+        <v>7689.75</v>
       </c>
       <c r="K31" s="3">
-        <v>46317.561805555553</v>
+        <v>46317.454861111109</v>
       </c>
       <c r="L31" s="3">
-        <v>46317.56527777778</v>
+        <v>46317.454861111109</v>
       </c>
       <c r="M31" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N31" t="s">
         <v>31</v>
       </c>
       <c r="O31" s="4">
-        <v>208.14</v>
+        <v>-266.86</v>
       </c>
       <c r="P31" s="4">
-        <v>-345.34</v>
+        <v>95.06</v>
       </c>
       <c r="Q31" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V31" s="4">
-        <v>112.5</v>
+        <v>300</v>
       </c>
       <c r="W31" s="4">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="X31" s="4">
-        <v>16.86</v>
+        <v>341.86</v>
       </c>
       <c r="Y31">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B32" s="2">
         <v>46317</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -2795,60 +2987,60 @@
         <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>7704.75</v>
+        <v>7689.5</v>
       </c>
       <c r="J32">
-        <v>7697.75</v>
+        <v>7694</v>
       </c>
       <c r="K32" s="3">
-        <v>46317.56527777778</v>
+        <v>46317.454861111109</v>
       </c>
       <c r="L32" s="3">
-        <v>46317.573611111111</v>
+        <v>46317.457638888889</v>
       </c>
       <c r="M32" t="s">
         <v>38</v>
       </c>
       <c r="N32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O32" s="4">
-        <v>-354.36</v>
+        <v>-229.36</v>
       </c>
       <c r="P32" s="4">
-        <v>-699.7</v>
+        <v>-134.30000000000001</v>
       </c>
       <c r="Q32" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V32" s="4">
-        <v>362.5</v>
+        <v>225</v>
       </c>
       <c r="W32" s="4">
-        <v>37.5</v>
+        <v>87.5</v>
       </c>
       <c r="X32" s="4">
-        <v>391.86</v>
+        <v>316.86</v>
       </c>
       <c r="Y32">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B33" s="2">
         <v>46317</v>
       </c>
       <c r="C33">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
@@ -2860,60 +3052,60 @@
         <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>7687.75</v>
+        <v>7692.25</v>
       </c>
       <c r="J33">
-        <v>7679.75</v>
+        <v>7696.25</v>
       </c>
       <c r="K33" s="3">
-        <v>46317.584027777775</v>
+        <v>46317.460416666669</v>
       </c>
       <c r="L33" s="3">
-        <v>46317.586111111108</v>
+        <v>46317.467361111114</v>
       </c>
       <c r="M33" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O33" s="4">
-        <v>395.64</v>
+        <v>-204.36</v>
       </c>
       <c r="P33" s="4">
-        <v>-304.06</v>
+        <v>-338.66</v>
       </c>
       <c r="Q33" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V33" s="4">
-        <v>25</v>
+        <v>212.5</v>
       </c>
       <c r="W33" s="4">
-        <v>425</v>
+        <v>162.5</v>
       </c>
       <c r="X33" s="4">
-        <v>29.36</v>
+        <v>366.86</v>
       </c>
       <c r="Y33">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B34" s="2">
         <v>46317</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
         <v>26</v>
@@ -2925,60 +3117,60 @@
         <v>28</v>
       </c>
       <c r="G34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="J34">
-        <v>7692.5</v>
+        <v>7696.25</v>
       </c>
       <c r="K34" s="3">
-        <v>46317.59375</v>
+        <v>46317.468055555553</v>
       </c>
       <c r="L34" s="3">
-        <v>46317.594444444447</v>
+        <v>46317.470138888886</v>
       </c>
       <c r="M34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O34" s="4">
-        <v>-129.36000000000001</v>
+        <v>-266.86</v>
       </c>
       <c r="P34" s="4">
-        <v>-433.42</v>
+        <v>-605.52</v>
       </c>
       <c r="Q34" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V34" s="4">
-        <v>137.5</v>
+        <v>275</v>
       </c>
       <c r="W34" s="4">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="X34" s="4">
-        <v>166.86</v>
+        <v>316.86</v>
       </c>
       <c r="Y34">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B35" s="2">
         <v>46317</v>
       </c>
       <c r="C35">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -2996,54 +3188,54 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>7699.75</v>
+        <v>7700.75</v>
       </c>
       <c r="J35">
-        <v>7694</v>
+        <v>7712</v>
       </c>
       <c r="K35" s="3">
-        <v>46317.59652777778</v>
+        <v>46317.470833333333</v>
       </c>
       <c r="L35" s="3">
-        <v>46317.602083333331</v>
+        <v>46317.474999999999</v>
       </c>
       <c r="M35" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O35" s="4">
-        <v>-291.86</v>
+        <v>558.14</v>
       </c>
       <c r="P35" s="4">
-        <v>-725.28</v>
+        <v>-47.38</v>
       </c>
       <c r="Q35" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V35" s="4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="W35" s="4">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="X35" s="4">
-        <v>466.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y35">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B36" s="2">
         <v>46317</v>
       </c>
       <c r="C36">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
         <v>26</v>
@@ -3055,60 +3247,60 @@
         <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>7684</v>
+        <v>7700.75</v>
       </c>
       <c r="J36">
-        <v>7682.5</v>
+        <v>7697.25</v>
       </c>
       <c r="K36" s="3">
-        <v>46317.606249999997</v>
+        <v>46317.482638888891</v>
       </c>
       <c r="L36" s="3">
-        <v>46317.611805555556</v>
+        <v>46317.484722222223</v>
       </c>
       <c r="M36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N36" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O36" s="4">
-        <v>70.64</v>
+        <v>-179.36</v>
       </c>
       <c r="P36" s="4">
-        <v>-654.64</v>
+        <v>-226.74</v>
       </c>
       <c r="Q36" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V36" s="4">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="W36" s="4">
-        <v>112.5</v>
+        <v>87.5</v>
       </c>
       <c r="X36" s="4">
-        <v>41.86</v>
+        <v>266.86</v>
       </c>
       <c r="Y36">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B37" s="2">
         <v>46317</v>
       </c>
       <c r="C37">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
@@ -3120,60 +3312,60 @@
         <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>7687</v>
+        <v>7697.25</v>
       </c>
       <c r="J37">
-        <v>7689.75</v>
+        <v>7692.75</v>
       </c>
       <c r="K37" s="3">
-        <v>46317.629861111112</v>
+        <v>46317.484722222223</v>
       </c>
       <c r="L37" s="3">
-        <v>46317.633333333331</v>
+        <v>46317.486111111109</v>
       </c>
       <c r="M37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N37" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O37" s="4">
-        <v>133.13999999999999</v>
+        <v>220.64</v>
       </c>
       <c r="P37" s="4">
-        <v>-521.5</v>
+        <v>-6.1</v>
       </c>
       <c r="Q37" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V37" s="4">
-        <v>175</v>
+        <v>162.5</v>
       </c>
       <c r="W37" s="4">
-        <v>162.5</v>
+        <v>425</v>
       </c>
       <c r="X37" s="4">
-        <v>29.36</v>
+        <v>204.36</v>
       </c>
       <c r="Y37">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B38" s="2">
         <v>46317</v>
       </c>
       <c r="C38">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
@@ -3185,60 +3377,60 @@
         <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>7688.25</v>
+        <v>7701.5</v>
       </c>
       <c r="J38">
-        <v>7685.25</v>
+        <v>7696.25</v>
       </c>
       <c r="K38" s="3">
-        <v>46317.649305555555</v>
+        <v>46317.488194444442</v>
       </c>
       <c r="L38" s="3">
-        <v>46317.652777777781</v>
+        <v>46317.489583333336</v>
       </c>
       <c r="M38" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38" t="s">
         <v>39</v>
       </c>
-      <c r="N38" t="s">
-        <v>31</v>
-      </c>
       <c r="O38" s="4">
-        <v>145.63999999999999</v>
+        <v>-266.86</v>
       </c>
       <c r="P38" s="4">
-        <v>-375.86</v>
+        <v>-272.95999999999998</v>
       </c>
       <c r="Q38" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V38" s="4">
-        <v>100</v>
+        <v>287.5</v>
       </c>
       <c r="W38" s="4">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="X38" s="4">
-        <v>29.36</v>
+        <v>266.86</v>
       </c>
       <c r="Y38">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>26</v>
@@ -3247,75 +3439,63 @@
         <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>7759.75</v>
+        <v>7696.25</v>
       </c>
       <c r="J39">
-        <v>7755.5</v>
+        <v>7701.25</v>
       </c>
       <c r="K39" s="3">
-        <v>46316.420138888891</v>
+        <v>46317.489583333336</v>
       </c>
       <c r="L39" s="3">
-        <v>46316.423611111109</v>
+        <v>46317.493055555555</v>
       </c>
       <c r="M39" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N39" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O39" s="4">
-        <v>208.14</v>
+        <v>-254.36</v>
       </c>
       <c r="P39" s="4">
-        <v>208.14</v>
+        <v>-527.32000000000005</v>
       </c>
       <c r="Q39" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R39" s="4">
-        <v>0</v>
-      </c>
-      <c r="S39" s="4">
-        <v>0</v>
-      </c>
-      <c r="T39" s="4">
-        <v>0</v>
-      </c>
-      <c r="U39" s="4">
-        <v>0</v>
-      </c>
       <c r="V39" s="4">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="W39" s="4">
-        <v>250</v>
+        <v>37.5</v>
       </c>
       <c r="X39" s="4">
-        <v>41.86</v>
+        <v>291.86</v>
       </c>
       <c r="Y39">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
@@ -3324,7 +3504,7 @@
         <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G40" t="s">
         <v>29</v>
@@ -3333,66 +3513,54 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>7762.25</v>
+        <v>7711</v>
       </c>
       <c r="J40">
-        <v>7765</v>
+        <v>7716.75</v>
       </c>
       <c r="K40" s="3">
-        <v>46316.436111111114</v>
+        <v>46317.49722222222</v>
       </c>
       <c r="L40" s="3">
-        <v>46316.438194444447</v>
+        <v>46317.5</v>
       </c>
       <c r="M40" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O40" s="4">
-        <v>133.13999999999999</v>
+        <v>283.14</v>
       </c>
       <c r="P40" s="4">
-        <v>341.28</v>
+        <v>-244.18</v>
       </c>
       <c r="Q40" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R40" s="4">
-        <v>0</v>
-      </c>
-      <c r="S40" s="4">
-        <v>0</v>
-      </c>
-      <c r="T40" s="4">
-        <v>0</v>
-      </c>
-      <c r="U40" s="4">
-        <v>0</v>
-      </c>
       <c r="V40" s="4">
-        <v>162.5</v>
+        <v>62.5</v>
       </c>
       <c r="W40" s="4">
-        <v>150</v>
+        <v>312.5</v>
       </c>
       <c r="X40" s="4">
-        <v>16.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y40">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B41" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -3401,75 +3569,63 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>7774.25</v>
+        <v>7711.5</v>
       </c>
       <c r="J41">
-        <v>7777.25</v>
+        <v>7709</v>
       </c>
       <c r="K41" s="3">
-        <v>46316.449305555558</v>
+        <v>46317.522222222222</v>
       </c>
       <c r="L41" s="3">
-        <v>46316.45208333333</v>
+        <v>46317.522916666669</v>
       </c>
       <c r="M41" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O41" s="4">
-        <v>145.63999999999999</v>
+        <v>120.64</v>
       </c>
       <c r="P41" s="4">
-        <v>486.92</v>
+        <v>-123.54</v>
       </c>
       <c r="Q41" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R41" s="4">
-        <v>0</v>
-      </c>
-      <c r="S41" s="4">
-        <v>0</v>
-      </c>
-      <c r="T41" s="4">
-        <v>0</v>
-      </c>
-      <c r="U41" s="4">
-        <v>0</v>
-      </c>
       <c r="V41" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="W41" s="4">
-        <v>250</v>
+        <v>137.5</v>
       </c>
       <c r="X41" s="4">
-        <v>104.36</v>
+        <v>16.86</v>
       </c>
       <c r="Y41">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
         <v>26</v>
@@ -3478,75 +3634,63 @@
         <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>7788.5</v>
+        <v>7701</v>
       </c>
       <c r="J42">
-        <v>7791.75</v>
+        <v>7698.25</v>
       </c>
       <c r="K42" s="3">
-        <v>46316.518750000003</v>
+        <v>46317.527083333334</v>
       </c>
       <c r="L42" s="3">
-        <v>46316.526388888888</v>
+        <v>46317.530555555553</v>
       </c>
       <c r="M42" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O42" s="4">
-        <v>-166.86</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P42" s="4">
-        <v>320.06</v>
+        <v>9.6</v>
       </c>
       <c r="Q42" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R42" s="4">
-        <v>0</v>
-      </c>
-      <c r="S42" s="4">
-        <v>0</v>
-      </c>
-      <c r="T42" s="4">
-        <v>0</v>
-      </c>
-      <c r="U42" s="4">
-        <v>0</v>
-      </c>
       <c r="V42" s="4">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="W42" s="4">
-        <v>50</v>
+        <v>237.5</v>
       </c>
       <c r="X42" s="4">
-        <v>216.86</v>
+        <v>104.36</v>
       </c>
       <c r="Y42">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B43" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -3555,7 +3699,7 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G43" t="s">
         <v>29</v>
@@ -3564,66 +3708,54 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>7799.5</v>
+        <v>7702.25</v>
       </c>
       <c r="J43">
-        <v>7798.75</v>
+        <v>7697.5</v>
       </c>
       <c r="K43" s="3">
-        <v>46316.527083333334</v>
+        <v>46317.540277777778</v>
       </c>
       <c r="L43" s="3">
-        <v>46316.527777777781</v>
+        <v>46317.543055555558</v>
       </c>
       <c r="M43" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O43" s="4">
-        <v>-41.86</v>
+        <v>-241.86</v>
       </c>
       <c r="P43" s="4">
-        <v>278.2</v>
+        <v>-232.26</v>
       </c>
       <c r="Q43" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R43" s="4">
-        <v>0</v>
-      </c>
-      <c r="S43" s="4">
-        <v>0</v>
-      </c>
-      <c r="T43" s="4">
-        <v>0</v>
-      </c>
-      <c r="U43" s="4">
-        <v>0</v>
-      </c>
       <c r="V43" s="4">
-        <v>37.5</v>
+        <v>250</v>
       </c>
       <c r="W43" s="4">
-        <v>350</v>
+        <v>87.5</v>
       </c>
       <c r="X43" s="4">
-        <v>391.86</v>
+        <v>329.36</v>
       </c>
       <c r="Y43">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
@@ -3632,75 +3764,63 @@
         <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>7805</v>
+        <v>7690</v>
       </c>
       <c r="J44">
-        <v>7802.5</v>
+        <v>7693</v>
       </c>
       <c r="K44" s="3">
-        <v>46316.615972222222</v>
+        <v>46317.547222222223</v>
       </c>
       <c r="L44" s="3">
-        <v>46316.616666666669</v>
+        <v>46317.551388888889</v>
       </c>
       <c r="M44" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="N44" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O44" s="4">
-        <v>120.64</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P44" s="4">
-        <v>398.84</v>
+        <v>-386.62</v>
       </c>
       <c r="Q44" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R44" s="4">
-        <v>0</v>
-      </c>
-      <c r="S44" s="4">
-        <v>0</v>
-      </c>
-      <c r="T44" s="4">
-        <v>0</v>
-      </c>
-      <c r="U44" s="4">
-        <v>0</v>
-      </c>
       <c r="V44" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="W44" s="4">
-        <v>162.5</v>
+        <v>175</v>
       </c>
       <c r="X44" s="4">
-        <v>41.86</v>
+        <v>329.36</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -3709,75 +3829,63 @@
         <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>7798.75</v>
+        <v>7695.5</v>
       </c>
       <c r="J45">
-        <v>7797.5</v>
+        <v>7698.75</v>
       </c>
       <c r="K45" s="3">
-        <v>46316.617361111108</v>
+        <v>46317.558333333334</v>
       </c>
       <c r="L45" s="3">
-        <v>46316.619444444441</v>
+        <v>46317.561111111114</v>
       </c>
       <c r="M45" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N45" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O45" s="4">
-        <v>58.14</v>
+        <v>-166.86</v>
       </c>
       <c r="P45" s="4">
-        <v>456.98</v>
+        <v>-553.48</v>
       </c>
       <c r="Q45" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R45" s="4">
-        <v>0</v>
-      </c>
-      <c r="S45" s="4">
-        <v>0</v>
-      </c>
-      <c r="T45" s="4">
-        <v>0</v>
-      </c>
-      <c r="U45" s="4">
-        <v>0</v>
-      </c>
       <c r="V45" s="4">
-        <v>137.5</v>
+        <v>162.5</v>
       </c>
       <c r="W45" s="4">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="X45" s="4">
-        <v>191.86</v>
+        <v>316.86</v>
       </c>
       <c r="Y45">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
@@ -3786,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G46" t="s">
         <v>29</v>
@@ -3795,66 +3903,54 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>7786.5</v>
+        <v>7698.25</v>
       </c>
       <c r="J46">
-        <v>7789.25</v>
+        <v>7702.5</v>
       </c>
       <c r="K46" s="3">
-        <v>46316.636111111111</v>
+        <v>46317.561805555553</v>
       </c>
       <c r="L46" s="3">
-        <v>46316.636805555558</v>
+        <v>46317.56527777778</v>
       </c>
       <c r="M46" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N46" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O46" s="4">
-        <v>133.13999999999999</v>
+        <v>208.14</v>
       </c>
       <c r="P46" s="4">
-        <v>590.12</v>
+        <v>-345.34</v>
       </c>
       <c r="Q46" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R46" s="4">
-        <v>0</v>
-      </c>
-      <c r="S46" s="4">
-        <v>0</v>
-      </c>
-      <c r="T46" s="4">
-        <v>0</v>
-      </c>
-      <c r="U46" s="4">
-        <v>0</v>
-      </c>
       <c r="V46" s="4">
-        <v>25</v>
+        <v>112.5</v>
       </c>
       <c r="W46" s="4">
-        <v>137.5</v>
+        <v>225</v>
       </c>
       <c r="X46" s="4">
-        <v>4.3600000000000003</v>
+        <v>16.86</v>
       </c>
       <c r="Y46">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2">
         <v>46317</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
@@ -3863,75 +3959,63 @@
         <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G47" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>7727.25</v>
+        <v>7704.75</v>
       </c>
       <c r="J47">
-        <v>7718.5</v>
+        <v>7697.75</v>
       </c>
       <c r="K47" s="3">
-        <v>46317.422222222223</v>
+        <v>46317.56527777778</v>
       </c>
       <c r="L47" s="3">
-        <v>46317.427083333336</v>
+        <v>46317.573611111111</v>
       </c>
       <c r="M47" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O47" s="4">
-        <v>433.14</v>
+        <v>-354.36</v>
       </c>
       <c r="P47" s="4">
-        <v>433.14</v>
+        <v>-699.7</v>
       </c>
       <c r="Q47" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R47" s="4">
-        <v>0</v>
-      </c>
-      <c r="S47" s="4">
-        <v>0</v>
-      </c>
-      <c r="T47" s="4">
-        <v>0</v>
-      </c>
-      <c r="U47" s="4">
-        <v>0</v>
-      </c>
       <c r="V47" s="4">
-        <v>100</v>
+        <v>362.5</v>
       </c>
       <c r="W47" s="4">
-        <v>462.5</v>
+        <v>37.5</v>
       </c>
       <c r="X47" s="4">
-        <v>29.36</v>
+        <v>391.86</v>
       </c>
       <c r="Y47">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2">
         <v>46317</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
         <v>26</v>
@@ -3940,75 +4024,63 @@
         <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G48" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>7695</v>
+        <v>7687.75</v>
       </c>
       <c r="J48">
-        <v>7689.75</v>
+        <v>7679.75</v>
       </c>
       <c r="K48" s="3">
-        <v>46317.454861111109</v>
+        <v>46317.584027777775</v>
       </c>
       <c r="L48" s="3">
-        <v>46317.454861111109</v>
+        <v>46317.586111111108</v>
       </c>
       <c r="M48" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="N48" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O48" s="4">
-        <v>-266.86</v>
+        <v>395.64</v>
       </c>
       <c r="P48" s="4">
-        <v>166.28</v>
+        <v>-304.06</v>
       </c>
       <c r="Q48" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R48" s="4">
-        <v>0</v>
-      </c>
-      <c r="S48" s="4">
-        <v>0</v>
-      </c>
-      <c r="T48" s="4">
-        <v>0</v>
-      </c>
-      <c r="U48" s="4">
-        <v>0</v>
-      </c>
       <c r="V48" s="4">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="W48" s="4">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="X48" s="4">
-        <v>341.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y48">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B49" s="2">
         <v>46317</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
@@ -4017,75 +4089,63 @@
         <v>27</v>
       </c>
       <c r="F49" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>7700.75</v>
+        <v>7690</v>
       </c>
       <c r="J49">
-        <v>7712</v>
+        <v>7692.5</v>
       </c>
       <c r="K49" s="3">
-        <v>46317.470833333333</v>
+        <v>46317.59375</v>
       </c>
       <c r="L49" s="3">
-        <v>46317.474999999999</v>
+        <v>46317.594444444447</v>
       </c>
       <c r="M49" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="N49" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O49" s="4">
-        <v>558.14</v>
+        <v>-129.36000000000001</v>
       </c>
       <c r="P49" s="4">
-        <v>724.42</v>
+        <v>-433.42</v>
       </c>
       <c r="Q49" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R49" s="4">
-        <v>0</v>
-      </c>
-      <c r="S49" s="4">
-        <v>0</v>
-      </c>
-      <c r="T49" s="4">
-        <v>0</v>
-      </c>
-      <c r="U49" s="4">
-        <v>0</v>
-      </c>
       <c r="V49" s="4">
-        <v>100</v>
+        <v>137.5</v>
       </c>
       <c r="W49" s="4">
-        <v>587.5</v>
+        <v>37.5</v>
       </c>
       <c r="X49" s="4">
-        <v>29.36</v>
+        <v>166.86</v>
       </c>
       <c r="Y49">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B50" s="2">
         <v>46317</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
         <v>26</v>
@@ -4094,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G50" t="s">
         <v>29</v>
@@ -4103,66 +4163,54 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>7711</v>
+        <v>7699.75</v>
       </c>
       <c r="J50">
-        <v>7716.75</v>
+        <v>7694</v>
       </c>
       <c r="K50" s="3">
-        <v>46317.49722222222</v>
+        <v>46317.59652777778</v>
       </c>
       <c r="L50" s="3">
-        <v>46317.5</v>
+        <v>46317.602083333331</v>
       </c>
       <c r="M50" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O50" s="4">
-        <v>283.14</v>
+        <v>-291.86</v>
       </c>
       <c r="P50" s="4">
-        <v>1007.56</v>
+        <v>-725.28</v>
       </c>
       <c r="Q50" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R50" s="4">
-        <v>0</v>
-      </c>
-      <c r="S50" s="4">
-        <v>0</v>
-      </c>
-      <c r="T50" s="4">
-        <v>0</v>
-      </c>
-      <c r="U50" s="4">
-        <v>0</v>
-      </c>
       <c r="V50" s="4">
-        <v>62.5</v>
+        <v>300</v>
       </c>
       <c r="W50" s="4">
-        <v>312.5</v>
+        <v>175</v>
       </c>
       <c r="X50" s="4">
-        <v>29.36</v>
+        <v>466.86</v>
       </c>
       <c r="Y50">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" s="2">
         <v>46317</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
         <v>26</v>
@@ -4171,75 +4219,63 @@
         <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>7711.5</v>
+        <v>7684</v>
       </c>
       <c r="J51">
-        <v>7709</v>
+        <v>7682.5</v>
       </c>
       <c r="K51" s="3">
-        <v>46317.522222222222</v>
+        <v>46317.606249999997</v>
       </c>
       <c r="L51" s="3">
-        <v>46317.522916666669</v>
+        <v>46317.611805555556</v>
       </c>
       <c r="M51" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="N51" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O51" s="4">
-        <v>120.64</v>
+        <v>70.64</v>
       </c>
       <c r="P51" s="4">
-        <v>1128.2</v>
+        <v>-654.64</v>
       </c>
       <c r="Q51" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R51" s="4">
-        <v>0</v>
-      </c>
-      <c r="S51" s="4">
-        <v>0</v>
-      </c>
-      <c r="T51" s="4">
-        <v>0</v>
-      </c>
-      <c r="U51" s="4">
-        <v>0</v>
-      </c>
       <c r="V51" s="4">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="W51" s="4">
-        <v>137.5</v>
+        <v>112.5</v>
       </c>
       <c r="X51" s="4">
-        <v>16.86</v>
+        <v>41.86</v>
       </c>
       <c r="Y51">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B52" s="2">
         <v>46317</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
         <v>26</v>
@@ -4248,75 +4284,63 @@
         <v>27</v>
       </c>
       <c r="F52" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>7687</v>
+      </c>
+      <c r="J52">
+        <v>7689.75</v>
+      </c>
+      <c r="K52" s="3">
+        <v>46317.629861111112</v>
+      </c>
+      <c r="L52" s="3">
+        <v>46317.633333333331</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
         <v>34</v>
-      </c>
-      <c r="H52">
-        <v>1</v>
-      </c>
-      <c r="I52">
-        <v>7701</v>
-      </c>
-      <c r="J52">
-        <v>7698.25</v>
-      </c>
-      <c r="K52" s="3">
-        <v>46317.527083333334</v>
-      </c>
-      <c r="L52" s="3">
-        <v>46317.530555555553</v>
-      </c>
-      <c r="M52" t="s">
-        <v>46</v>
-      </c>
-      <c r="N52" t="s">
-        <v>36</v>
       </c>
       <c r="O52" s="4">
         <v>133.13999999999999</v>
       </c>
       <c r="P52" s="4">
-        <v>1261.3399999999999</v>
+        <v>-521.5</v>
       </c>
       <c r="Q52" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R52" s="4">
-        <v>0</v>
-      </c>
-      <c r="S52" s="4">
-        <v>0</v>
-      </c>
-      <c r="T52" s="4">
-        <v>0</v>
-      </c>
-      <c r="U52" s="4">
-        <v>0</v>
-      </c>
       <c r="V52" s="4">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="W52" s="4">
-        <v>237.5</v>
+        <v>162.5</v>
       </c>
       <c r="X52" s="4">
-        <v>104.36</v>
+        <v>29.36</v>
       </c>
       <c r="Y52">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B53" s="2">
         <v>46317</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
@@ -4325,75 +4349,63 @@
         <v>27</v>
       </c>
       <c r="F53" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G53" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>7702.25</v>
+        <v>7688.25</v>
       </c>
       <c r="J53">
-        <v>7697.5</v>
+        <v>7685.25</v>
       </c>
       <c r="K53" s="3">
-        <v>46317.540277777778</v>
+        <v>46317.649305555555</v>
       </c>
       <c r="L53" s="3">
-        <v>46317.543055555558</v>
+        <v>46317.652777777781</v>
       </c>
       <c r="M53" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="N53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O53" s="4">
-        <v>-241.86</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P53" s="4">
-        <v>1019.48</v>
+        <v>-375.86</v>
       </c>
       <c r="Q53" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R53" s="4">
-        <v>0</v>
-      </c>
-      <c r="S53" s="4">
-        <v>0</v>
-      </c>
-      <c r="T53" s="4">
-        <v>0</v>
-      </c>
-      <c r="U53" s="4">
-        <v>0</v>
-      </c>
       <c r="V53" s="4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="W53" s="4">
-        <v>87.5</v>
+        <v>175</v>
       </c>
       <c r="X53" s="4">
-        <v>329.36</v>
+        <v>29.36</v>
       </c>
       <c r="Y53">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B54" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
@@ -4402,37 +4414,37 @@
         <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G54" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>7690</v>
+        <v>7733</v>
       </c>
       <c r="J54">
-        <v>7693</v>
+        <v>7732.75</v>
       </c>
       <c r="K54" s="3">
-        <v>46317.547222222223</v>
+        <v>46315.411111111112</v>
       </c>
       <c r="L54" s="3">
-        <v>46317.551388888889</v>
+        <v>46315.413194444445</v>
       </c>
       <c r="M54" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O54" s="4">
-        <v>-154.36000000000001</v>
+        <v>-16.86</v>
       </c>
       <c r="P54" s="4">
-        <v>865.12</v>
+        <v>-16.86</v>
       </c>
       <c r="Q54" s="4">
         <v>4.3600000000000003</v>
@@ -4450,104 +4462,104 @@
         <v>0</v>
       </c>
       <c r="V54" s="4">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="W54" s="4">
-        <v>175</v>
+        <v>237.5</v>
       </c>
       <c r="X54" s="4">
-        <v>329.36</v>
+        <v>254.36</v>
       </c>
       <c r="Y54">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" t="s">
+        <v>48</v>
+      </c>
+      <c r="G55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>7778.5</v>
+      </c>
+      <c r="J55">
+        <v>7775.75</v>
+      </c>
+      <c r="K55" s="3">
+        <v>46315.460416666669</v>
+      </c>
+      <c r="L55" s="3">
+        <v>46315.465277777781</v>
+      </c>
+      <c r="M55" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="2">
-        <v>46317</v>
-      </c>
-      <c r="C55">
-        <v>9</v>
-      </c>
-      <c r="D55" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" t="s">
-        <v>45</v>
-      </c>
-      <c r="G55" t="s">
-        <v>29</v>
-      </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55">
-        <v>7704.75</v>
-      </c>
-      <c r="J55">
-        <v>7697.75</v>
-      </c>
-      <c r="K55" s="3">
-        <v>46317.56527777778</v>
-      </c>
-      <c r="L55" s="3">
-        <v>46317.573611111111</v>
-      </c>
-      <c r="M55" t="s">
-        <v>48</v>
-      </c>
       <c r="N55" t="s">
+        <v>34</v>
+      </c>
+      <c r="O55" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P55" s="4">
+        <v>116.28</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R55" s="4">
+        <v>0</v>
+      </c>
+      <c r="S55" s="4">
+        <v>0</v>
+      </c>
+      <c r="T55" s="4">
+        <v>0</v>
+      </c>
+      <c r="U55" s="4">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <v>200</v>
+      </c>
+      <c r="W55" s="4">
+        <v>150</v>
+      </c>
+      <c r="X55" s="4">
+        <v>16.86</v>
+      </c>
+      <c r="Y55">
         <v>33</v>
-      </c>
-      <c r="O55" s="4">
-        <v>-354.36</v>
-      </c>
-      <c r="P55" s="4">
-        <v>510.76</v>
-      </c>
-      <c r="Q55" s="4">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="R55" s="4">
-        <v>0</v>
-      </c>
-      <c r="S55" s="4">
-        <v>0</v>
-      </c>
-      <c r="T55" s="4">
-        <v>0</v>
-      </c>
-      <c r="U55" s="4">
-        <v>0</v>
-      </c>
-      <c r="V55" s="4">
-        <v>362.5</v>
-      </c>
-      <c r="W55" s="4">
-        <v>37.5</v>
-      </c>
-      <c r="X55" s="4">
-        <v>391.86</v>
-      </c>
-      <c r="Y55">
-        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B56" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -4556,37 +4568,37 @@
         <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>7687.75</v>
+        <v>7772.75</v>
       </c>
       <c r="J56">
-        <v>7679.75</v>
+        <v>7755.75</v>
       </c>
       <c r="K56" s="3">
-        <v>46317.584027777775</v>
+        <v>46315.46597222222</v>
       </c>
       <c r="L56" s="3">
-        <v>46317.586111111108</v>
+        <v>46315.467361111114</v>
       </c>
       <c r="M56" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N56" t="s">
         <v>36</v>
       </c>
       <c r="O56" s="4">
-        <v>395.64</v>
+        <v>845.64</v>
       </c>
       <c r="P56" s="4">
-        <v>906.4</v>
+        <v>961.92</v>
       </c>
       <c r="Q56" s="4">
         <v>4.3600000000000003</v>
@@ -4604,27 +4616,27 @@
         <v>0</v>
       </c>
       <c r="V56" s="4">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="W56" s="4">
-        <v>425</v>
+        <v>862.5</v>
       </c>
       <c r="X56" s="4">
-        <v>29.36</v>
+        <v>16.86</v>
       </c>
       <c r="Y56">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B57" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C57">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D57" t="s">
         <v>26</v>
@@ -4633,7 +4645,7 @@
         <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G57" t="s">
         <v>29</v>
@@ -4642,28 +4654,28 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>7699.75</v>
+        <v>7763</v>
       </c>
       <c r="J57">
-        <v>7694</v>
+        <v>7766</v>
       </c>
       <c r="K57" s="3">
-        <v>46317.59652777778</v>
+        <v>46315.487500000003</v>
       </c>
       <c r="L57" s="3">
-        <v>46317.602083333331</v>
+        <v>46315.487500000003</v>
       </c>
       <c r="M57" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O57" s="4">
-        <v>-291.86</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P57" s="4">
-        <v>614.54</v>
+        <v>1107.56</v>
       </c>
       <c r="Q57" s="4">
         <v>4.3600000000000003</v>
@@ -4681,27 +4693,27 @@
         <v>0</v>
       </c>
       <c r="V57" s="4">
-        <v>300</v>
+        <v>37.5</v>
       </c>
       <c r="W57" s="4">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="X57" s="4">
-        <v>466.86</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y57">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B58" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C58">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D58" t="s">
         <v>26</v>
@@ -4710,37 +4722,37 @@
         <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G58" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>7684</v>
+        <v>7754</v>
       </c>
       <c r="J58">
-        <v>7682.5</v>
+        <v>7758.75</v>
       </c>
       <c r="K58" s="3">
-        <v>46317.606249999997</v>
+        <v>46315.512499999997</v>
       </c>
       <c r="L58" s="3">
-        <v>46317.611805555556</v>
+        <v>46315.518750000003</v>
       </c>
       <c r="M58" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N58" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="O58" s="4">
-        <v>70.64</v>
+        <v>-241.86</v>
       </c>
       <c r="P58" s="4">
-        <v>685.18</v>
+        <v>865.7</v>
       </c>
       <c r="Q58" s="4">
         <v>4.3600000000000003</v>
@@ -4758,27 +4770,27 @@
         <v>0</v>
       </c>
       <c r="V58" s="4">
-        <v>200</v>
+        <v>262.5</v>
       </c>
       <c r="W58" s="4">
-        <v>112.5</v>
+        <v>150</v>
       </c>
       <c r="X58" s="4">
-        <v>41.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y58">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B59" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C59">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D59" t="s">
         <v>26</v>
@@ -4787,7 +4799,7 @@
         <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G59" t="s">
         <v>29</v>
@@ -4796,28 +4808,28 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>7687</v>
+        <v>7766.25</v>
       </c>
       <c r="J59">
-        <v>7689.75</v>
+        <v>7762.25</v>
       </c>
       <c r="K59" s="3">
-        <v>46317.629861111112</v>
+        <v>46315.5625</v>
       </c>
       <c r="L59" s="3">
-        <v>46317.633333333331</v>
+        <v>46315.581250000003</v>
       </c>
       <c r="M59" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N59" t="s">
         <v>31</v>
       </c>
       <c r="O59" s="4">
-        <v>133.13999999999999</v>
+        <v>-204.36</v>
       </c>
       <c r="P59" s="4">
-        <v>818.32</v>
+        <v>661.34</v>
       </c>
       <c r="Q59" s="4">
         <v>4.3600000000000003</v>
@@ -4835,27 +4847,27 @@
         <v>0</v>
       </c>
       <c r="V59" s="4">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="W59" s="4">
-        <v>162.5</v>
+        <v>112.5</v>
       </c>
       <c r="X59" s="4">
-        <v>29.36</v>
+        <v>316.86</v>
       </c>
       <c r="Y59">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B60" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
@@ -4864,63 +4876,1834 @@
         <v>27</v>
       </c>
       <c r="F60" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G60" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60">
-        <v>7688.25</v>
+        <v>7754.5</v>
       </c>
       <c r="J60">
-        <v>7685.25</v>
+        <v>7753.25</v>
       </c>
       <c r="K60" s="3">
-        <v>46317.649305555555</v>
+        <v>46315.60833333333</v>
       </c>
       <c r="L60" s="3">
-        <v>46317.652777777781</v>
+        <v>46315.614583333336</v>
       </c>
       <c r="M60" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N60" t="s">
         <v>31</v>
       </c>
       <c r="O60" s="4">
+        <v>58.14</v>
+      </c>
+      <c r="P60" s="4">
+        <v>719.48</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R60" s="4">
+        <v>0</v>
+      </c>
+      <c r="S60" s="4">
+        <v>0</v>
+      </c>
+      <c r="T60" s="4">
+        <v>0</v>
+      </c>
+      <c r="U60" s="4">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4">
+        <v>75</v>
+      </c>
+      <c r="W60" s="4">
+        <v>287.5</v>
+      </c>
+      <c r="X60" s="4">
+        <v>229.36</v>
+      </c>
+      <c r="Y60">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C61">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>7750.25</v>
+      </c>
+      <c r="J61">
+        <v>7751</v>
+      </c>
+      <c r="K61" s="3">
+        <v>46315.63958333333</v>
+      </c>
+      <c r="L61" s="3">
+        <v>46315.643055555556</v>
+      </c>
+      <c r="M61" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" t="s">
+        <v>31</v>
+      </c>
+      <c r="O61" s="4">
+        <v>-41.86</v>
+      </c>
+      <c r="P61" s="4">
+        <v>677.62</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R61" s="4">
+        <v>0</v>
+      </c>
+      <c r="S61" s="4">
+        <v>0</v>
+      </c>
+      <c r="T61" s="4">
+        <v>0</v>
+      </c>
+      <c r="U61" s="4">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4">
+        <v>50</v>
+      </c>
+      <c r="W61" s="4">
+        <v>187.5</v>
+      </c>
+      <c r="X61" s="4">
+        <v>229.36</v>
+      </c>
+      <c r="Y61">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+      <c r="G62" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>7759.75</v>
+      </c>
+      <c r="J62">
+        <v>7755.5</v>
+      </c>
+      <c r="K62" s="3">
+        <v>46316.420138888891</v>
+      </c>
+      <c r="L62" s="3">
+        <v>46316.423611111109</v>
+      </c>
+      <c r="M62" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" t="s">
+        <v>36</v>
+      </c>
+      <c r="O62" s="4">
+        <v>208.14</v>
+      </c>
+      <c r="P62" s="4">
+        <v>208.14</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R62" s="4">
+        <v>0</v>
+      </c>
+      <c r="S62" s="4">
+        <v>0</v>
+      </c>
+      <c r="T62" s="4">
+        <v>0</v>
+      </c>
+      <c r="U62" s="4">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4">
+        <v>150</v>
+      </c>
+      <c r="W62" s="4">
+        <v>250</v>
+      </c>
+      <c r="X62" s="4">
+        <v>41.86</v>
+      </c>
+      <c r="Y62">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" t="s">
+        <v>48</v>
+      </c>
+      <c r="G63" t="s">
+        <v>29</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>7762.25</v>
+      </c>
+      <c r="J63">
+        <v>7765</v>
+      </c>
+      <c r="K63" s="3">
+        <v>46316.436111111114</v>
+      </c>
+      <c r="L63" s="3">
+        <v>46316.438194444447</v>
+      </c>
+      <c r="M63" t="s">
+        <v>52</v>
+      </c>
+      <c r="N63" t="s">
+        <v>34</v>
+      </c>
+      <c r="O63" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P63" s="4">
+        <v>341.28</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R63" s="4">
+        <v>0</v>
+      </c>
+      <c r="S63" s="4">
+        <v>0</v>
+      </c>
+      <c r="T63" s="4">
+        <v>0</v>
+      </c>
+      <c r="U63" s="4">
+        <v>0</v>
+      </c>
+      <c r="V63" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="W63" s="4">
+        <v>150</v>
+      </c>
+      <c r="X63" s="4">
+        <v>16.86</v>
+      </c>
+      <c r="Y63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s">
+        <v>48</v>
+      </c>
+      <c r="G64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>7774.25</v>
+      </c>
+      <c r="J64">
+        <v>7777.25</v>
+      </c>
+      <c r="K64" s="3">
+        <v>46316.449305555558</v>
+      </c>
+      <c r="L64" s="3">
+        <v>46316.45208333333</v>
+      </c>
+      <c r="M64" t="s">
+        <v>49</v>
+      </c>
+      <c r="N64" t="s">
+        <v>36</v>
+      </c>
+      <c r="O64" s="4">
         <v>145.63999999999999</v>
       </c>
-      <c r="P60" s="4">
+      <c r="P64" s="4">
+        <v>486.92</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R64" s="4">
+        <v>0</v>
+      </c>
+      <c r="S64" s="4">
+        <v>0</v>
+      </c>
+      <c r="T64" s="4">
+        <v>0</v>
+      </c>
+      <c r="U64" s="4">
+        <v>0</v>
+      </c>
+      <c r="V64" s="4">
+        <v>25</v>
+      </c>
+      <c r="W64" s="4">
+        <v>250</v>
+      </c>
+      <c r="X64" s="4">
+        <v>104.36</v>
+      </c>
+      <c r="Y64">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" t="s">
+        <v>48</v>
+      </c>
+      <c r="G65" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>7788.5</v>
+      </c>
+      <c r="J65">
+        <v>7791.75</v>
+      </c>
+      <c r="K65" s="3">
+        <v>46316.518750000003</v>
+      </c>
+      <c r="L65" s="3">
+        <v>46316.526388888888</v>
+      </c>
+      <c r="M65" t="s">
+        <v>50</v>
+      </c>
+      <c r="N65" t="s">
+        <v>31</v>
+      </c>
+      <c r="O65" s="4">
+        <v>-166.86</v>
+      </c>
+      <c r="P65" s="4">
+        <v>320.06</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R65" s="4">
+        <v>0</v>
+      </c>
+      <c r="S65" s="4">
+        <v>0</v>
+      </c>
+      <c r="T65" s="4">
+        <v>0</v>
+      </c>
+      <c r="U65" s="4">
+        <v>0</v>
+      </c>
+      <c r="V65" s="4">
+        <v>175</v>
+      </c>
+      <c r="W65" s="4">
+        <v>50</v>
+      </c>
+      <c r="X65" s="4">
+        <v>216.86</v>
+      </c>
+      <c r="Y65">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s">
+        <v>48</v>
+      </c>
+      <c r="G66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>7799.5</v>
+      </c>
+      <c r="J66">
+        <v>7798.75</v>
+      </c>
+      <c r="K66" s="3">
+        <v>46316.527083333334</v>
+      </c>
+      <c r="L66" s="3">
+        <v>46316.527777777781</v>
+      </c>
+      <c r="M66" t="s">
+        <v>49</v>
+      </c>
+      <c r="N66" t="s">
+        <v>31</v>
+      </c>
+      <c r="O66" s="4">
+        <v>-41.86</v>
+      </c>
+      <c r="P66" s="4">
+        <v>278.2</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R66" s="4">
+        <v>0</v>
+      </c>
+      <c r="S66" s="4">
+        <v>0</v>
+      </c>
+      <c r="T66" s="4">
+        <v>0</v>
+      </c>
+      <c r="U66" s="4">
+        <v>0</v>
+      </c>
+      <c r="V66" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="W66" s="4">
+        <v>350</v>
+      </c>
+      <c r="X66" s="4">
+        <v>391.86</v>
+      </c>
+      <c r="Y66">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" t="s">
+        <v>48</v>
+      </c>
+      <c r="G67" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>7805</v>
+      </c>
+      <c r="J67">
+        <v>7802.5</v>
+      </c>
+      <c r="K67" s="3">
+        <v>46316.615972222222</v>
+      </c>
+      <c r="L67" s="3">
+        <v>46316.616666666669</v>
+      </c>
+      <c r="M67" t="s">
+        <v>50</v>
+      </c>
+      <c r="N67" t="s">
+        <v>34</v>
+      </c>
+      <c r="O67" s="4">
+        <v>120.64</v>
+      </c>
+      <c r="P67" s="4">
+        <v>398.84</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R67" s="4">
+        <v>0</v>
+      </c>
+      <c r="S67" s="4">
+        <v>0</v>
+      </c>
+      <c r="T67" s="4">
+        <v>0</v>
+      </c>
+      <c r="U67" s="4">
+        <v>0</v>
+      </c>
+      <c r="V67" s="4">
+        <v>100</v>
+      </c>
+      <c r="W67" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="X67" s="4">
+        <v>41.86</v>
+      </c>
+      <c r="Y67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C68">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s">
+        <v>48</v>
+      </c>
+      <c r="G68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>7798.75</v>
+      </c>
+      <c r="J68">
+        <v>7797.5</v>
+      </c>
+      <c r="K68" s="3">
+        <v>46316.617361111108</v>
+      </c>
+      <c r="L68" s="3">
+        <v>46316.619444444441</v>
+      </c>
+      <c r="M68" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" s="4">
+        <v>58.14</v>
+      </c>
+      <c r="P68" s="4">
+        <v>456.98</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R68" s="4">
+        <v>0</v>
+      </c>
+      <c r="S68" s="4">
+        <v>0</v>
+      </c>
+      <c r="T68" s="4">
+        <v>0</v>
+      </c>
+      <c r="U68" s="4">
+        <v>0</v>
+      </c>
+      <c r="V68" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="W68" s="4">
+        <v>250</v>
+      </c>
+      <c r="X68" s="4">
+        <v>191.86</v>
+      </c>
+      <c r="Y68">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>7786.5</v>
+      </c>
+      <c r="J69">
+        <v>7789.25</v>
+      </c>
+      <c r="K69" s="3">
+        <v>46316.636111111111</v>
+      </c>
+      <c r="L69" s="3">
+        <v>46316.636805555558</v>
+      </c>
+      <c r="M69" t="s">
+        <v>52</v>
+      </c>
+      <c r="N69" t="s">
+        <v>34</v>
+      </c>
+      <c r="O69" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P69" s="4">
+        <v>590.12</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R69" s="4">
+        <v>0</v>
+      </c>
+      <c r="S69" s="4">
+        <v>0</v>
+      </c>
+      <c r="T69" s="4">
+        <v>0</v>
+      </c>
+      <c r="U69" s="4">
+        <v>0</v>
+      </c>
+      <c r="V69" s="4">
+        <v>25</v>
+      </c>
+      <c r="W69" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="X69" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="Y69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>54</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" t="s">
+        <v>48</v>
+      </c>
+      <c r="G70" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>7727.25</v>
+      </c>
+      <c r="J70">
+        <v>7718.5</v>
+      </c>
+      <c r="K70" s="3">
+        <v>46317.422222222223</v>
+      </c>
+      <c r="L70" s="3">
+        <v>46317.427083333336</v>
+      </c>
+      <c r="M70" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" t="s">
+        <v>36</v>
+      </c>
+      <c r="O70" s="4">
+        <v>433.14</v>
+      </c>
+      <c r="P70" s="4">
+        <v>433.14</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R70" s="4">
+        <v>0</v>
+      </c>
+      <c r="S70" s="4">
+        <v>0</v>
+      </c>
+      <c r="T70" s="4">
+        <v>0</v>
+      </c>
+      <c r="U70" s="4">
+        <v>0</v>
+      </c>
+      <c r="V70" s="4">
+        <v>100</v>
+      </c>
+      <c r="W70" s="4">
+        <v>462.5</v>
+      </c>
+      <c r="X70" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y70">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>54</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s">
+        <v>48</v>
+      </c>
+      <c r="G71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>7695</v>
+      </c>
+      <c r="J71">
+        <v>7689.75</v>
+      </c>
+      <c r="K71" s="3">
+        <v>46317.454861111109</v>
+      </c>
+      <c r="L71" s="3">
+        <v>46317.454861111109</v>
+      </c>
+      <c r="M71" t="s">
+        <v>52</v>
+      </c>
+      <c r="N71" t="s">
+        <v>31</v>
+      </c>
+      <c r="O71" s="4">
+        <v>-266.86</v>
+      </c>
+      <c r="P71" s="4">
+        <v>166.28</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R71" s="4">
+        <v>0</v>
+      </c>
+      <c r="S71" s="4">
+        <v>0</v>
+      </c>
+      <c r="T71" s="4">
+        <v>0</v>
+      </c>
+      <c r="U71" s="4">
+        <v>0</v>
+      </c>
+      <c r="V71" s="4">
+        <v>300</v>
+      </c>
+      <c r="W71" s="4">
+        <v>75</v>
+      </c>
+      <c r="X71" s="4">
+        <v>341.86</v>
+      </c>
+      <c r="Y71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" t="s">
+        <v>48</v>
+      </c>
+      <c r="G72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>7700.75</v>
+      </c>
+      <c r="J72">
+        <v>7712</v>
+      </c>
+      <c r="K72" s="3">
+        <v>46317.470833333333</v>
+      </c>
+      <c r="L72" s="3">
+        <v>46317.474999999999</v>
+      </c>
+      <c r="M72" t="s">
+        <v>49</v>
+      </c>
+      <c r="N72" t="s">
+        <v>36</v>
+      </c>
+      <c r="O72" s="4">
+        <v>558.14</v>
+      </c>
+      <c r="P72" s="4">
+        <v>724.42</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R72" s="4">
+        <v>0</v>
+      </c>
+      <c r="S72" s="4">
+        <v>0</v>
+      </c>
+      <c r="T72" s="4">
+        <v>0</v>
+      </c>
+      <c r="U72" s="4">
+        <v>0</v>
+      </c>
+      <c r="V72" s="4">
+        <v>100</v>
+      </c>
+      <c r="W72" s="4">
+        <v>587.5</v>
+      </c>
+      <c r="X72" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y72">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C73">
+        <v>4</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" t="s">
+        <v>48</v>
+      </c>
+      <c r="G73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>7711</v>
+      </c>
+      <c r="J73">
+        <v>7716.75</v>
+      </c>
+      <c r="K73" s="3">
+        <v>46317.49722222222</v>
+      </c>
+      <c r="L73" s="3">
+        <v>46317.5</v>
+      </c>
+      <c r="M73" t="s">
+        <v>49</v>
+      </c>
+      <c r="N73" t="s">
+        <v>36</v>
+      </c>
+      <c r="O73" s="4">
+        <v>283.14</v>
+      </c>
+      <c r="P73" s="4">
+        <v>1007.56</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R73" s="4">
+        <v>0</v>
+      </c>
+      <c r="S73" s="4">
+        <v>0</v>
+      </c>
+      <c r="T73" s="4">
+        <v>0</v>
+      </c>
+      <c r="U73" s="4">
+        <v>0</v>
+      </c>
+      <c r="V73" s="4">
+        <v>62.5</v>
+      </c>
+      <c r="W73" s="4">
+        <v>312.5</v>
+      </c>
+      <c r="X73" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y73">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C74">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>7711.5</v>
+      </c>
+      <c r="J74">
+        <v>7709</v>
+      </c>
+      <c r="K74" s="3">
+        <v>46317.522222222222</v>
+      </c>
+      <c r="L74" s="3">
+        <v>46317.522916666669</v>
+      </c>
+      <c r="M74" t="s">
+        <v>50</v>
+      </c>
+      <c r="N74" t="s">
+        <v>34</v>
+      </c>
+      <c r="O74" s="4">
+        <v>120.64</v>
+      </c>
+      <c r="P74" s="4">
+        <v>1128.2</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R74" s="4">
+        <v>0</v>
+      </c>
+      <c r="S74" s="4">
+        <v>0</v>
+      </c>
+      <c r="T74" s="4">
+        <v>0</v>
+      </c>
+      <c r="U74" s="4">
+        <v>0</v>
+      </c>
+      <c r="V74" s="4">
+        <v>50</v>
+      </c>
+      <c r="W74" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="X74" s="4">
+        <v>16.86</v>
+      </c>
+      <c r="Y74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C75">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" t="s">
+        <v>48</v>
+      </c>
+      <c r="G75" t="s">
+        <v>32</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>7701</v>
+      </c>
+      <c r="J75">
+        <v>7698.25</v>
+      </c>
+      <c r="K75" s="3">
+        <v>46317.527083333334</v>
+      </c>
+      <c r="L75" s="3">
+        <v>46317.530555555553</v>
+      </c>
+      <c r="M75" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" t="s">
+        <v>36</v>
+      </c>
+      <c r="O75" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P75" s="4">
+        <v>1261.3399999999999</v>
+      </c>
+      <c r="Q75" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R75" s="4">
+        <v>0</v>
+      </c>
+      <c r="S75" s="4">
+        <v>0</v>
+      </c>
+      <c r="T75" s="4">
+        <v>0</v>
+      </c>
+      <c r="U75" s="4">
+        <v>0</v>
+      </c>
+      <c r="V75" s="4">
+        <v>50</v>
+      </c>
+      <c r="W75" s="4">
+        <v>237.5</v>
+      </c>
+      <c r="X75" s="4">
+        <v>104.36</v>
+      </c>
+      <c r="Y75">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C76">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" t="s">
+        <v>48</v>
+      </c>
+      <c r="G76" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>7702.25</v>
+      </c>
+      <c r="J76">
+        <v>7697.5</v>
+      </c>
+      <c r="K76" s="3">
+        <v>46317.540277777778</v>
+      </c>
+      <c r="L76" s="3">
+        <v>46317.543055555558</v>
+      </c>
+      <c r="M76" t="s">
+        <v>52</v>
+      </c>
+      <c r="N76" t="s">
+        <v>31</v>
+      </c>
+      <c r="O76" s="4">
+        <v>-241.86</v>
+      </c>
+      <c r="P76" s="4">
+        <v>1019.48</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R76" s="4">
+        <v>0</v>
+      </c>
+      <c r="S76" s="4">
+        <v>0</v>
+      </c>
+      <c r="T76" s="4">
+        <v>0</v>
+      </c>
+      <c r="U76" s="4">
+        <v>0</v>
+      </c>
+      <c r="V76" s="4">
+        <v>250</v>
+      </c>
+      <c r="W76" s="4">
+        <v>87.5</v>
+      </c>
+      <c r="X76" s="4">
+        <v>329.36</v>
+      </c>
+      <c r="Y76">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C77">
+        <v>8</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>7690</v>
+      </c>
+      <c r="J77">
+        <v>7693</v>
+      </c>
+      <c r="K77" s="3">
+        <v>46317.547222222223</v>
+      </c>
+      <c r="L77" s="3">
+        <v>46317.551388888889</v>
+      </c>
+      <c r="M77" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" t="s">
+        <v>36</v>
+      </c>
+      <c r="O77" s="4">
+        <v>-154.36000000000001</v>
+      </c>
+      <c r="P77" s="4">
+        <v>865.12</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R77" s="4">
+        <v>0</v>
+      </c>
+      <c r="S77" s="4">
+        <v>0</v>
+      </c>
+      <c r="T77" s="4">
+        <v>0</v>
+      </c>
+      <c r="U77" s="4">
+        <v>0</v>
+      </c>
+      <c r="V77" s="4">
+        <v>150</v>
+      </c>
+      <c r="W77" s="4">
+        <v>175</v>
+      </c>
+      <c r="X77" s="4">
+        <v>329.36</v>
+      </c>
+      <c r="Y77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>54</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C78">
+        <v>9</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" t="s">
+        <v>29</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>7704.75</v>
+      </c>
+      <c r="J78">
+        <v>7697.75</v>
+      </c>
+      <c r="K78" s="3">
+        <v>46317.56527777778</v>
+      </c>
+      <c r="L78" s="3">
+        <v>46317.573611111111</v>
+      </c>
+      <c r="M78" t="s">
+        <v>49</v>
+      </c>
+      <c r="N78" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" s="4">
+        <v>-354.36</v>
+      </c>
+      <c r="P78" s="4">
+        <v>510.76</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R78" s="4">
+        <v>0</v>
+      </c>
+      <c r="S78" s="4">
+        <v>0</v>
+      </c>
+      <c r="T78" s="4">
+        <v>0</v>
+      </c>
+      <c r="U78" s="4">
+        <v>0</v>
+      </c>
+      <c r="V78" s="4">
+        <v>362.5</v>
+      </c>
+      <c r="W78" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="X78" s="4">
+        <v>391.86</v>
+      </c>
+      <c r="Y78">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>54</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C79">
+        <v>10</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79" t="s">
+        <v>48</v>
+      </c>
+      <c r="G79" t="s">
+        <v>32</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>7687.75</v>
+      </c>
+      <c r="J79">
+        <v>7679.75</v>
+      </c>
+      <c r="K79" s="3">
+        <v>46317.584027777775</v>
+      </c>
+      <c r="L79" s="3">
+        <v>46317.586111111108</v>
+      </c>
+      <c r="M79" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" t="s">
+        <v>36</v>
+      </c>
+      <c r="O79" s="4">
+        <v>395.64</v>
+      </c>
+      <c r="P79" s="4">
+        <v>906.4</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R79" s="4">
+        <v>0</v>
+      </c>
+      <c r="S79" s="4">
+        <v>0</v>
+      </c>
+      <c r="T79" s="4">
+        <v>0</v>
+      </c>
+      <c r="U79" s="4">
+        <v>0</v>
+      </c>
+      <c r="V79" s="4">
+        <v>25</v>
+      </c>
+      <c r="W79" s="4">
+        <v>425</v>
+      </c>
+      <c r="X79" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y79">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C80">
+        <v>11</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" t="s">
+        <v>48</v>
+      </c>
+      <c r="G80" t="s">
+        <v>29</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>7699.75</v>
+      </c>
+      <c r="J80">
+        <v>7694</v>
+      </c>
+      <c r="K80" s="3">
+        <v>46317.59652777778</v>
+      </c>
+      <c r="L80" s="3">
+        <v>46317.602083333331</v>
+      </c>
+      <c r="M80" t="s">
+        <v>49</v>
+      </c>
+      <c r="N80" t="s">
+        <v>31</v>
+      </c>
+      <c r="O80" s="4">
+        <v>-291.86</v>
+      </c>
+      <c r="P80" s="4">
+        <v>614.54</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R80" s="4">
+        <v>0</v>
+      </c>
+      <c r="S80" s="4">
+        <v>0</v>
+      </c>
+      <c r="T80" s="4">
+        <v>0</v>
+      </c>
+      <c r="U80" s="4">
+        <v>0</v>
+      </c>
+      <c r="V80" s="4">
+        <v>300</v>
+      </c>
+      <c r="W80" s="4">
+        <v>175</v>
+      </c>
+      <c r="X80" s="4">
+        <v>466.86</v>
+      </c>
+      <c r="Y80">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C81">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" t="s">
+        <v>48</v>
+      </c>
+      <c r="G81" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>7684</v>
+      </c>
+      <c r="J81">
+        <v>7682.5</v>
+      </c>
+      <c r="K81" s="3">
+        <v>46317.606249999997</v>
+      </c>
+      <c r="L81" s="3">
+        <v>46317.611805555556</v>
+      </c>
+      <c r="M81" t="s">
+        <v>51</v>
+      </c>
+      <c r="N81" t="s">
+        <v>36</v>
+      </c>
+      <c r="O81" s="4">
+        <v>70.64</v>
+      </c>
+      <c r="P81" s="4">
+        <v>685.18</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R81" s="4">
+        <v>0</v>
+      </c>
+      <c r="S81" s="4">
+        <v>0</v>
+      </c>
+      <c r="T81" s="4">
+        <v>0</v>
+      </c>
+      <c r="U81" s="4">
+        <v>0</v>
+      </c>
+      <c r="V81" s="4">
+        <v>200</v>
+      </c>
+      <c r="W81" s="4">
+        <v>112.5</v>
+      </c>
+      <c r="X81" s="4">
+        <v>41.86</v>
+      </c>
+      <c r="Y81">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>54</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C82">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" t="s">
+        <v>48</v>
+      </c>
+      <c r="G82" t="s">
+        <v>29</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>7687</v>
+      </c>
+      <c r="J82">
+        <v>7689.75</v>
+      </c>
+      <c r="K82" s="3">
+        <v>46317.629861111112</v>
+      </c>
+      <c r="L82" s="3">
+        <v>46317.633333333331</v>
+      </c>
+      <c r="M82" t="s">
+        <v>52</v>
+      </c>
+      <c r="N82" t="s">
+        <v>34</v>
+      </c>
+      <c r="O82" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P82" s="4">
+        <v>818.32</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R82" s="4">
+        <v>0</v>
+      </c>
+      <c r="S82" s="4">
+        <v>0</v>
+      </c>
+      <c r="T82" s="4">
+        <v>0</v>
+      </c>
+      <c r="U82" s="4">
+        <v>0</v>
+      </c>
+      <c r="V82" s="4">
+        <v>175</v>
+      </c>
+      <c r="W82" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="X82" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y82">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>54</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C83">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F83" t="s">
+        <v>48</v>
+      </c>
+      <c r="G83" t="s">
+        <v>32</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>7688.25</v>
+      </c>
+      <c r="J83">
+        <v>7685.25</v>
+      </c>
+      <c r="K83" s="3">
+        <v>46317.649305555555</v>
+      </c>
+      <c r="L83" s="3">
+        <v>46317.652777777781</v>
+      </c>
+      <c r="M83" t="s">
+        <v>50</v>
+      </c>
+      <c r="N83" t="s">
+        <v>34</v>
+      </c>
+      <c r="O83" s="4">
+        <v>145.63999999999999</v>
+      </c>
+      <c r="P83" s="4">
         <v>963.96</v>
       </c>
-      <c r="Q60" s="4">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="R60" s="4">
-        <v>0</v>
-      </c>
-      <c r="S60" s="4">
-        <v>0</v>
-      </c>
-      <c r="T60" s="4">
-        <v>0</v>
-      </c>
-      <c r="U60" s="4">
-        <v>0</v>
-      </c>
-      <c r="V60" s="4">
+      <c r="Q83" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R83" s="4">
+        <v>0</v>
+      </c>
+      <c r="S83" s="4">
+        <v>0</v>
+      </c>
+      <c r="T83" s="4">
+        <v>0</v>
+      </c>
+      <c r="U83" s="4">
+        <v>0</v>
+      </c>
+      <c r="V83" s="4">
         <v>100</v>
       </c>
-      <c r="W60" s="4">
+      <c r="W83" s="4">
         <v>175</v>
       </c>
-      <c r="X60" s="4">
+      <c r="X83" s="4">
         <v>29.36</v>
       </c>
-      <c r="Y60">
+      <c r="Y83">
         <v>21</v>
       </c>
     </row>
@@ -4930,8 +6713,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D204CE-67BB-4C95-9CC4-F666B8C4CDA0}">
-  <dimension ref="A1:E23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E6661C-AA91-4C8A-BCF8-86A021BC4B3F}">
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -4946,21 +6729,21 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -4969,32 +6752,32 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>70.64</v>
+        <v>-221.22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>-204.36</v>
+        <v>133.13999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -5003,15 +6786,15 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>266.27999999999997</v>
+        <v>620.05999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -5020,15 +6803,15 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>266.27999999999997</v>
+        <v>145.63999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -5040,63 +6823,63 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>103.78</v>
+        <v>-33.72</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>-46.22</v>
+        <v>-329.94</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>-79.36</v>
+        <v>-16.86</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>-204.36</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -5105,15 +6888,15 @@
         <v>40</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>-897.38</v>
+        <v>-204.36</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -5122,15 +6905,15 @@
         <v>35</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>878.2</v>
+        <v>266.27999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
@@ -5139,129 +6922,129 @@
         <v>37</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>-375.58</v>
+        <v>266.27999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>195.06</v>
+        <v>103.78</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>-238.08</v>
+        <v>-46.22</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>266.27999999999997</v>
+        <v>-79.36</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>266.27999999999997</v>
+        <v>-204.36</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>266.27999999999997</v>
+        <v>-897.38</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>103.78</v>
+        <v>878.2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>-46.22</v>
+        <v>-375.58</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5269,16 +7052,16 @@
         <v>46317</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>878.2</v>
+        <v>195.06</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5286,16 +7069,16 @@
         <v>46317</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21">
-        <v>-375.58</v>
+        <v>-238.08</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5303,24 +7086,24 @@
         <v>46317</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>195.06</v>
+        <v>266.27999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
         <v>49</v>
@@ -5329,6 +7112,193 @@
         <v>2</v>
       </c>
       <c r="E23">
+        <v>-221.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>133.13999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>620.05999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>145.63999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>266.27999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>266.27999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>103.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>-46.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>878.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>-375.58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>195.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
         <v>266.27999999999997</v>
       </c>
     </row>

--- a/ReportesTrades/Tabla_Maestra_Trades.xlsx
+++ b/ReportesTrades/Tabla_Maestra_Trades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Documents\NinjaTrader 8\bin\Custom\ReportesTrades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2801731-89DD-4AF9-9005-397EACE20C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4C8D9B3-4C13-4907-AD0D-30686DA8F5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{ED65FE19-A058-430B-85C9-6EBD53BB409C}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B93D3E58-490D-438F-8130-361BB9F58CC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Trades" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="62">
   <si>
     <t>ArchivoOrigen</t>
   </si>
@@ -117,7 +117,7 @@
     <t>Bars</t>
   </si>
   <si>
-    <t>NTMatrix10202026.xlsx</t>
+    <t>NTMatrix10192026.xlsx</t>
   </si>
   <si>
     <t>ES 12-26</t>
@@ -129,40 +129,46 @@
     <t>Tick610_KeltnerMatrixES</t>
   </si>
   <si>
-    <t>Long</t>
-  </si>
-  <si>
-    <t>MatrixLong_Surfer</t>
-  </si>
-  <si>
-    <t>Stop loss</t>
-  </si>
-  <si>
     <t>Short</t>
   </si>
   <si>
     <t>MatrixShort_Zona1</t>
   </si>
   <si>
+    <t>Stop loss</t>
+  </si>
+  <si>
+    <t>MatrixShort_Inner</t>
+  </si>
+  <si>
     <t>Profit target</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>MatrixLong_Inner</t>
+  </si>
+  <si>
+    <t>MatrixLong_Surfer</t>
+  </si>
+  <si>
+    <t>Exit_Surfer_CicloTerminado</t>
+  </si>
+  <si>
+    <t>SL_Candado_Surfer</t>
   </si>
   <si>
     <t>MatrixShort_Surfer</t>
   </si>
   <si>
-    <t>Exit_Surfer_CicloTerminado</t>
-  </si>
-  <si>
     <t>MatrixLong_Zona1</t>
-  </si>
-  <si>
-    <t>MatrixShort_Inner</t>
   </si>
   <si>
     <t>Close position</t>
   </si>
   <si>
-    <t>MatrixLong_Inner</t>
+    <t>NTMatrix10202026.xlsx</t>
   </si>
   <si>
     <t>StopReverse_CierreLargo</t>
@@ -183,22 +189,25 @@
     <t>NTMatrix10222026.xlsx</t>
   </si>
   <si>
-    <t>NTSniperSurfer10202026.xlsx</t>
+    <t>NTSniperSurfer10192026.xlsx</t>
   </si>
   <si>
     <t>Tick610_SniperSurferES</t>
   </si>
   <si>
-    <t>SniperSurfer_Long</t>
+    <t>SniperZona1_Short</t>
   </si>
   <si>
-    <t>SniperZona1_Short</t>
+    <t>SniperSurfer_Long</t>
   </si>
   <si>
     <t>SniperSurfer_Short</t>
   </si>
   <si>
     <t>SniperZona1_Long</t>
+  </si>
+  <si>
+    <t>NTSniperSurfer10202026.xlsx</t>
   </si>
   <si>
     <t>NTSniperSurfer10212026.xlsx</t>
@@ -602,8 +611,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6BE70E0-9802-43AC-9B06-E3B4656B0DCB}">
-  <dimension ref="A1:Y83"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{798BA75A-788C-4262-97FF-9C0A5094A8F7}">
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -710,7 +719,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -734,13 +743,13 @@
         <v>7733</v>
       </c>
       <c r="J2">
-        <v>7732.75</v>
+        <v>7736.5</v>
       </c>
       <c r="K2" s="3">
-        <v>46315.411111111112</v>
+        <v>46314.412499999999</v>
       </c>
       <c r="L2" s="3">
-        <v>46315.413194444445</v>
+        <v>46314.413888888892</v>
       </c>
       <c r="M2" t="s">
         <v>30</v>
@@ -749,10 +758,10 @@
         <v>31</v>
       </c>
       <c r="O2" s="4">
-        <v>-16.86</v>
+        <v>-179.36</v>
       </c>
       <c r="P2" s="4">
-        <v>-16.86</v>
+        <v>-179.36</v>
       </c>
       <c r="Q2" s="4">
         <v>4.3600000000000003</v>
@@ -773,10 +782,10 @@
         <v>175</v>
       </c>
       <c r="W2" s="4">
-        <v>237.5</v>
+        <v>50</v>
       </c>
       <c r="X2" s="4">
-        <v>254.36</v>
+        <v>229.36</v>
       </c>
       <c r="Y2">
         <v>17</v>
@@ -787,7 +796,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -802,34 +811,34 @@
         <v>28</v>
       </c>
       <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>7734</v>
+      </c>
+      <c r="J3">
+        <v>7729</v>
+      </c>
+      <c r="K3" s="3">
+        <v>46314.414583333331</v>
+      </c>
+      <c r="L3" s="3">
+        <v>46314.418749999997</v>
+      </c>
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>7778.5</v>
-      </c>
-      <c r="J3">
-        <v>7775.75</v>
-      </c>
-      <c r="K3" s="3">
-        <v>46315.460416666669</v>
-      </c>
-      <c r="L3" s="3">
-        <v>46315.465277777781</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
       <c r="O3" s="4">
-        <v>133.13999999999999</v>
+        <v>245.64</v>
       </c>
       <c r="P3" s="4">
-        <v>116.28</v>
+        <v>66.28</v>
       </c>
       <c r="Q3" s="4">
         <v>4.3600000000000003</v>
@@ -847,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="V3" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="W3" s="4">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="X3" s="4">
-        <v>16.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y3">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -864,7 +873,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -879,34 +888,34 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>7772.75</v>
+        <v>7735.25</v>
       </c>
       <c r="J4">
-        <v>7755.75</v>
+        <v>7737.75</v>
       </c>
       <c r="K4" s="3">
-        <v>46315.46597222222</v>
+        <v>46314.420138888891</v>
       </c>
       <c r="L4" s="3">
-        <v>46315.467361111114</v>
+        <v>46314.423611111109</v>
       </c>
       <c r="M4" t="s">
         <v>35</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O4" s="4">
-        <v>845.64</v>
+        <v>120.64</v>
       </c>
       <c r="P4" s="4">
-        <v>961.92</v>
+        <v>186.92</v>
       </c>
       <c r="Q4" s="4">
         <v>4.3600000000000003</v>
@@ -924,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="V4" s="4">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="W4" s="4">
-        <v>862.5</v>
+        <v>137.5</v>
       </c>
       <c r="X4" s="4">
         <v>16.86</v>
       </c>
       <c r="Y4">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -941,7 +950,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -956,34 +965,34 @@
         <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>7763</v>
+        <v>7743.25</v>
       </c>
       <c r="J5">
-        <v>7766</v>
+        <v>7753.25</v>
       </c>
       <c r="K5" s="3">
-        <v>46315.487500000003</v>
+        <v>46314.425694444442</v>
       </c>
       <c r="L5" s="3">
-        <v>46315.487500000003</v>
+        <v>46314.427083333336</v>
       </c>
       <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
         <v>37</v>
       </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
       <c r="O5" s="4">
-        <v>145.63999999999999</v>
+        <v>495.64</v>
       </c>
       <c r="P5" s="4">
-        <v>1107.56</v>
+        <v>682.56</v>
       </c>
       <c r="Q5" s="4">
         <v>4.3600000000000003</v>
@@ -1004,13 +1013,13 @@
         <v>37.5</v>
       </c>
       <c r="W5" s="4">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="X5" s="4">
-        <v>4.3600000000000003</v>
+        <v>154.36000000000001</v>
       </c>
       <c r="Y5">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1018,7 +1027,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1033,34 +1042,34 @@
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>7759.25</v>
+        <v>7746.5</v>
       </c>
       <c r="J6">
-        <v>7762.25</v>
+        <v>7743.5</v>
       </c>
       <c r="K6" s="3">
-        <v>46315.489583333336</v>
+        <v>46314.438194444447</v>
       </c>
       <c r="L6" s="3">
-        <v>46315.491666666669</v>
+        <v>46314.438888888886</v>
       </c>
       <c r="M6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="O6" s="4">
-        <v>-154.36000000000001</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P6" s="4">
-        <v>953.2</v>
+        <v>828.2</v>
       </c>
       <c r="Q6" s="4">
         <v>4.3600000000000003</v>
@@ -1078,16 +1087,16 @@
         <v>0</v>
       </c>
       <c r="V6" s="4">
-        <v>225</v>
+        <v>137.5</v>
       </c>
       <c r="W6" s="4">
-        <v>112.5</v>
+        <v>175</v>
       </c>
       <c r="X6" s="4">
-        <v>266.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y6">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1095,7 +1104,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1116,28 +1125,28 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>7762.25</v>
+        <v>7744</v>
       </c>
       <c r="J7">
-        <v>7758.25</v>
+        <v>7747.25</v>
       </c>
       <c r="K7" s="3">
-        <v>46315.491666666669</v>
+        <v>46314.446527777778</v>
       </c>
       <c r="L7" s="3">
-        <v>46315.493750000001</v>
+        <v>46314.447916666664</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="N7" t="s">
         <v>31</v>
       </c>
       <c r="O7" s="4">
-        <v>-204.36</v>
+        <v>-166.86</v>
       </c>
       <c r="P7" s="4">
-        <v>748.84</v>
+        <v>661.34</v>
       </c>
       <c r="Q7" s="4">
         <v>4.3600000000000003</v>
@@ -1155,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="V7" s="4">
-        <v>212.5</v>
+        <v>162.5</v>
       </c>
       <c r="W7" s="4">
-        <v>37.5</v>
+        <v>162.5</v>
       </c>
       <c r="X7" s="4">
-        <v>241.86</v>
+        <v>329.36</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1172,7 +1181,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1193,28 +1202,28 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>7763.25</v>
+        <v>7745.25</v>
       </c>
       <c r="J8">
-        <v>7767.25</v>
+        <v>7749.25</v>
       </c>
       <c r="K8" s="3">
-        <v>46315.495833333334</v>
+        <v>46314.45</v>
       </c>
       <c r="L8" s="3">
-        <v>46315.495833333334</v>
+        <v>46314.454861111109</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O8" s="4">
-        <v>195.64</v>
+        <v>-204.36</v>
       </c>
       <c r="P8" s="4">
-        <v>944.48</v>
+        <v>456.98</v>
       </c>
       <c r="Q8" s="4">
         <v>4.3600000000000003</v>
@@ -1232,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="V8" s="4">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="W8" s="4">
-        <v>212.5</v>
+        <v>187.5</v>
       </c>
       <c r="X8" s="4">
-        <v>16.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y8">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -1249,7 +1258,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1264,34 +1273,34 @@
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>7764.25</v>
+        <v>7754</v>
       </c>
       <c r="J9">
-        <v>7761.25</v>
+        <v>7755.5</v>
       </c>
       <c r="K9" s="3">
-        <v>46315.504166666666</v>
+        <v>46314.458333333336</v>
       </c>
       <c r="L9" s="3">
-        <v>46315.506944444445</v>
+        <v>46314.463194444441</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O9" s="4">
-        <v>-154.36000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="P9" s="4">
-        <v>790.12</v>
+        <v>527.62</v>
       </c>
       <c r="Q9" s="4">
         <v>4.3600000000000003</v>
@@ -1309,16 +1318,16 @@
         <v>0</v>
       </c>
       <c r="V9" s="4">
-        <v>150</v>
+        <v>212.5</v>
       </c>
       <c r="W9" s="4">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="X9" s="4">
-        <v>254.36</v>
+        <v>154.36000000000001</v>
       </c>
       <c r="Y9">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -1326,7 +1335,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1341,34 +1350,34 @@
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>7754</v>
+        <v>7763.25</v>
       </c>
       <c r="J10">
-        <v>7758.75</v>
+        <v>7759.75</v>
       </c>
       <c r="K10" s="3">
-        <v>46315.512499999997</v>
+        <v>46314.498611111114</v>
       </c>
       <c r="L10" s="3">
-        <v>46315.518750000003</v>
+        <v>46314.5</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O10" s="4">
-        <v>-241.86</v>
+        <v>170.64</v>
       </c>
       <c r="P10" s="4">
-        <v>548.26</v>
+        <v>698.26</v>
       </c>
       <c r="Q10" s="4">
         <v>4.3600000000000003</v>
@@ -1386,16 +1395,16 @@
         <v>0</v>
       </c>
       <c r="V10" s="4">
-        <v>262.5</v>
+        <v>37.5</v>
       </c>
       <c r="W10" s="4">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="X10" s="4">
-        <v>391.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y10">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -1403,7 +1412,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1424,28 +1433,28 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>7762</v>
+        <v>7752.75</v>
       </c>
       <c r="J11">
-        <v>7758.75</v>
+        <v>7754.25</v>
       </c>
       <c r="K11" s="3">
-        <v>46315.533333333333</v>
+        <v>46314.501388888886</v>
       </c>
       <c r="L11" s="3">
-        <v>46315.536111111112</v>
+        <v>46314.503472222219</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N11" t="s">
         <v>31</v>
       </c>
       <c r="O11" s="4">
-        <v>-166.86</v>
+        <v>-79.36</v>
       </c>
       <c r="P11" s="4">
-        <v>381.4</v>
+        <v>618.9</v>
       </c>
       <c r="Q11" s="4">
         <v>4.3600000000000003</v>
@@ -1463,16 +1472,16 @@
         <v>0</v>
       </c>
       <c r="V11" s="4">
-        <v>187.5</v>
+        <v>87.5</v>
       </c>
       <c r="W11" s="4">
-        <v>75</v>
+        <v>275</v>
       </c>
       <c r="X11" s="4">
-        <v>241.86</v>
+        <v>354.36</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -1480,7 +1489,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1495,34 +1504,34 @@
         <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>7766.25</v>
+        <v>7744.5</v>
       </c>
       <c r="J12">
-        <v>7762.25</v>
+        <v>7741.75</v>
       </c>
       <c r="K12" s="3">
-        <v>46315.5625</v>
+        <v>46314.571527777778</v>
       </c>
       <c r="L12" s="3">
-        <v>46315.581250000003</v>
+        <v>46314.571527777778</v>
       </c>
       <c r="M12" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N12" t="s">
         <v>31</v>
       </c>
       <c r="O12" s="4">
-        <v>-204.36</v>
+        <v>-141.86000000000001</v>
       </c>
       <c r="P12" s="4">
-        <v>177.04</v>
+        <v>477.04</v>
       </c>
       <c r="Q12" s="4">
         <v>4.3600000000000003</v>
@@ -1540,16 +1549,16 @@
         <v>0</v>
       </c>
       <c r="V12" s="4">
-        <v>275</v>
+        <v>137.5</v>
       </c>
       <c r="W12" s="4">
-        <v>112.5</v>
+        <v>62.5</v>
       </c>
       <c r="X12" s="4">
-        <v>316.86</v>
+        <v>204.36</v>
       </c>
       <c r="Y12">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1557,7 +1566,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1572,34 +1581,34 @@
         <v>28</v>
       </c>
       <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>7741.75</v>
+      </c>
+      <c r="J13">
+        <v>7736.75</v>
+      </c>
+      <c r="K13" s="3">
+        <v>46314.571527777778</v>
+      </c>
+      <c r="L13" s="3">
+        <v>46314.574999999997</v>
+      </c>
+      <c r="M13" t="s">
         <v>32</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>7761.25</v>
-      </c>
-      <c r="J13">
-        <v>7758.75</v>
-      </c>
-      <c r="K13" s="3">
-        <v>46315.6</v>
-      </c>
-      <c r="L13" s="3">
-        <v>46315.600694444445</v>
-      </c>
-      <c r="M13" t="s">
-        <v>38</v>
-      </c>
       <c r="N13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O13" s="4">
-        <v>120.64</v>
+        <v>245.64</v>
       </c>
       <c r="P13" s="4">
-        <v>297.68</v>
+        <v>722.68</v>
       </c>
       <c r="Q13" s="4">
         <v>4.3600000000000003</v>
@@ -1617,16 +1626,16 @@
         <v>0</v>
       </c>
       <c r="V13" s="4">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="W13" s="4">
-        <v>137.5</v>
+        <v>262.5</v>
       </c>
       <c r="X13" s="4">
         <v>16.86</v>
       </c>
       <c r="Y13">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1634,7 +1643,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1649,34 +1658,34 @@
         <v>28</v>
       </c>
       <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>7740.5</v>
+      </c>
+      <c r="J14">
+        <v>7743.5</v>
+      </c>
+      <c r="K14" s="3">
+        <v>46314.585416666669</v>
+      </c>
+      <c r="L14" s="3">
+        <v>46314.589583333334</v>
+      </c>
+      <c r="M14" t="s">
         <v>32</v>
       </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>7754.5</v>
-      </c>
-      <c r="J14">
-        <v>7753.25</v>
-      </c>
-      <c r="K14" s="3">
-        <v>46315.60833333333</v>
-      </c>
-      <c r="L14" s="3">
-        <v>46315.614583333336</v>
-      </c>
-      <c r="M14" t="s">
-        <v>35</v>
-      </c>
       <c r="N14" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O14" s="4">
-        <v>58.14</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P14" s="4">
-        <v>355.82</v>
+        <v>568.32000000000005</v>
       </c>
       <c r="Q14" s="4">
         <v>4.3600000000000003</v>
@@ -1694,16 +1703,16 @@
         <v>0</v>
       </c>
       <c r="V14" s="4">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="W14" s="4">
-        <v>287.5</v>
+        <v>150</v>
       </c>
       <c r="X14" s="4">
-        <v>229.36</v>
+        <v>304.36</v>
       </c>
       <c r="Y14">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -1711,7 +1720,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1726,34 +1735,34 @@
         <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>7755.75</v>
+        <v>7743.5</v>
       </c>
       <c r="J15">
-        <v>7756</v>
+        <v>7748.5</v>
       </c>
       <c r="K15" s="3">
-        <v>46315.622916666667</v>
+        <v>46314.589583333334</v>
       </c>
       <c r="L15" s="3">
-        <v>46315.630555555559</v>
+        <v>46314.59652777778</v>
       </c>
       <c r="M15" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O15" s="4">
-        <v>-16.86</v>
+        <v>245.64</v>
       </c>
       <c r="P15" s="4">
-        <v>338.96</v>
+        <v>813.96</v>
       </c>
       <c r="Q15" s="4">
         <v>4.3600000000000003</v>
@@ -1771,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="V15" s="4">
-        <v>150</v>
+        <v>37.5</v>
       </c>
       <c r="W15" s="4">
-        <v>12.5</v>
+        <v>250</v>
       </c>
       <c r="X15" s="4">
-        <v>29.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y15">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -1788,7 +1797,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1803,34 +1812,34 @@
         <v>28</v>
       </c>
       <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>7742.5</v>
+      </c>
+      <c r="J16">
+        <v>7740.5</v>
+      </c>
+      <c r="K16" s="3">
+        <v>46314.599305555559</v>
+      </c>
+      <c r="L16" s="3">
+        <v>46314.601388888892</v>
+      </c>
+      <c r="M16" t="s">
         <v>32</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>7750.25</v>
-      </c>
-      <c r="J16">
-        <v>7751</v>
-      </c>
-      <c r="K16" s="3">
-        <v>46315.63958333333</v>
-      </c>
-      <c r="L16" s="3">
-        <v>46315.643055555556</v>
-      </c>
-      <c r="M16" t="s">
-        <v>35</v>
-      </c>
       <c r="N16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O16" s="4">
-        <v>-41.86</v>
+        <v>95.64</v>
       </c>
       <c r="P16" s="4">
-        <v>297.10000000000002</v>
+        <v>909.6</v>
       </c>
       <c r="Q16" s="4">
         <v>4.3600000000000003</v>
@@ -1848,27 +1857,27 @@
         <v>0</v>
       </c>
       <c r="V16" s="4">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="W16" s="4">
-        <v>187.5</v>
+        <v>100</v>
       </c>
       <c r="X16" s="4">
-        <v>229.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y16">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -1880,34 +1889,34 @@
         <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>7774.5</v>
+        <v>7745</v>
       </c>
       <c r="J17">
-        <v>7776</v>
+        <v>7750</v>
       </c>
       <c r="K17" s="3">
-        <v>46316.413194444445</v>
+        <v>46314.632638888892</v>
       </c>
       <c r="L17" s="3">
-        <v>46316.413194444445</v>
+        <v>46314.638194444444</v>
       </c>
       <c r="M17" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O17" s="4">
-        <v>70.64</v>
+        <v>245.64</v>
       </c>
       <c r="P17" s="4">
-        <v>70.64</v>
+        <v>1155.24</v>
       </c>
       <c r="Q17" s="4">
         <v>4.3600000000000003</v>
@@ -1925,27 +1934,27 @@
         <v>0</v>
       </c>
       <c r="V17" s="4">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="W17" s="4">
-        <v>87.5</v>
+        <v>250</v>
       </c>
       <c r="X17" s="4">
-        <v>16.86</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y17">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -1957,34 +1966,34 @@
         <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>7775</v>
+        <v>7733</v>
       </c>
       <c r="J18">
-        <v>7771</v>
+        <v>7732.75</v>
       </c>
       <c r="K18" s="3">
-        <v>46316.418055555558</v>
+        <v>46315.411111111112</v>
       </c>
       <c r="L18" s="3">
-        <v>46316.419444444444</v>
+        <v>46315.413194444445</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N18" t="s">
         <v>31</v>
       </c>
       <c r="O18" s="4">
-        <v>-204.36</v>
+        <v>-16.86</v>
       </c>
       <c r="P18" s="4">
-        <v>-133.72</v>
+        <v>-16.86</v>
       </c>
       <c r="Q18" s="4">
         <v>4.3600000000000003</v>
@@ -2002,27 +2011,27 @@
         <v>0</v>
       </c>
       <c r="V18" s="4">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="W18" s="4">
-        <v>100</v>
+        <v>237.5</v>
       </c>
       <c r="X18" s="4">
-        <v>304.36</v>
+        <v>254.36</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -2034,34 +2043,34 @@
         <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>7759.75</v>
+        <v>7778.5</v>
       </c>
       <c r="J19">
-        <v>7755.5</v>
+        <v>7775.75</v>
       </c>
       <c r="K19" s="3">
-        <v>46316.420138888891</v>
+        <v>46315.460416666669</v>
       </c>
       <c r="L19" s="3">
-        <v>46316.423611111109</v>
+        <v>46315.465277777781</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O19" s="4">
-        <v>208.14</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P19" s="4">
-        <v>74.42</v>
+        <v>116.28</v>
       </c>
       <c r="Q19" s="4">
         <v>4.3600000000000003</v>
@@ -2079,27 +2088,27 @@
         <v>0</v>
       </c>
       <c r="V19" s="4">
+        <v>200</v>
+      </c>
+      <c r="W19" s="4">
         <v>150</v>
       </c>
-      <c r="W19" s="4">
-        <v>250</v>
-      </c>
       <c r="X19" s="4">
-        <v>41.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y19">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
@@ -2117,28 +2126,28 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>7762.25</v>
+        <v>7772.75</v>
       </c>
       <c r="J20">
-        <v>7765</v>
+        <v>7755.75</v>
       </c>
       <c r="K20" s="3">
-        <v>46316.436111111114</v>
+        <v>46315.46597222222</v>
       </c>
       <c r="L20" s="3">
-        <v>46316.438194444447</v>
+        <v>46315.467361111114</v>
       </c>
       <c r="M20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" t="s">
         <v>37</v>
       </c>
-      <c r="N20" t="s">
-        <v>34</v>
-      </c>
       <c r="O20" s="4">
-        <v>133.13999999999999</v>
+        <v>845.64</v>
       </c>
       <c r="P20" s="4">
-        <v>207.56</v>
+        <v>961.92</v>
       </c>
       <c r="Q20" s="4">
         <v>4.3600000000000003</v>
@@ -2156,27 +2165,27 @@
         <v>0</v>
       </c>
       <c r="V20" s="4">
-        <v>162.5</v>
+        <v>150</v>
       </c>
       <c r="W20" s="4">
-        <v>150</v>
+        <v>862.5</v>
       </c>
       <c r="X20" s="4">
         <v>16.86</v>
       </c>
       <c r="Y20">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
@@ -2188,34 +2197,34 @@
         <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>7774.25</v>
+        <v>7763</v>
       </c>
       <c r="J21">
-        <v>7777.25</v>
+        <v>7766</v>
       </c>
       <c r="K21" s="3">
-        <v>46316.449305555558</v>
+        <v>46315.487500000003</v>
       </c>
       <c r="L21" s="3">
-        <v>46316.45208333333</v>
+        <v>46315.487500000003</v>
       </c>
       <c r="M21" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O21" s="4">
         <v>145.63999999999999</v>
       </c>
       <c r="P21" s="4">
-        <v>353.2</v>
+        <v>1107.56</v>
       </c>
       <c r="Q21" s="4">
         <v>4.3600000000000003</v>
@@ -2233,27 +2242,27 @@
         <v>0</v>
       </c>
       <c r="V21" s="4">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="W21" s="4">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="X21" s="4">
-        <v>104.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y21">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -2265,34 +2274,34 @@
         <v>28</v>
       </c>
       <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>7759.25</v>
+      </c>
+      <c r="J22">
+        <v>7762.25</v>
+      </c>
+      <c r="K22" s="3">
+        <v>46315.489583333336</v>
+      </c>
+      <c r="L22" s="3">
+        <v>46315.491666666669</v>
+      </c>
+      <c r="M22" t="s">
         <v>32</v>
       </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>7788.5</v>
-      </c>
-      <c r="J22">
-        <v>7791.75</v>
-      </c>
-      <c r="K22" s="3">
-        <v>46316.518750000003</v>
-      </c>
-      <c r="L22" s="3">
-        <v>46316.526388888888</v>
-      </c>
-      <c r="M22" t="s">
-        <v>33</v>
-      </c>
       <c r="N22" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O22" s="4">
-        <v>-166.86</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P22" s="4">
-        <v>186.34</v>
+        <v>953.2</v>
       </c>
       <c r="Q22" s="4">
         <v>4.3600000000000003</v>
@@ -2310,27 +2319,27 @@
         <v>0</v>
       </c>
       <c r="V22" s="4">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="W22" s="4">
-        <v>50</v>
+        <v>112.5</v>
       </c>
       <c r="X22" s="4">
-        <v>216.86</v>
+        <v>266.86</v>
       </c>
       <c r="Y22">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -2342,34 +2351,34 @@
         <v>28</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>7799.5</v>
+        <v>7762.25</v>
       </c>
       <c r="J23">
-        <v>7798.75</v>
+        <v>7758.25</v>
       </c>
       <c r="K23" s="3">
-        <v>46316.527083333334</v>
+        <v>46315.491666666669</v>
       </c>
       <c r="L23" s="3">
-        <v>46316.527777777781</v>
+        <v>46315.493750000001</v>
       </c>
       <c r="M23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N23" t="s">
         <v>31</v>
       </c>
       <c r="O23" s="4">
-        <v>-41.86</v>
+        <v>-204.36</v>
       </c>
       <c r="P23" s="4">
-        <v>144.47999999999999</v>
+        <v>748.84</v>
       </c>
       <c r="Q23" s="4">
         <v>4.3600000000000003</v>
@@ -2387,27 +2396,27 @@
         <v>0</v>
       </c>
       <c r="V23" s="4">
+        <v>212.5</v>
+      </c>
+      <c r="W23" s="4">
         <v>37.5</v>
       </c>
-      <c r="W23" s="4">
-        <v>350</v>
-      </c>
       <c r="X23" s="4">
-        <v>391.86</v>
+        <v>241.86</v>
       </c>
       <c r="Y23">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -2419,34 +2428,34 @@
         <v>28</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>7805</v>
+        <v>7763.25</v>
       </c>
       <c r="J24">
-        <v>7802.5</v>
+        <v>7767.25</v>
       </c>
       <c r="K24" s="3">
-        <v>46316.615972222222</v>
+        <v>46315.495833333334</v>
       </c>
       <c r="L24" s="3">
-        <v>46316.616666666669</v>
+        <v>46315.495833333334</v>
       </c>
       <c r="M24" t="s">
+        <v>35</v>
+      </c>
+      <c r="N24" t="s">
         <v>33</v>
       </c>
-      <c r="N24" t="s">
-        <v>34</v>
-      </c>
       <c r="O24" s="4">
-        <v>120.64</v>
+        <v>195.64</v>
       </c>
       <c r="P24" s="4">
-        <v>265.12</v>
+        <v>944.48</v>
       </c>
       <c r="Q24" s="4">
         <v>4.3600000000000003</v>
@@ -2464,27 +2473,27 @@
         <v>0</v>
       </c>
       <c r="V24" s="4">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="W24" s="4">
-        <v>162.5</v>
+        <v>212.5</v>
       </c>
       <c r="X24" s="4">
-        <v>41.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
@@ -2496,34 +2505,34 @@
         <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>7798.75</v>
+        <v>7764.25</v>
       </c>
       <c r="J25">
-        <v>7797.5</v>
+        <v>7761.25</v>
       </c>
       <c r="K25" s="3">
-        <v>46316.617361111108</v>
+        <v>46315.504166666666</v>
       </c>
       <c r="L25" s="3">
-        <v>46316.619444444441</v>
+        <v>46315.506944444445</v>
       </c>
       <c r="M25" t="s">
         <v>35</v>
       </c>
       <c r="N25" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O25" s="4">
-        <v>58.14</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P25" s="4">
-        <v>323.26</v>
+        <v>790.12</v>
       </c>
       <c r="Q25" s="4">
         <v>4.3600000000000003</v>
@@ -2541,27 +2550,27 @@
         <v>0</v>
       </c>
       <c r="V25" s="4">
-        <v>137.5</v>
+        <v>150</v>
       </c>
       <c r="W25" s="4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="X25" s="4">
-        <v>191.86</v>
+        <v>254.36</v>
       </c>
       <c r="Y25">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -2579,28 +2588,28 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>7786.5</v>
+        <v>7754</v>
       </c>
       <c r="J26">
-        <v>7789.25</v>
+        <v>7758.75</v>
       </c>
       <c r="K26" s="3">
-        <v>46316.636111111111</v>
+        <v>46315.512499999997</v>
       </c>
       <c r="L26" s="3">
-        <v>46316.636805555558</v>
+        <v>46315.518750000003</v>
       </c>
       <c r="M26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="O26" s="4">
-        <v>133.13999999999999</v>
+        <v>-241.86</v>
       </c>
       <c r="P26" s="4">
-        <v>456.4</v>
+        <v>548.26</v>
       </c>
       <c r="Q26" s="4">
         <v>4.3600000000000003</v>
@@ -2618,27 +2627,27 @@
         <v>0</v>
       </c>
       <c r="V26" s="4">
-        <v>25</v>
+        <v>262.5</v>
       </c>
       <c r="W26" s="4">
-        <v>137.5</v>
+        <v>150</v>
       </c>
       <c r="X26" s="4">
-        <v>4.3600000000000003</v>
+        <v>391.86</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -2650,34 +2659,34 @@
         <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>7784.5</v>
+        <v>7762</v>
       </c>
       <c r="J27">
-        <v>7786</v>
+        <v>7758.75</v>
       </c>
       <c r="K27" s="3">
-        <v>46316.637499999997</v>
+        <v>46315.533333333333</v>
       </c>
       <c r="L27" s="3">
-        <v>46316.638194444444</v>
+        <v>46315.536111111112</v>
       </c>
       <c r="M27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N27" t="s">
         <v>31</v>
       </c>
       <c r="O27" s="4">
-        <v>-79.36</v>
+        <v>-166.86</v>
       </c>
       <c r="P27" s="4">
-        <v>377.04</v>
+        <v>381.4</v>
       </c>
       <c r="Q27" s="4">
         <v>4.3600000000000003</v>
@@ -2695,27 +2704,27 @@
         <v>0</v>
       </c>
       <c r="V27" s="4">
-        <v>112.5</v>
+        <v>187.5</v>
       </c>
       <c r="W27" s="4">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="X27" s="4">
-        <v>91.86</v>
+        <v>241.86</v>
       </c>
       <c r="Y27">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -2727,25 +2736,25 @@
         <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>7735</v>
+        <v>7766.25</v>
       </c>
       <c r="J28">
-        <v>7739</v>
+        <v>7762.25</v>
       </c>
       <c r="K28" s="3">
-        <v>46317.416666666664</v>
+        <v>46315.5625</v>
       </c>
       <c r="L28" s="3">
-        <v>46317.416666666664</v>
+        <v>46315.581250000003</v>
       </c>
       <c r="M28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N28" t="s">
         <v>31</v>
@@ -2754,33 +2763,45 @@
         <v>-204.36</v>
       </c>
       <c r="P28" s="4">
-        <v>-204.36</v>
+        <v>177.04</v>
       </c>
       <c r="Q28" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R28" s="4">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4">
+        <v>0</v>
+      </c>
       <c r="V28" s="4">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="W28" s="4">
-        <v>62.5</v>
+        <v>112.5</v>
       </c>
       <c r="X28" s="4">
-        <v>266.86</v>
+        <v>316.86</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -2792,60 +2813,72 @@
         <v>28</v>
       </c>
       <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>7761.25</v>
+      </c>
+      <c r="J29">
+        <v>7758.75</v>
+      </c>
+      <c r="K29" s="3">
+        <v>46315.6</v>
+      </c>
+      <c r="L29" s="3">
+        <v>46315.600694444445</v>
+      </c>
+      <c r="M29" t="s">
         <v>32</v>
       </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>7735.75</v>
-      </c>
-      <c r="J29">
-        <v>7733</v>
-      </c>
-      <c r="K29" s="3">
-        <v>46317.420138888891</v>
-      </c>
-      <c r="L29" s="3">
-        <v>46317.42083333333</v>
-      </c>
-      <c r="M29" t="s">
-        <v>38</v>
-      </c>
       <c r="N29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O29" s="4">
-        <v>133.13999999999999</v>
+        <v>120.64</v>
       </c>
       <c r="P29" s="4">
-        <v>-71.22</v>
+        <v>297.68</v>
       </c>
       <c r="Q29" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R29" s="4">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4">
+        <v>0</v>
+      </c>
+      <c r="T29" s="4">
+        <v>0</v>
+      </c>
+      <c r="U29" s="4">
+        <v>0</v>
+      </c>
       <c r="V29" s="4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="W29" s="4">
         <v>137.5</v>
       </c>
       <c r="X29" s="4">
-        <v>4.3600000000000003</v>
+        <v>16.86</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
         <v>26</v>
@@ -2857,60 +2890,72 @@
         <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>7727.25</v>
+        <v>7754.5</v>
       </c>
       <c r="J30">
-        <v>7718.5</v>
+        <v>7753.25</v>
       </c>
       <c r="K30" s="3">
-        <v>46317.422222222223</v>
+        <v>46315.60833333333</v>
       </c>
       <c r="L30" s="3">
-        <v>46317.427083333336</v>
+        <v>46315.614583333336</v>
       </c>
       <c r="M30" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O30" s="4">
-        <v>433.14</v>
+        <v>58.14</v>
       </c>
       <c r="P30" s="4">
-        <v>361.92</v>
+        <v>355.82</v>
       </c>
       <c r="Q30" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R30" s="4">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0</v>
+      </c>
       <c r="V30" s="4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="W30" s="4">
-        <v>462.5</v>
+        <v>287.5</v>
       </c>
       <c r="X30" s="4">
-        <v>29.36</v>
+        <v>229.36</v>
       </c>
       <c r="Y30">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -2928,54 +2973,66 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>7695</v>
+        <v>7755.75</v>
       </c>
       <c r="J31">
-        <v>7689.75</v>
+        <v>7756</v>
       </c>
       <c r="K31" s="3">
-        <v>46317.454861111109</v>
+        <v>46315.622916666667</v>
       </c>
       <c r="L31" s="3">
-        <v>46317.454861111109</v>
+        <v>46315.630555555559</v>
       </c>
       <c r="M31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="N31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O31" s="4">
-        <v>-266.86</v>
+        <v>-16.86</v>
       </c>
       <c r="P31" s="4">
-        <v>95.06</v>
+        <v>338.96</v>
       </c>
       <c r="Q31" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R31" s="4">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4">
+        <v>0</v>
+      </c>
+      <c r="T31" s="4">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0</v>
+      </c>
       <c r="V31" s="4">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="W31" s="4">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="X31" s="4">
-        <v>341.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B32" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -2987,49 +3044,61 @@
         <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>7689.5</v>
+        <v>7750.25</v>
       </c>
       <c r="J32">
-        <v>7694</v>
+        <v>7751</v>
       </c>
       <c r="K32" s="3">
-        <v>46317.454861111109</v>
+        <v>46315.63958333333</v>
       </c>
       <c r="L32" s="3">
-        <v>46317.457638888889</v>
+        <v>46315.643055555556</v>
       </c>
       <c r="M32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N32" t="s">
         <v>31</v>
       </c>
       <c r="O32" s="4">
-        <v>-229.36</v>
+        <v>-41.86</v>
       </c>
       <c r="P32" s="4">
-        <v>-134.30000000000001</v>
+        <v>297.10000000000002</v>
       </c>
       <c r="Q32" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R32" s="4">
+        <v>0</v>
+      </c>
+      <c r="S32" s="4">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4">
+        <v>0</v>
+      </c>
       <c r="V32" s="4">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="W32" s="4">
-        <v>87.5</v>
+        <v>187.5</v>
       </c>
       <c r="X32" s="4">
-        <v>316.86</v>
+        <v>229.36</v>
       </c>
       <c r="Y32">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
@@ -3037,10 +3106,10 @@
         <v>46</v>
       </c>
       <c r="B33" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
@@ -3052,49 +3121,61 @@
         <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>7692.25</v>
+        <v>7774.5</v>
       </c>
       <c r="J33">
-        <v>7696.25</v>
+        <v>7776</v>
       </c>
       <c r="K33" s="3">
-        <v>46317.460416666669</v>
+        <v>46316.413194444445</v>
       </c>
       <c r="L33" s="3">
-        <v>46317.467361111114</v>
+        <v>46316.413194444445</v>
       </c>
       <c r="M33" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O33" s="4">
-        <v>-204.36</v>
+        <v>70.64</v>
       </c>
       <c r="P33" s="4">
-        <v>-338.66</v>
+        <v>70.64</v>
       </c>
       <c r="Q33" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R33" s="4">
+        <v>0</v>
+      </c>
+      <c r="S33" s="4">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4">
+        <v>0</v>
+      </c>
+      <c r="U33" s="4">
+        <v>0</v>
+      </c>
       <c r="V33" s="4">
-        <v>212.5</v>
+        <v>25</v>
       </c>
       <c r="W33" s="4">
-        <v>162.5</v>
+        <v>87.5</v>
       </c>
       <c r="X33" s="4">
-        <v>366.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y33">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
@@ -3102,10 +3183,10 @@
         <v>46</v>
       </c>
       <c r="B34" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
         <v>26</v>
@@ -3117,49 +3198,61 @@
         <v>28</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>7691</v>
+        <v>7775</v>
       </c>
       <c r="J34">
-        <v>7696.25</v>
+        <v>7771</v>
       </c>
       <c r="K34" s="3">
-        <v>46317.468055555553</v>
+        <v>46316.418055555558</v>
       </c>
       <c r="L34" s="3">
-        <v>46317.470138888886</v>
+        <v>46316.419444444444</v>
       </c>
       <c r="M34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N34" t="s">
         <v>31</v>
       </c>
       <c r="O34" s="4">
-        <v>-266.86</v>
+        <v>-204.36</v>
       </c>
       <c r="P34" s="4">
-        <v>-605.52</v>
+        <v>-133.72</v>
       </c>
       <c r="Q34" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R34" s="4">
+        <v>0</v>
+      </c>
+      <c r="S34" s="4">
+        <v>0</v>
+      </c>
+      <c r="T34" s="4">
+        <v>0</v>
+      </c>
+      <c r="U34" s="4">
+        <v>0</v>
+      </c>
       <c r="V34" s="4">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="W34" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="X34" s="4">
-        <v>316.86</v>
+        <v>304.36</v>
       </c>
       <c r="Y34">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
@@ -3167,10 +3260,10 @@
         <v>46</v>
       </c>
       <c r="B35" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
@@ -3188,40 +3281,52 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>7700.75</v>
+        <v>7759.75</v>
       </c>
       <c r="J35">
-        <v>7712</v>
+        <v>7755.5</v>
       </c>
       <c r="K35" s="3">
-        <v>46317.470833333333</v>
+        <v>46316.420138888891</v>
       </c>
       <c r="L35" s="3">
-        <v>46317.474999999999</v>
+        <v>46316.423611111109</v>
       </c>
       <c r="M35" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O35" s="4">
-        <v>558.14</v>
+        <v>208.14</v>
       </c>
       <c r="P35" s="4">
-        <v>-47.38</v>
+        <v>74.42</v>
       </c>
       <c r="Q35" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R35" s="4">
+        <v>0</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0</v>
+      </c>
+      <c r="T35" s="4">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4">
+        <v>0</v>
+      </c>
       <c r="V35" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="W35" s="4">
-        <v>587.5</v>
+        <v>250</v>
       </c>
       <c r="X35" s="4">
-        <v>29.36</v>
+        <v>41.86</v>
       </c>
       <c r="Y35">
         <v>36</v>
@@ -3232,10 +3337,10 @@
         <v>46</v>
       </c>
       <c r="B36" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
         <v>26</v>
@@ -3247,49 +3352,61 @@
         <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>7700.75</v>
+        <v>7762.25</v>
       </c>
       <c r="J36">
-        <v>7697.25</v>
+        <v>7765</v>
       </c>
       <c r="K36" s="3">
-        <v>46317.482638888891</v>
+        <v>46316.436111111114</v>
       </c>
       <c r="L36" s="3">
-        <v>46317.484722222223</v>
+        <v>46316.438194444447</v>
       </c>
       <c r="M36" t="s">
         <v>40</v>
       </c>
       <c r="N36" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="O36" s="4">
-        <v>-179.36</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P36" s="4">
-        <v>-226.74</v>
+        <v>207.56</v>
       </c>
       <c r="Q36" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R36" s="4">
+        <v>0</v>
+      </c>
+      <c r="S36" s="4">
+        <v>0</v>
+      </c>
+      <c r="T36" s="4">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0</v>
+      </c>
       <c r="V36" s="4">
-        <v>175</v>
+        <v>162.5</v>
       </c>
       <c r="W36" s="4">
-        <v>87.5</v>
+        <v>150</v>
       </c>
       <c r="X36" s="4">
-        <v>266.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y36">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
@@ -3297,10 +3414,10 @@
         <v>46</v>
       </c>
       <c r="B37" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
@@ -3312,49 +3429,61 @@
         <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>7697.25</v>
+        <v>7774.25</v>
       </c>
       <c r="J37">
-        <v>7692.75</v>
+        <v>7777.25</v>
       </c>
       <c r="K37" s="3">
-        <v>46317.484722222223</v>
+        <v>46316.449305555558</v>
       </c>
       <c r="L37" s="3">
-        <v>46317.486111111109</v>
+        <v>46316.45208333333</v>
       </c>
       <c r="M37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N37" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O37" s="4">
-        <v>220.64</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P37" s="4">
-        <v>-6.1</v>
+        <v>353.2</v>
       </c>
       <c r="Q37" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R37" s="4">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0</v>
+      </c>
+      <c r="T37" s="4">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4">
+        <v>0</v>
+      </c>
       <c r="V37" s="4">
-        <v>162.5</v>
+        <v>25</v>
       </c>
       <c r="W37" s="4">
-        <v>425</v>
+        <v>250</v>
       </c>
       <c r="X37" s="4">
-        <v>204.36</v>
+        <v>104.36</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
@@ -3362,10 +3491,10 @@
         <v>46</v>
       </c>
       <c r="B38" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
@@ -3383,43 +3512,55 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>7701.5</v>
+        <v>7788.5</v>
       </c>
       <c r="J38">
-        <v>7696.25</v>
+        <v>7791.75</v>
       </c>
       <c r="K38" s="3">
-        <v>46317.488194444442</v>
+        <v>46316.518750000003</v>
       </c>
       <c r="L38" s="3">
-        <v>46317.489583333336</v>
+        <v>46316.526388888888</v>
       </c>
       <c r="M38" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O38" s="4">
-        <v>-266.86</v>
+        <v>-166.86</v>
       </c>
       <c r="P38" s="4">
-        <v>-272.95999999999998</v>
+        <v>186.34</v>
       </c>
       <c r="Q38" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R38" s="4">
+        <v>0</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0</v>
+      </c>
+      <c r="T38" s="4">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4">
+        <v>0</v>
+      </c>
       <c r="V38" s="4">
-        <v>287.5</v>
+        <v>175</v>
       </c>
       <c r="W38" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X38" s="4">
-        <v>266.86</v>
+        <v>216.86</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
@@ -3427,10 +3568,10 @@
         <v>46</v>
       </c>
       <c r="B39" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
         <v>26</v>
@@ -3442,49 +3583,61 @@
         <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>7696.25</v>
+        <v>7799.5</v>
       </c>
       <c r="J39">
-        <v>7701.25</v>
+        <v>7798.75</v>
       </c>
       <c r="K39" s="3">
-        <v>46317.489583333336</v>
+        <v>46316.527083333334</v>
       </c>
       <c r="L39" s="3">
-        <v>46317.493055555555</v>
+        <v>46316.527777777781</v>
       </c>
       <c r="M39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N39" t="s">
         <v>31</v>
       </c>
       <c r="O39" s="4">
-        <v>-254.36</v>
+        <v>-41.86</v>
       </c>
       <c r="P39" s="4">
-        <v>-527.32000000000005</v>
+        <v>144.47999999999999</v>
       </c>
       <c r="Q39" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R39" s="4">
+        <v>0</v>
+      </c>
+      <c r="S39" s="4">
+        <v>0</v>
+      </c>
+      <c r="T39" s="4">
+        <v>0</v>
+      </c>
+      <c r="U39" s="4">
+        <v>0</v>
+      </c>
       <c r="V39" s="4">
-        <v>250</v>
+        <v>37.5</v>
       </c>
       <c r="W39" s="4">
-        <v>37.5</v>
+        <v>350</v>
       </c>
       <c r="X39" s="4">
-        <v>291.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y39">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
@@ -3492,10 +3645,10 @@
         <v>46</v>
       </c>
       <c r="B40" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
@@ -3513,43 +3666,55 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>7711</v>
+        <v>7805</v>
       </c>
       <c r="J40">
-        <v>7716.75</v>
+        <v>7802.5</v>
       </c>
       <c r="K40" s="3">
-        <v>46317.49722222222</v>
+        <v>46316.615972222222</v>
       </c>
       <c r="L40" s="3">
-        <v>46317.5</v>
+        <v>46316.616666666669</v>
       </c>
       <c r="M40" t="s">
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O40" s="4">
-        <v>283.14</v>
+        <v>120.64</v>
       </c>
       <c r="P40" s="4">
-        <v>-244.18</v>
+        <v>265.12</v>
       </c>
       <c r="Q40" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R40" s="4">
+        <v>0</v>
+      </c>
+      <c r="S40" s="4">
+        <v>0</v>
+      </c>
+      <c r="T40" s="4">
+        <v>0</v>
+      </c>
+      <c r="U40" s="4">
+        <v>0</v>
+      </c>
       <c r="V40" s="4">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="W40" s="4">
-        <v>312.5</v>
+        <v>162.5</v>
       </c>
       <c r="X40" s="4">
-        <v>29.36</v>
+        <v>41.86</v>
       </c>
       <c r="Y40">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
@@ -3557,10 +3722,10 @@
         <v>46</v>
       </c>
       <c r="B41" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -3572,49 +3737,61 @@
         <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>7711.5</v>
+        <v>7798.75</v>
       </c>
       <c r="J41">
-        <v>7709</v>
+        <v>7797.5</v>
       </c>
       <c r="K41" s="3">
-        <v>46317.522222222222</v>
+        <v>46316.617361111108</v>
       </c>
       <c r="L41" s="3">
-        <v>46317.522916666669</v>
+        <v>46316.619444444441</v>
       </c>
       <c r="M41" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N41" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O41" s="4">
-        <v>120.64</v>
+        <v>58.14</v>
       </c>
       <c r="P41" s="4">
-        <v>-123.54</v>
+        <v>323.26</v>
       </c>
       <c r="Q41" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R41" s="4">
+        <v>0</v>
+      </c>
+      <c r="S41" s="4">
+        <v>0</v>
+      </c>
+      <c r="T41" s="4">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4">
+        <v>0</v>
+      </c>
       <c r="V41" s="4">
-        <v>50</v>
+        <v>137.5</v>
       </c>
       <c r="W41" s="4">
-        <v>137.5</v>
+        <v>250</v>
       </c>
       <c r="X41" s="4">
-        <v>16.86</v>
+        <v>191.86</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
@@ -3622,10 +3799,10 @@
         <v>46</v>
       </c>
       <c r="B42" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
         <v>26</v>
@@ -3637,49 +3814,61 @@
         <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>7701</v>
+        <v>7786.5</v>
       </c>
       <c r="J42">
-        <v>7698.25</v>
+        <v>7789.25</v>
       </c>
       <c r="K42" s="3">
-        <v>46317.527083333334</v>
+        <v>46316.636111111111</v>
       </c>
       <c r="L42" s="3">
-        <v>46317.530555555553</v>
+        <v>46316.636805555558</v>
       </c>
       <c r="M42" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N42" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O42" s="4">
         <v>133.13999999999999</v>
       </c>
       <c r="P42" s="4">
-        <v>9.6</v>
+        <v>456.4</v>
       </c>
       <c r="Q42" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R42" s="4">
+        <v>0</v>
+      </c>
+      <c r="S42" s="4">
+        <v>0</v>
+      </c>
+      <c r="T42" s="4">
+        <v>0</v>
+      </c>
+      <c r="U42" s="4">
+        <v>0</v>
+      </c>
       <c r="V42" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="W42" s="4">
-        <v>237.5</v>
+        <v>137.5</v>
       </c>
       <c r="X42" s="4">
-        <v>104.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y42">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
@@ -3687,10 +3876,10 @@
         <v>46</v>
       </c>
       <c r="B43" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -3708,54 +3897,66 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>7702.25</v>
+        <v>7784.5</v>
       </c>
       <c r="J43">
-        <v>7697.5</v>
+        <v>7786</v>
       </c>
       <c r="K43" s="3">
-        <v>46317.540277777778</v>
+        <v>46316.637499999997</v>
       </c>
       <c r="L43" s="3">
-        <v>46317.543055555558</v>
+        <v>46316.638194444444</v>
       </c>
       <c r="M43" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N43" t="s">
         <v>31</v>
       </c>
       <c r="O43" s="4">
-        <v>-241.86</v>
+        <v>-79.36</v>
       </c>
       <c r="P43" s="4">
-        <v>-232.26</v>
+        <v>377.04</v>
       </c>
       <c r="Q43" s="4">
         <v>4.3600000000000003</v>
       </c>
+      <c r="R43" s="4">
+        <v>0</v>
+      </c>
+      <c r="S43" s="4">
+        <v>0</v>
+      </c>
+      <c r="T43" s="4">
+        <v>0</v>
+      </c>
+      <c r="U43" s="4">
+        <v>0</v>
+      </c>
       <c r="V43" s="4">
-        <v>250</v>
+        <v>112.5</v>
       </c>
       <c r="W43" s="4">
-        <v>87.5</v>
+        <v>12.5</v>
       </c>
       <c r="X43" s="4">
-        <v>329.36</v>
+        <v>91.86</v>
       </c>
       <c r="Y43">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B44" s="2">
         <v>46317</v>
       </c>
       <c r="C44">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
@@ -3767,60 +3968,60 @@
         <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>7690</v>
+        <v>7735</v>
       </c>
       <c r="J44">
-        <v>7693</v>
+        <v>7739</v>
       </c>
       <c r="K44" s="3">
-        <v>46317.547222222223</v>
+        <v>46317.416666666664</v>
       </c>
       <c r="L44" s="3">
-        <v>46317.551388888889</v>
+        <v>46317.416666666664</v>
       </c>
       <c r="M44" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="N44" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O44" s="4">
-        <v>-154.36000000000001</v>
+        <v>-204.36</v>
       </c>
       <c r="P44" s="4">
-        <v>-386.62</v>
+        <v>-204.36</v>
       </c>
       <c r="Q44" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V44" s="4">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="W44" s="4">
-        <v>175</v>
+        <v>62.5</v>
       </c>
       <c r="X44" s="4">
-        <v>329.36</v>
+        <v>266.86</v>
       </c>
       <c r="Y44">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B45" s="2">
         <v>46317</v>
       </c>
       <c r="C45">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -3832,60 +4033,60 @@
         <v>28</v>
       </c>
       <c r="G45" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>7735.75</v>
+      </c>
+      <c r="J45">
+        <v>7733</v>
+      </c>
+      <c r="K45" s="3">
+        <v>46317.420138888891</v>
+      </c>
+      <c r="L45" s="3">
+        <v>46317.42083333333</v>
+      </c>
+      <c r="M45" t="s">
         <v>32</v>
       </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>7695.5</v>
-      </c>
-      <c r="J45">
-        <v>7698.75</v>
-      </c>
-      <c r="K45" s="3">
-        <v>46317.558333333334</v>
-      </c>
-      <c r="L45" s="3">
-        <v>46317.561111111114</v>
-      </c>
-      <c r="M45" t="s">
-        <v>38</v>
-      </c>
       <c r="N45" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O45" s="4">
-        <v>-166.86</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P45" s="4">
-        <v>-553.48</v>
+        <v>-71.22</v>
       </c>
       <c r="Q45" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V45" s="4">
-        <v>162.5</v>
+        <v>25</v>
       </c>
       <c r="W45" s="4">
-        <v>150</v>
+        <v>137.5</v>
       </c>
       <c r="X45" s="4">
-        <v>316.86</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y45">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B46" s="2">
         <v>46317</v>
       </c>
       <c r="C46">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
@@ -3903,54 +4104,54 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>7698.25</v>
+        <v>7727.25</v>
       </c>
       <c r="J46">
-        <v>7702.5</v>
+        <v>7718.5</v>
       </c>
       <c r="K46" s="3">
-        <v>46317.561805555553</v>
+        <v>46317.422222222223</v>
       </c>
       <c r="L46" s="3">
-        <v>46317.56527777778</v>
+        <v>46317.427083333336</v>
       </c>
       <c r="M46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N46" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O46" s="4">
-        <v>208.14</v>
+        <v>433.14</v>
       </c>
       <c r="P46" s="4">
-        <v>-345.34</v>
+        <v>361.92</v>
       </c>
       <c r="Q46" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V46" s="4">
-        <v>112.5</v>
+        <v>100</v>
       </c>
       <c r="W46" s="4">
-        <v>225</v>
+        <v>462.5</v>
       </c>
       <c r="X46" s="4">
-        <v>16.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y46">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" s="2">
         <v>46317</v>
       </c>
       <c r="C47">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
@@ -3962,125 +4163,125 @@
         <v>28</v>
       </c>
       <c r="G47" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>7704.75</v>
+        <v>7695</v>
       </c>
       <c r="J47">
-        <v>7697.75</v>
+        <v>7689.75</v>
       </c>
       <c r="K47" s="3">
-        <v>46317.56527777778</v>
+        <v>46317.454861111109</v>
       </c>
       <c r="L47" s="3">
-        <v>46317.573611111111</v>
+        <v>46317.454861111109</v>
       </c>
       <c r="M47" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N47" t="s">
         <v>31</v>
       </c>
       <c r="O47" s="4">
-        <v>-354.36</v>
+        <v>-266.86</v>
       </c>
       <c r="P47" s="4">
-        <v>-699.7</v>
+        <v>95.06</v>
       </c>
       <c r="Q47" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V47" s="4">
-        <v>362.5</v>
+        <v>300</v>
       </c>
       <c r="W47" s="4">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="X47" s="4">
-        <v>391.86</v>
+        <v>341.86</v>
       </c>
       <c r="Y47">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2">
         <v>46317</v>
       </c>
       <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" t="s">
+        <v>29</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>7689.5</v>
+      </c>
+      <c r="J48">
+        <v>7694</v>
+      </c>
+      <c r="K48" s="3">
+        <v>46317.454861111109</v>
+      </c>
+      <c r="L48" s="3">
+        <v>46317.457638888889</v>
+      </c>
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" s="4">
+        <v>-229.36</v>
+      </c>
+      <c r="P48" s="4">
+        <v>-134.30000000000001</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="V48" s="4">
+        <v>225</v>
+      </c>
+      <c r="W48" s="4">
+        <v>87.5</v>
+      </c>
+      <c r="X48" s="4">
+        <v>316.86</v>
+      </c>
+      <c r="Y48">
         <v>21</v>
-      </c>
-      <c r="D48" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" t="s">
-        <v>28</v>
-      </c>
-      <c r="G48" t="s">
-        <v>32</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48">
-        <v>7687.75</v>
-      </c>
-      <c r="J48">
-        <v>7679.75</v>
-      </c>
-      <c r="K48" s="3">
-        <v>46317.584027777775</v>
-      </c>
-      <c r="L48" s="3">
-        <v>46317.586111111108</v>
-      </c>
-      <c r="M48" t="s">
-        <v>35</v>
-      </c>
-      <c r="N48" t="s">
-        <v>36</v>
-      </c>
-      <c r="O48" s="4">
-        <v>395.64</v>
-      </c>
-      <c r="P48" s="4">
-        <v>-304.06</v>
-      </c>
-      <c r="Q48" s="4">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="V48" s="4">
-        <v>25</v>
-      </c>
-      <c r="W48" s="4">
-        <v>425</v>
-      </c>
-      <c r="X48" s="4">
-        <v>29.36</v>
-      </c>
-      <c r="Y48">
-        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>46317</v>
       </c>
       <c r="C49">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
@@ -4092,60 +4293,60 @@
         <v>28</v>
       </c>
       <c r="G49" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>7692.25</v>
+      </c>
+      <c r="J49">
+        <v>7696.25</v>
+      </c>
+      <c r="K49" s="3">
+        <v>46317.460416666669</v>
+      </c>
+      <c r="L49" s="3">
+        <v>46317.467361111114</v>
+      </c>
+      <c r="M49" t="s">
         <v>32</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49">
-        <v>7690</v>
-      </c>
-      <c r="J49">
-        <v>7692.5</v>
-      </c>
-      <c r="K49" s="3">
-        <v>46317.59375</v>
-      </c>
-      <c r="L49" s="3">
-        <v>46317.594444444447</v>
-      </c>
-      <c r="M49" t="s">
-        <v>38</v>
       </c>
       <c r="N49" t="s">
         <v>31</v>
       </c>
       <c r="O49" s="4">
-        <v>-129.36000000000001</v>
+        <v>-204.36</v>
       </c>
       <c r="P49" s="4">
-        <v>-433.42</v>
+        <v>-338.66</v>
       </c>
       <c r="Q49" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V49" s="4">
-        <v>137.5</v>
+        <v>212.5</v>
       </c>
       <c r="W49" s="4">
-        <v>37.5</v>
+        <v>162.5</v>
       </c>
       <c r="X49" s="4">
-        <v>166.86</v>
+        <v>366.86</v>
       </c>
       <c r="Y49">
-        <v>4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2">
         <v>46317</v>
       </c>
       <c r="C50">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
         <v>26</v>
@@ -4163,54 +4364,54 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>7699.75</v>
+        <v>7691</v>
       </c>
       <c r="J50">
-        <v>7694</v>
+        <v>7696.25</v>
       </c>
       <c r="K50" s="3">
-        <v>46317.59652777778</v>
+        <v>46317.468055555553</v>
       </c>
       <c r="L50" s="3">
-        <v>46317.602083333331</v>
+        <v>46317.470138888886</v>
       </c>
       <c r="M50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N50" t="s">
         <v>31</v>
       </c>
       <c r="O50" s="4">
-        <v>-291.86</v>
+        <v>-266.86</v>
       </c>
       <c r="P50" s="4">
-        <v>-725.28</v>
+        <v>-605.52</v>
       </c>
       <c r="Q50" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V50" s="4">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="W50" s="4">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="X50" s="4">
-        <v>466.86</v>
+        <v>316.86</v>
       </c>
       <c r="Y50">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B51" s="2">
         <v>46317</v>
       </c>
       <c r="C51">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D51" t="s">
         <v>26</v>
@@ -4222,60 +4423,60 @@
         <v>28</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>7684</v>
+        <v>7700.75</v>
       </c>
       <c r="J51">
-        <v>7682.5</v>
+        <v>7712</v>
       </c>
       <c r="K51" s="3">
-        <v>46317.606249999997</v>
+        <v>46317.470833333333</v>
       </c>
       <c r="L51" s="3">
-        <v>46317.611805555556</v>
+        <v>46317.474999999999</v>
       </c>
       <c r="M51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" s="4">
+        <v>558.14</v>
+      </c>
+      <c r="P51" s="4">
+        <v>-47.38</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="V51" s="4">
+        <v>100</v>
+      </c>
+      <c r="W51" s="4">
+        <v>587.5</v>
+      </c>
+      <c r="X51" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y51">
         <v>36</v>
-      </c>
-      <c r="O51" s="4">
-        <v>70.64</v>
-      </c>
-      <c r="P51" s="4">
-        <v>-654.64</v>
-      </c>
-      <c r="Q51" s="4">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="V51" s="4">
-        <v>200</v>
-      </c>
-      <c r="W51" s="4">
-        <v>112.5</v>
-      </c>
-      <c r="X51" s="4">
-        <v>41.86</v>
-      </c>
-      <c r="Y51">
-        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B52" s="2">
         <v>46317</v>
       </c>
       <c r="C52">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" t="s">
         <v>26</v>
@@ -4287,34 +4488,34 @@
         <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>7687</v>
+        <v>7700.75</v>
       </c>
       <c r="J52">
-        <v>7689.75</v>
+        <v>7697.25</v>
       </c>
       <c r="K52" s="3">
-        <v>46317.629861111112</v>
+        <v>46317.482638888891</v>
       </c>
       <c r="L52" s="3">
-        <v>46317.633333333331</v>
+        <v>46317.484722222223</v>
       </c>
       <c r="M52" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N52" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O52" s="4">
-        <v>133.13999999999999</v>
+        <v>-179.36</v>
       </c>
       <c r="P52" s="4">
-        <v>-521.5</v>
+        <v>-226.74</v>
       </c>
       <c r="Q52" s="4">
         <v>4.3600000000000003</v>
@@ -4323,24 +4524,24 @@
         <v>175</v>
       </c>
       <c r="W52" s="4">
-        <v>162.5</v>
+        <v>87.5</v>
       </c>
       <c r="X52" s="4">
-        <v>29.36</v>
+        <v>266.86</v>
       </c>
       <c r="Y52">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B53" s="2">
         <v>46317</v>
       </c>
       <c r="C53">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
@@ -4352,60 +4553,60 @@
         <v>28</v>
       </c>
       <c r="G53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>7697.25</v>
+      </c>
+      <c r="J53">
+        <v>7692.75</v>
+      </c>
+      <c r="K53" s="3">
+        <v>46317.484722222223</v>
+      </c>
+      <c r="L53" s="3">
+        <v>46317.486111111109</v>
+      </c>
+      <c r="M53" t="s">
         <v>32</v>
       </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53">
-        <v>7688.25</v>
-      </c>
-      <c r="J53">
-        <v>7685.25</v>
-      </c>
-      <c r="K53" s="3">
-        <v>46317.649305555555</v>
-      </c>
-      <c r="L53" s="3">
-        <v>46317.652777777781</v>
-      </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>33</v>
       </c>
-      <c r="N53" t="s">
-        <v>34</v>
-      </c>
       <c r="O53" s="4">
-        <v>145.63999999999999</v>
+        <v>220.64</v>
       </c>
       <c r="P53" s="4">
-        <v>-375.86</v>
+        <v>-6.1</v>
       </c>
       <c r="Q53" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="V53" s="4">
-        <v>100</v>
+        <v>162.5</v>
       </c>
       <c r="W53" s="4">
-        <v>175</v>
+        <v>425</v>
       </c>
       <c r="X53" s="4">
-        <v>29.36</v>
+        <v>204.36</v>
       </c>
       <c r="Y53">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B54" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
@@ -4414,75 +4615,63 @@
         <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>7733</v>
+        <v>7701.5</v>
       </c>
       <c r="J54">
-        <v>7732.75</v>
+        <v>7696.25</v>
       </c>
       <c r="K54" s="3">
-        <v>46315.411111111112</v>
+        <v>46317.488194444442</v>
       </c>
       <c r="L54" s="3">
-        <v>46315.413194444445</v>
+        <v>46317.489583333336</v>
       </c>
       <c r="M54" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="N54" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O54" s="4">
-        <v>-16.86</v>
+        <v>-266.86</v>
       </c>
       <c r="P54" s="4">
-        <v>-16.86</v>
+        <v>-272.95999999999998</v>
       </c>
       <c r="Q54" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R54" s="4">
-        <v>0</v>
-      </c>
-      <c r="S54" s="4">
-        <v>0</v>
-      </c>
-      <c r="T54" s="4">
-        <v>0</v>
-      </c>
-      <c r="U54" s="4">
-        <v>0</v>
-      </c>
       <c r="V54" s="4">
-        <v>175</v>
+        <v>287.5</v>
       </c>
       <c r="W54" s="4">
-        <v>237.5</v>
+        <v>0</v>
       </c>
       <c r="X54" s="4">
-        <v>254.36</v>
+        <v>266.86</v>
       </c>
       <c r="Y54">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B55" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -4491,75 +4680,63 @@
         <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>7696.25</v>
+      </c>
+      <c r="J55">
+        <v>7701.25</v>
+      </c>
+      <c r="K55" s="3">
+        <v>46317.489583333336</v>
+      </c>
+      <c r="L55" s="3">
+        <v>46317.493055555555</v>
+      </c>
+      <c r="M55" t="s">
         <v>32</v>
       </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55">
-        <v>7778.5</v>
-      </c>
-      <c r="J55">
-        <v>7775.75</v>
-      </c>
-      <c r="K55" s="3">
-        <v>46315.460416666669</v>
-      </c>
-      <c r="L55" s="3">
-        <v>46315.465277777781</v>
-      </c>
-      <c r="M55" t="s">
-        <v>50</v>
-      </c>
       <c r="N55" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O55" s="4">
-        <v>133.13999999999999</v>
+        <v>-254.36</v>
       </c>
       <c r="P55" s="4">
-        <v>116.28</v>
+        <v>-527.32000000000005</v>
       </c>
       <c r="Q55" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R55" s="4">
-        <v>0</v>
-      </c>
-      <c r="S55" s="4">
-        <v>0</v>
-      </c>
-      <c r="T55" s="4">
-        <v>0</v>
-      </c>
-      <c r="U55" s="4">
-        <v>0</v>
-      </c>
       <c r="V55" s="4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="W55" s="4">
-        <v>150</v>
+        <v>37.5</v>
       </c>
       <c r="X55" s="4">
-        <v>16.86</v>
+        <v>291.86</v>
       </c>
       <c r="Y55">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B56" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
@@ -4568,75 +4745,63 @@
         <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>7772.75</v>
+        <v>7711</v>
       </c>
       <c r="J56">
-        <v>7755.75</v>
+        <v>7716.75</v>
       </c>
       <c r="K56" s="3">
-        <v>46315.46597222222</v>
+        <v>46317.49722222222</v>
       </c>
       <c r="L56" s="3">
-        <v>46315.467361111114</v>
+        <v>46317.5</v>
       </c>
       <c r="M56" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="N56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O56" s="4">
-        <v>845.64</v>
+        <v>283.14</v>
       </c>
       <c r="P56" s="4">
-        <v>961.92</v>
+        <v>-244.18</v>
       </c>
       <c r="Q56" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R56" s="4">
-        <v>0</v>
-      </c>
-      <c r="S56" s="4">
-        <v>0</v>
-      </c>
-      <c r="T56" s="4">
-        <v>0</v>
-      </c>
-      <c r="U56" s="4">
-        <v>0</v>
-      </c>
       <c r="V56" s="4">
-        <v>150</v>
+        <v>62.5</v>
       </c>
       <c r="W56" s="4">
-        <v>862.5</v>
+        <v>312.5</v>
       </c>
       <c r="X56" s="4">
-        <v>16.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y56">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B57" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
         <v>26</v>
@@ -4645,7 +4810,7 @@
         <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G57" t="s">
         <v>29</v>
@@ -4654,66 +4819,54 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>7763</v>
+        <v>7711.5</v>
       </c>
       <c r="J57">
-        <v>7766</v>
+        <v>7709</v>
       </c>
       <c r="K57" s="3">
-        <v>46315.487500000003</v>
+        <v>46317.522222222222</v>
       </c>
       <c r="L57" s="3">
-        <v>46315.487500000003</v>
+        <v>46317.522916666669</v>
       </c>
       <c r="M57" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O57" s="4">
-        <v>145.63999999999999</v>
+        <v>120.64</v>
       </c>
       <c r="P57" s="4">
-        <v>1107.56</v>
+        <v>-123.54</v>
       </c>
       <c r="Q57" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R57" s="4">
-        <v>0</v>
-      </c>
-      <c r="S57" s="4">
-        <v>0</v>
-      </c>
-      <c r="T57" s="4">
-        <v>0</v>
-      </c>
-      <c r="U57" s="4">
-        <v>0</v>
-      </c>
       <c r="V57" s="4">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="W57" s="4">
-        <v>150</v>
+        <v>137.5</v>
       </c>
       <c r="X57" s="4">
-        <v>4.3600000000000003</v>
+        <v>16.86</v>
       </c>
       <c r="Y57">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B58" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
         <v>26</v>
@@ -4722,75 +4875,63 @@
         <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>7754</v>
+        <v>7701</v>
       </c>
       <c r="J58">
-        <v>7758.75</v>
+        <v>7698.25</v>
       </c>
       <c r="K58" s="3">
-        <v>46315.512499999997</v>
+        <v>46317.527083333334</v>
       </c>
       <c r="L58" s="3">
-        <v>46315.518750000003</v>
+        <v>46317.530555555553</v>
       </c>
       <c r="M58" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N58" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O58" s="4">
-        <v>-241.86</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P58" s="4">
-        <v>865.7</v>
+        <v>9.6</v>
       </c>
       <c r="Q58" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R58" s="4">
-        <v>0</v>
-      </c>
-      <c r="S58" s="4">
-        <v>0</v>
-      </c>
-      <c r="T58" s="4">
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
-        <v>0</v>
-      </c>
       <c r="V58" s="4">
-        <v>262.5</v>
+        <v>50</v>
       </c>
       <c r="W58" s="4">
-        <v>150</v>
+        <v>237.5</v>
       </c>
       <c r="X58" s="4">
-        <v>391.86</v>
+        <v>104.36</v>
       </c>
       <c r="Y58">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B59" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D59" t="s">
         <v>26</v>
@@ -4799,75 +4940,63 @@
         <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>7766.25</v>
+        <v>7702.25</v>
       </c>
       <c r="J59">
-        <v>7762.25</v>
+        <v>7697.5</v>
       </c>
       <c r="K59" s="3">
-        <v>46315.5625</v>
+        <v>46317.540277777778</v>
       </c>
       <c r="L59" s="3">
-        <v>46315.581250000003</v>
+        <v>46317.543055555558</v>
       </c>
       <c r="M59" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N59" t="s">
         <v>31</v>
       </c>
       <c r="O59" s="4">
-        <v>-204.36</v>
+        <v>-241.86</v>
       </c>
       <c r="P59" s="4">
-        <v>661.34</v>
+        <v>-232.26</v>
       </c>
       <c r="Q59" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R59" s="4">
-        <v>0</v>
-      </c>
-      <c r="S59" s="4">
-        <v>0</v>
-      </c>
-      <c r="T59" s="4">
-        <v>0</v>
-      </c>
-      <c r="U59" s="4">
-        <v>0</v>
-      </c>
       <c r="V59" s="4">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="W59" s="4">
-        <v>112.5</v>
+        <v>87.5</v>
       </c>
       <c r="X59" s="4">
-        <v>316.86</v>
+        <v>329.36</v>
       </c>
       <c r="Y59">
-        <v>53</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B60" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
@@ -4876,75 +5005,63 @@
         <v>27</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G60" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60">
-        <v>7754.5</v>
+        <v>7690</v>
       </c>
       <c r="J60">
-        <v>7753.25</v>
+        <v>7693</v>
       </c>
       <c r="K60" s="3">
-        <v>46315.60833333333</v>
+        <v>46317.547222222223</v>
       </c>
       <c r="L60" s="3">
-        <v>46315.614583333336</v>
+        <v>46317.551388888889</v>
       </c>
       <c r="M60" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N60" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O60" s="4">
-        <v>58.14</v>
+        <v>-154.36000000000001</v>
       </c>
       <c r="P60" s="4">
-        <v>719.48</v>
+        <v>-386.62</v>
       </c>
       <c r="Q60" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R60" s="4">
-        <v>0</v>
-      </c>
-      <c r="S60" s="4">
-        <v>0</v>
-      </c>
-      <c r="T60" s="4">
-        <v>0</v>
-      </c>
-      <c r="U60" s="4">
-        <v>0</v>
-      </c>
       <c r="V60" s="4">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="W60" s="4">
-        <v>287.5</v>
+        <v>175</v>
       </c>
       <c r="X60" s="4">
-        <v>229.36</v>
+        <v>329.36</v>
       </c>
       <c r="Y60">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B61" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
         <v>26</v>
@@ -4953,75 +5070,63 @@
         <v>27</v>
       </c>
       <c r="F61" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G61" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>7695.5</v>
+      </c>
+      <c r="J61">
+        <v>7698.75</v>
+      </c>
+      <c r="K61" s="3">
+        <v>46317.558333333334</v>
+      </c>
+      <c r="L61" s="3">
+        <v>46317.561111111114</v>
+      </c>
+      <c r="M61" t="s">
         <v>32</v>
-      </c>
-      <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
-        <v>7750.25</v>
-      </c>
-      <c r="J61">
-        <v>7751</v>
-      </c>
-      <c r="K61" s="3">
-        <v>46315.63958333333</v>
-      </c>
-      <c r="L61" s="3">
-        <v>46315.643055555556</v>
-      </c>
-      <c r="M61" t="s">
-        <v>51</v>
       </c>
       <c r="N61" t="s">
         <v>31</v>
       </c>
       <c r="O61" s="4">
-        <v>-41.86</v>
+        <v>-166.86</v>
       </c>
       <c r="P61" s="4">
-        <v>677.62</v>
+        <v>-553.48</v>
       </c>
       <c r="Q61" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R61" s="4">
-        <v>0</v>
-      </c>
-      <c r="S61" s="4">
-        <v>0</v>
-      </c>
-      <c r="T61" s="4">
-        <v>0</v>
-      </c>
-      <c r="U61" s="4">
-        <v>0</v>
-      </c>
       <c r="V61" s="4">
-        <v>50</v>
+        <v>162.5</v>
       </c>
       <c r="W61" s="4">
-        <v>187.5</v>
+        <v>150</v>
       </c>
       <c r="X61" s="4">
-        <v>229.36</v>
+        <v>316.86</v>
       </c>
       <c r="Y61">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B62" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
@@ -5030,75 +5135,63 @@
         <v>27</v>
       </c>
       <c r="F62" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G62" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>7759.75</v>
+        <v>7698.25</v>
       </c>
       <c r="J62">
-        <v>7755.5</v>
+        <v>7702.5</v>
       </c>
       <c r="K62" s="3">
-        <v>46316.420138888891</v>
+        <v>46317.561805555553</v>
       </c>
       <c r="L62" s="3">
-        <v>46316.423611111109</v>
+        <v>46317.56527777778</v>
       </c>
       <c r="M62" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="N62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O62" s="4">
         <v>208.14</v>
       </c>
       <c r="P62" s="4">
-        <v>208.14</v>
+        <v>-345.34</v>
       </c>
       <c r="Q62" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R62" s="4">
-        <v>0</v>
-      </c>
-      <c r="S62" s="4">
-        <v>0</v>
-      </c>
-      <c r="T62" s="4">
-        <v>0</v>
-      </c>
-      <c r="U62" s="4">
-        <v>0</v>
-      </c>
       <c r="V62" s="4">
-        <v>150</v>
+        <v>112.5</v>
       </c>
       <c r="W62" s="4">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="X62" s="4">
-        <v>41.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y62">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B63" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D63" t="s">
         <v>26</v>
@@ -5107,75 +5200,63 @@
         <v>27</v>
       </c>
       <c r="F63" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G63" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>7762.25</v>
+        <v>7704.75</v>
       </c>
       <c r="J63">
-        <v>7765</v>
+        <v>7697.75</v>
       </c>
       <c r="K63" s="3">
-        <v>46316.436111111114</v>
+        <v>46317.56527777778</v>
       </c>
       <c r="L63" s="3">
-        <v>46316.438194444447</v>
+        <v>46317.573611111111</v>
       </c>
       <c r="M63" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N63" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O63" s="4">
-        <v>133.13999999999999</v>
+        <v>-354.36</v>
       </c>
       <c r="P63" s="4">
-        <v>341.28</v>
+        <v>-699.7</v>
       </c>
       <c r="Q63" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R63" s="4">
-        <v>0</v>
-      </c>
-      <c r="S63" s="4">
-        <v>0</v>
-      </c>
-      <c r="T63" s="4">
-        <v>0</v>
-      </c>
-      <c r="U63" s="4">
-        <v>0</v>
-      </c>
       <c r="V63" s="4">
-        <v>162.5</v>
+        <v>362.5</v>
       </c>
       <c r="W63" s="4">
-        <v>150</v>
+        <v>37.5</v>
       </c>
       <c r="X63" s="4">
-        <v>16.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y63">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B64" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -5184,7 +5265,7 @@
         <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G64" t="s">
         <v>29</v>
@@ -5193,52 +5274,40 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>7774.25</v>
+        <v>7687.75</v>
       </c>
       <c r="J64">
-        <v>7777.25</v>
+        <v>7679.75</v>
       </c>
       <c r="K64" s="3">
-        <v>46316.449305555558</v>
+        <v>46317.584027777775</v>
       </c>
       <c r="L64" s="3">
-        <v>46316.45208333333</v>
+        <v>46317.586111111108</v>
       </c>
       <c r="M64" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O64" s="4">
-        <v>145.63999999999999</v>
+        <v>395.64</v>
       </c>
       <c r="P64" s="4">
-        <v>486.92</v>
+        <v>-304.06</v>
       </c>
       <c r="Q64" s="4">
         <v>4.3600000000000003</v>
-      </c>
-      <c r="R64" s="4">
-        <v>0</v>
-      </c>
-      <c r="S64" s="4">
-        <v>0</v>
-      </c>
-      <c r="T64" s="4">
-        <v>0</v>
-      </c>
-      <c r="U64" s="4">
-        <v>0</v>
       </c>
       <c r="V64" s="4">
         <v>25</v>
       </c>
       <c r="W64" s="4">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="X64" s="4">
-        <v>104.36</v>
+        <v>29.36</v>
       </c>
       <c r="Y64">
         <v>22</v>
@@ -5246,13 +5315,13 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B65" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
         <v>26</v>
@@ -5261,75 +5330,63 @@
         <v>27</v>
       </c>
       <c r="F65" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G65" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>7690</v>
+      </c>
+      <c r="J65">
+        <v>7692.5</v>
+      </c>
+      <c r="K65" s="3">
+        <v>46317.59375</v>
+      </c>
+      <c r="L65" s="3">
+        <v>46317.594444444447</v>
+      </c>
+      <c r="M65" t="s">
         <v>32</v>
-      </c>
-      <c r="H65">
-        <v>1</v>
-      </c>
-      <c r="I65">
-        <v>7788.5</v>
-      </c>
-      <c r="J65">
-        <v>7791.75</v>
-      </c>
-      <c r="K65" s="3">
-        <v>46316.518750000003</v>
-      </c>
-      <c r="L65" s="3">
-        <v>46316.526388888888</v>
-      </c>
-      <c r="M65" t="s">
-        <v>50</v>
       </c>
       <c r="N65" t="s">
         <v>31</v>
       </c>
       <c r="O65" s="4">
-        <v>-166.86</v>
+        <v>-129.36000000000001</v>
       </c>
       <c r="P65" s="4">
-        <v>320.06</v>
+        <v>-433.42</v>
       </c>
       <c r="Q65" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R65" s="4">
-        <v>0</v>
-      </c>
-      <c r="S65" s="4">
-        <v>0</v>
-      </c>
-      <c r="T65" s="4">
-        <v>0</v>
-      </c>
-      <c r="U65" s="4">
-        <v>0</v>
-      </c>
       <c r="V65" s="4">
-        <v>175</v>
+        <v>137.5</v>
       </c>
       <c r="W65" s="4">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="X65" s="4">
-        <v>216.86</v>
+        <v>166.86</v>
       </c>
       <c r="Y65">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B66" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>26</v>
@@ -5338,75 +5395,63 @@
         <v>27</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G66" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>7799.5</v>
+        <v>7699.75</v>
       </c>
       <c r="J66">
-        <v>7798.75</v>
+        <v>7694</v>
       </c>
       <c r="K66" s="3">
-        <v>46316.527083333334</v>
+        <v>46317.59652777778</v>
       </c>
       <c r="L66" s="3">
-        <v>46316.527777777781</v>
+        <v>46317.602083333331</v>
       </c>
       <c r="M66" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N66" t="s">
         <v>31</v>
       </c>
       <c r="O66" s="4">
-        <v>-41.86</v>
+        <v>-291.86</v>
       </c>
       <c r="P66" s="4">
-        <v>278.2</v>
+        <v>-725.28</v>
       </c>
       <c r="Q66" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R66" s="4">
-        <v>0</v>
-      </c>
-      <c r="S66" s="4">
-        <v>0</v>
-      </c>
-      <c r="T66" s="4">
-        <v>0</v>
-      </c>
-      <c r="U66" s="4">
-        <v>0</v>
-      </c>
       <c r="V66" s="4">
-        <v>37.5</v>
+        <v>300</v>
       </c>
       <c r="W66" s="4">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="X66" s="4">
-        <v>391.86</v>
+        <v>466.86</v>
       </c>
       <c r="Y66">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B67" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -5415,75 +5460,63 @@
         <v>27</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>7805</v>
+        <v>7684</v>
       </c>
       <c r="J67">
-        <v>7802.5</v>
+        <v>7682.5</v>
       </c>
       <c r="K67" s="3">
-        <v>46316.615972222222</v>
+        <v>46317.606249999997</v>
       </c>
       <c r="L67" s="3">
-        <v>46316.616666666669</v>
+        <v>46317.611805555556</v>
       </c>
       <c r="M67" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="N67" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O67" s="4">
-        <v>120.64</v>
+        <v>70.64</v>
       </c>
       <c r="P67" s="4">
-        <v>398.84</v>
+        <v>-654.64</v>
       </c>
       <c r="Q67" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R67" s="4">
-        <v>0</v>
-      </c>
-      <c r="S67" s="4">
-        <v>0</v>
-      </c>
-      <c r="T67" s="4">
-        <v>0</v>
-      </c>
-      <c r="U67" s="4">
-        <v>0</v>
-      </c>
       <c r="V67" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W67" s="4">
-        <v>162.5</v>
+        <v>112.5</v>
       </c>
       <c r="X67" s="4">
         <v>41.86</v>
       </c>
       <c r="Y67">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B68" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
@@ -5492,75 +5525,63 @@
         <v>27</v>
       </c>
       <c r="F68" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G68" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68">
-        <v>7798.75</v>
+        <v>7687</v>
       </c>
       <c r="J68">
-        <v>7797.5</v>
+        <v>7689.75</v>
       </c>
       <c r="K68" s="3">
-        <v>46316.617361111108</v>
+        <v>46317.629861111112</v>
       </c>
       <c r="L68" s="3">
-        <v>46316.619444444441</v>
+        <v>46317.633333333331</v>
       </c>
       <c r="M68" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="N68" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O68" s="4">
-        <v>58.14</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P68" s="4">
-        <v>456.98</v>
+        <v>-521.5</v>
       </c>
       <c r="Q68" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R68" s="4">
-        <v>0</v>
-      </c>
-      <c r="S68" s="4">
-        <v>0</v>
-      </c>
-      <c r="T68" s="4">
-        <v>0</v>
-      </c>
-      <c r="U68" s="4">
-        <v>0</v>
-      </c>
       <c r="V68" s="4">
-        <v>137.5</v>
+        <v>175</v>
       </c>
       <c r="W68" s="4">
-        <v>250</v>
+        <v>162.5</v>
       </c>
       <c r="X68" s="4">
-        <v>191.86</v>
+        <v>29.36</v>
       </c>
       <c r="Y68">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B69" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
         <v>26</v>
@@ -5569,7 +5590,7 @@
         <v>27</v>
       </c>
       <c r="F69" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G69" t="s">
         <v>29</v>
@@ -5578,63 +5599,51 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>7786.5</v>
+        <v>7688.25</v>
       </c>
       <c r="J69">
-        <v>7789.25</v>
+        <v>7685.25</v>
       </c>
       <c r="K69" s="3">
-        <v>46316.636111111111</v>
+        <v>46317.649305555555</v>
       </c>
       <c r="L69" s="3">
-        <v>46316.636805555558</v>
+        <v>46317.652777777781</v>
       </c>
       <c r="M69" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="N69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O69" s="4">
-        <v>133.13999999999999</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P69" s="4">
-        <v>590.12</v>
+        <v>-375.86</v>
       </c>
       <c r="Q69" s="4">
         <v>4.3600000000000003</v>
       </c>
-      <c r="R69" s="4">
-        <v>0</v>
-      </c>
-      <c r="S69" s="4">
-        <v>0</v>
-      </c>
-      <c r="T69" s="4">
-        <v>0</v>
-      </c>
-      <c r="U69" s="4">
-        <v>0</v>
-      </c>
       <c r="V69" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="W69" s="4">
-        <v>137.5</v>
+        <v>175</v>
       </c>
       <c r="X69" s="4">
-        <v>4.3600000000000003</v>
+        <v>29.36</v>
       </c>
       <c r="Y69">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B70" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -5646,37 +5655,37 @@
         <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>7727.25</v>
+        <v>7733</v>
       </c>
       <c r="J70">
-        <v>7718.5</v>
+        <v>7736.5</v>
       </c>
       <c r="K70" s="3">
-        <v>46317.422222222223</v>
+        <v>46314.412499999999</v>
       </c>
       <c r="L70" s="3">
-        <v>46317.427083333336</v>
+        <v>46314.413888888892</v>
       </c>
       <c r="M70" t="s">
         <v>51</v>
       </c>
       <c r="N70" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O70" s="4">
-        <v>433.14</v>
+        <v>-179.36</v>
       </c>
       <c r="P70" s="4">
-        <v>433.14</v>
+        <v>-179.36</v>
       </c>
       <c r="Q70" s="4">
         <v>4.3600000000000003</v>
@@ -5694,24 +5703,24 @@
         <v>0</v>
       </c>
       <c r="V70" s="4">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="W70" s="4">
-        <v>462.5</v>
+        <v>50</v>
       </c>
       <c r="X70" s="4">
-        <v>29.36</v>
+        <v>229.36</v>
       </c>
       <c r="Y70">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B71" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -5723,37 +5732,37 @@
         <v>27</v>
       </c>
       <c r="F71" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G71" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>7695</v>
+        <v>7743.25</v>
       </c>
       <c r="J71">
-        <v>7689.75</v>
+        <v>7753.25</v>
       </c>
       <c r="K71" s="3">
-        <v>46317.454861111109</v>
+        <v>46314.425694444442</v>
       </c>
       <c r="L71" s="3">
-        <v>46317.454861111109</v>
+        <v>46314.427083333336</v>
       </c>
       <c r="M71" t="s">
         <v>52</v>
       </c>
       <c r="N71" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O71" s="4">
-        <v>-266.86</v>
+        <v>495.64</v>
       </c>
       <c r="P71" s="4">
-        <v>166.28</v>
+        <v>316.27999999999997</v>
       </c>
       <c r="Q71" s="4">
         <v>4.3600000000000003</v>
@@ -5771,24 +5780,24 @@
         <v>0</v>
       </c>
       <c r="V71" s="4">
-        <v>300</v>
+        <v>37.5</v>
       </c>
       <c r="W71" s="4">
-        <v>75</v>
+        <v>650</v>
       </c>
       <c r="X71" s="4">
-        <v>341.86</v>
+        <v>154.36000000000001</v>
       </c>
       <c r="Y71">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B72" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C72">
         <v>3</v>
@@ -5800,7 +5809,7 @@
         <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G72" t="s">
         <v>29</v>
@@ -5809,28 +5818,28 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>7700.75</v>
+        <v>7746.5</v>
       </c>
       <c r="J72">
-        <v>7712</v>
+        <v>7743.5</v>
       </c>
       <c r="K72" s="3">
-        <v>46317.470833333333</v>
+        <v>46314.438194444447</v>
       </c>
       <c r="L72" s="3">
-        <v>46317.474999999999</v>
+        <v>46314.438888888886</v>
       </c>
       <c r="M72" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N72" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O72" s="4">
-        <v>558.14</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P72" s="4">
-        <v>724.42</v>
+        <v>461.92</v>
       </c>
       <c r="Q72" s="4">
         <v>4.3600000000000003</v>
@@ -5848,24 +5857,24 @@
         <v>0</v>
       </c>
       <c r="V72" s="4">
-        <v>100</v>
+        <v>137.5</v>
       </c>
       <c r="W72" s="4">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="X72" s="4">
         <v>29.36</v>
       </c>
       <c r="Y72">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B73" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C73">
         <v>4</v>
@@ -5877,37 +5886,37 @@
         <v>27</v>
       </c>
       <c r="F73" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G73" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>7711</v>
+        <v>7754</v>
       </c>
       <c r="J73">
-        <v>7716.75</v>
+        <v>7755.5</v>
       </c>
       <c r="K73" s="3">
-        <v>46317.49722222222</v>
+        <v>46314.458333333336</v>
       </c>
       <c r="L73" s="3">
-        <v>46317.5</v>
+        <v>46314.463194444441</v>
       </c>
       <c r="M73" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N73" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O73" s="4">
-        <v>283.14</v>
+        <v>70.64</v>
       </c>
       <c r="P73" s="4">
-        <v>1007.56</v>
+        <v>532.55999999999995</v>
       </c>
       <c r="Q73" s="4">
         <v>4.3600000000000003</v>
@@ -5925,24 +5934,24 @@
         <v>0</v>
       </c>
       <c r="V73" s="4">
-        <v>62.5</v>
+        <v>212.5</v>
       </c>
       <c r="W73" s="4">
-        <v>312.5</v>
+        <v>225</v>
       </c>
       <c r="X73" s="4">
-        <v>29.36</v>
+        <v>154.36000000000001</v>
       </c>
       <c r="Y73">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B74" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -5954,37 +5963,37 @@
         <v>27</v>
       </c>
       <c r="F74" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>7711.5</v>
+        <v>7763.25</v>
       </c>
       <c r="J74">
-        <v>7709</v>
+        <v>7759.75</v>
       </c>
       <c r="K74" s="3">
-        <v>46317.522222222222</v>
+        <v>46314.498611111114</v>
       </c>
       <c r="L74" s="3">
-        <v>46317.522916666669</v>
+        <v>46314.5</v>
       </c>
       <c r="M74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O74" s="4">
-        <v>120.64</v>
+        <v>170.64</v>
       </c>
       <c r="P74" s="4">
-        <v>1128.2</v>
+        <v>703.2</v>
       </c>
       <c r="Q74" s="4">
         <v>4.3600000000000003</v>
@@ -6002,24 +6011,24 @@
         <v>0</v>
       </c>
       <c r="V74" s="4">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="W74" s="4">
-        <v>137.5</v>
+        <v>187.5</v>
       </c>
       <c r="X74" s="4">
         <v>16.86</v>
       </c>
       <c r="Y74">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B75" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C75">
         <v>6</v>
@@ -6031,37 +6040,37 @@
         <v>27</v>
       </c>
       <c r="F75" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>7701</v>
+        <v>7752.75</v>
       </c>
       <c r="J75">
-        <v>7698.25</v>
+        <v>7754.25</v>
       </c>
       <c r="K75" s="3">
-        <v>46317.527083333334</v>
+        <v>46314.501388888886</v>
       </c>
       <c r="L75" s="3">
-        <v>46317.530555555553</v>
+        <v>46314.503472222219</v>
       </c>
       <c r="M75" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N75" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O75" s="4">
-        <v>133.13999999999999</v>
+        <v>-79.36</v>
       </c>
       <c r="P75" s="4">
-        <v>1261.3399999999999</v>
+        <v>623.84</v>
       </c>
       <c r="Q75" s="4">
         <v>4.3600000000000003</v>
@@ -6079,13 +6088,13 @@
         <v>0</v>
       </c>
       <c r="V75" s="4">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="W75" s="4">
-        <v>237.5</v>
+        <v>275</v>
       </c>
       <c r="X75" s="4">
-        <v>104.36</v>
+        <v>354.36</v>
       </c>
       <c r="Y75">
         <v>21</v>
@@ -6093,10 +6102,10 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B76" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -6108,37 +6117,37 @@
         <v>27</v>
       </c>
       <c r="F76" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G76" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>7702.25</v>
+        <v>7744.5</v>
       </c>
       <c r="J76">
-        <v>7697.5</v>
+        <v>7741.75</v>
       </c>
       <c r="K76" s="3">
-        <v>46317.540277777778</v>
+        <v>46314.571527777778</v>
       </c>
       <c r="L76" s="3">
-        <v>46317.543055555558</v>
+        <v>46314.571527777778</v>
       </c>
       <c r="M76" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N76" t="s">
         <v>31</v>
       </c>
       <c r="O76" s="4">
-        <v>-241.86</v>
+        <v>-141.86000000000001</v>
       </c>
       <c r="P76" s="4">
-        <v>1019.48</v>
+        <v>481.98</v>
       </c>
       <c r="Q76" s="4">
         <v>4.3600000000000003</v>
@@ -6156,27 +6165,27 @@
         <v>0</v>
       </c>
       <c r="V76" s="4">
-        <v>250</v>
+        <v>137.5</v>
       </c>
       <c r="W76" s="4">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="X76" s="4">
-        <v>329.36</v>
+        <v>204.36</v>
       </c>
       <c r="Y76">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B77" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C77">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D77" t="s">
         <v>26</v>
@@ -6185,37 +6194,37 @@
         <v>27</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G77" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>7690</v>
+        <v>7733</v>
       </c>
       <c r="J77">
-        <v>7693</v>
+        <v>7732.75</v>
       </c>
       <c r="K77" s="3">
-        <v>46317.547222222223</v>
+        <v>46315.411111111112</v>
       </c>
       <c r="L77" s="3">
-        <v>46317.551388888889</v>
+        <v>46315.413194444445</v>
       </c>
       <c r="M77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N77" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O77" s="4">
-        <v>-154.36000000000001</v>
+        <v>-16.86</v>
       </c>
       <c r="P77" s="4">
-        <v>865.12</v>
+        <v>-16.86</v>
       </c>
       <c r="Q77" s="4">
         <v>4.3600000000000003</v>
@@ -6233,27 +6242,27 @@
         <v>0</v>
       </c>
       <c r="V77" s="4">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="W77" s="4">
-        <v>175</v>
+        <v>237.5</v>
       </c>
       <c r="X77" s="4">
-        <v>329.36</v>
+        <v>254.36</v>
       </c>
       <c r="Y77">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B78" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
@@ -6262,7 +6271,7 @@
         <v>27</v>
       </c>
       <c r="F78" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G78" t="s">
         <v>29</v>
@@ -6271,28 +6280,28 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>7704.75</v>
+        <v>7778.5</v>
       </c>
       <c r="J78">
-        <v>7697.75</v>
+        <v>7775.75</v>
       </c>
       <c r="K78" s="3">
-        <v>46317.56527777778</v>
+        <v>46315.460416666669</v>
       </c>
       <c r="L78" s="3">
-        <v>46317.573611111111</v>
+        <v>46315.465277777781</v>
       </c>
       <c r="M78" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N78" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O78" s="4">
-        <v>-354.36</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="P78" s="4">
-        <v>510.76</v>
+        <v>116.28</v>
       </c>
       <c r="Q78" s="4">
         <v>4.3600000000000003</v>
@@ -6310,27 +6319,27 @@
         <v>0</v>
       </c>
       <c r="V78" s="4">
-        <v>362.5</v>
+        <v>200</v>
       </c>
       <c r="W78" s="4">
-        <v>37.5</v>
+        <v>150</v>
       </c>
       <c r="X78" s="4">
-        <v>391.86</v>
+        <v>16.86</v>
       </c>
       <c r="Y78">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B79" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D79" t="s">
         <v>26</v>
@@ -6339,37 +6348,37 @@
         <v>27</v>
       </c>
       <c r="F79" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G79" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79">
-        <v>7687.75</v>
+        <v>7772.75</v>
       </c>
       <c r="J79">
-        <v>7679.75</v>
+        <v>7755.75</v>
       </c>
       <c r="K79" s="3">
-        <v>46317.584027777775</v>
+        <v>46315.46597222222</v>
       </c>
       <c r="L79" s="3">
-        <v>46317.586111111108</v>
+        <v>46315.467361111114</v>
       </c>
       <c r="M79" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O79" s="4">
-        <v>395.64</v>
+        <v>845.64</v>
       </c>
       <c r="P79" s="4">
-        <v>906.4</v>
+        <v>961.92</v>
       </c>
       <c r="Q79" s="4">
         <v>4.3600000000000003</v>
@@ -6387,66 +6396,66 @@
         <v>0</v>
       </c>
       <c r="V79" s="4">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="W79" s="4">
-        <v>425</v>
+        <v>862.5</v>
       </c>
       <c r="X79" s="4">
-        <v>29.36</v>
+        <v>16.86</v>
       </c>
       <c r="Y79">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>55</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" t="s">
+        <v>50</v>
+      </c>
+      <c r="G80" t="s">
+        <v>34</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>7763</v>
+      </c>
+      <c r="J80">
+        <v>7766</v>
+      </c>
+      <c r="K80" s="3">
+        <v>46315.487500000003</v>
+      </c>
+      <c r="L80" s="3">
+        <v>46315.487500000003</v>
+      </c>
+      <c r="M80" t="s">
         <v>54</v>
       </c>
-      <c r="B80" s="2">
-        <v>46317</v>
-      </c>
-      <c r="C80">
-        <v>11</v>
-      </c>
-      <c r="D80" t="s">
-        <v>26</v>
-      </c>
-      <c r="E80" t="s">
-        <v>27</v>
-      </c>
-      <c r="F80" t="s">
-        <v>48</v>
-      </c>
-      <c r="G80" t="s">
-        <v>29</v>
-      </c>
-      <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="I80">
-        <v>7699.75</v>
-      </c>
-      <c r="J80">
-        <v>7694</v>
-      </c>
-      <c r="K80" s="3">
-        <v>46317.59652777778</v>
-      </c>
-      <c r="L80" s="3">
-        <v>46317.602083333331</v>
-      </c>
-      <c r="M80" t="s">
-        <v>49</v>
-      </c>
       <c r="N80" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O80" s="4">
-        <v>-291.86</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="P80" s="4">
-        <v>614.54</v>
+        <v>1107.56</v>
       </c>
       <c r="Q80" s="4">
         <v>4.3600000000000003</v>
@@ -6464,27 +6473,27 @@
         <v>0</v>
       </c>
       <c r="V80" s="4">
-        <v>300</v>
+        <v>37.5</v>
       </c>
       <c r="W80" s="4">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="X80" s="4">
-        <v>466.86</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Y80">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B81" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C81">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D81" t="s">
         <v>26</v>
@@ -6493,37 +6502,37 @@
         <v>27</v>
       </c>
       <c r="F81" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>7684</v>
+        <v>7754</v>
       </c>
       <c r="J81">
-        <v>7682.5</v>
+        <v>7758.75</v>
       </c>
       <c r="K81" s="3">
-        <v>46317.606249999997</v>
+        <v>46315.512499999997</v>
       </c>
       <c r="L81" s="3">
-        <v>46317.611805555556</v>
+        <v>46315.518750000003</v>
       </c>
       <c r="M81" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N81" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O81" s="4">
-        <v>70.64</v>
+        <v>-241.86</v>
       </c>
       <c r="P81" s="4">
-        <v>685.18</v>
+        <v>865.7</v>
       </c>
       <c r="Q81" s="4">
         <v>4.3600000000000003</v>
@@ -6541,27 +6550,27 @@
         <v>0</v>
       </c>
       <c r="V81" s="4">
-        <v>200</v>
+        <v>262.5</v>
       </c>
       <c r="W81" s="4">
-        <v>112.5</v>
+        <v>150</v>
       </c>
       <c r="X81" s="4">
-        <v>41.86</v>
+        <v>391.86</v>
       </c>
       <c r="Y81">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B82" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="C82">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D82" t="s">
         <v>26</v>
@@ -6570,37 +6579,37 @@
         <v>27</v>
       </c>
       <c r="F82" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>7687</v>
+        <v>7766.25</v>
       </c>
       <c r="J82">
-        <v>7689.75</v>
+        <v>7762.25</v>
       </c>
       <c r="K82" s="3">
-        <v>46317.629861111112</v>
+        <v>46315.5625</v>
       </c>
       <c r="L82" s="3">
-        <v>46317.633333333331</v>
+        <v>46315.581250000003</v>
       </c>
       <c r="M82" t="s">
         <v>52</v>
       </c>
       <c r="N82" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O82" s="4">
-        <v>133.13999999999999</v>
+        <v>-204.36</v>
       </c>
       <c r="P82" s="4">
-        <v>818.32</v>
+        <v>661.34</v>
       </c>
       <c r="Q82" s="4">
         <v>4.3600000000000003</v>
@@ -6618,92 +6627,1863 @@
         <v>0</v>
       </c>
       <c r="V82" s="4">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="W82" s="4">
-        <v>162.5</v>
+        <v>112.5</v>
       </c>
       <c r="X82" s="4">
-        <v>29.36</v>
+        <v>316.86</v>
       </c>
       <c r="Y82">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C83">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F83" t="s">
+        <v>50</v>
+      </c>
+      <c r="G83" t="s">
+        <v>29</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>7754.5</v>
+      </c>
+      <c r="J83">
+        <v>7753.25</v>
+      </c>
+      <c r="K83" s="3">
+        <v>46315.60833333333</v>
+      </c>
+      <c r="L83" s="3">
+        <v>46315.614583333336</v>
+      </c>
+      <c r="M83" t="s">
+        <v>53</v>
+      </c>
+      <c r="N83" t="s">
+        <v>31</v>
+      </c>
+      <c r="O83" s="4">
+        <v>58.14</v>
+      </c>
+      <c r="P83" s="4">
+        <v>719.48</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R83" s="4">
+        <v>0</v>
+      </c>
+      <c r="S83" s="4">
+        <v>0</v>
+      </c>
+      <c r="T83" s="4">
+        <v>0</v>
+      </c>
+      <c r="U83" s="4">
+        <v>0</v>
+      </c>
+      <c r="V83" s="4">
+        <v>75</v>
+      </c>
+      <c r="W83" s="4">
+        <v>287.5</v>
+      </c>
+      <c r="X83" s="4">
+        <v>229.36</v>
+      </c>
+      <c r="Y83">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C84">
+        <v>8</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" t="s">
+        <v>50</v>
+      </c>
+      <c r="G84" t="s">
+        <v>29</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>7750.25</v>
+      </c>
+      <c r="J84">
+        <v>7751</v>
+      </c>
+      <c r="K84" s="3">
+        <v>46315.63958333333</v>
+      </c>
+      <c r="L84" s="3">
+        <v>46315.643055555556</v>
+      </c>
+      <c r="M84" t="s">
+        <v>53</v>
+      </c>
+      <c r="N84" t="s">
+        <v>31</v>
+      </c>
+      <c r="O84" s="4">
+        <v>-41.86</v>
+      </c>
+      <c r="P84" s="4">
+        <v>677.62</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R84" s="4">
+        <v>0</v>
+      </c>
+      <c r="S84" s="4">
+        <v>0</v>
+      </c>
+      <c r="T84" s="4">
+        <v>0</v>
+      </c>
+      <c r="U84" s="4">
+        <v>0</v>
+      </c>
+      <c r="V84" s="4">
+        <v>50</v>
+      </c>
+      <c r="W84" s="4">
+        <v>187.5</v>
+      </c>
+      <c r="X84" s="4">
+        <v>229.36</v>
+      </c>
+      <c r="Y84">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>56</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" t="s">
+        <v>50</v>
+      </c>
+      <c r="G85" t="s">
+        <v>29</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>7759.75</v>
+      </c>
+      <c r="J85">
+        <v>7755.5</v>
+      </c>
+      <c r="K85" s="3">
+        <v>46316.420138888891</v>
+      </c>
+      <c r="L85" s="3">
+        <v>46316.423611111109</v>
+      </c>
+      <c r="M85" t="s">
+        <v>53</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" s="4">
+        <v>208.14</v>
+      </c>
+      <c r="P85" s="4">
+        <v>208.14</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R85" s="4">
+        <v>0</v>
+      </c>
+      <c r="S85" s="4">
+        <v>0</v>
+      </c>
+      <c r="T85" s="4">
+        <v>0</v>
+      </c>
+      <c r="U85" s="4">
+        <v>0</v>
+      </c>
+      <c r="V85" s="4">
+        <v>150</v>
+      </c>
+      <c r="W85" s="4">
+        <v>250</v>
+      </c>
+      <c r="X85" s="4">
+        <v>41.86</v>
+      </c>
+      <c r="Y85">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>56</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" t="s">
+        <v>50</v>
+      </c>
+      <c r="G86" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>7762.25</v>
+      </c>
+      <c r="J86">
+        <v>7765</v>
+      </c>
+      <c r="K86" s="3">
+        <v>46316.436111111114</v>
+      </c>
+      <c r="L86" s="3">
+        <v>46316.438194444447</v>
+      </c>
+      <c r="M86" t="s">
         <v>54</v>
       </c>
-      <c r="B83" s="2">
+      <c r="N86" t="s">
+        <v>33</v>
+      </c>
+      <c r="O86" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P86" s="4">
+        <v>341.28</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R86" s="4">
+        <v>0</v>
+      </c>
+      <c r="S86" s="4">
+        <v>0</v>
+      </c>
+      <c r="T86" s="4">
+        <v>0</v>
+      </c>
+      <c r="U86" s="4">
+        <v>0</v>
+      </c>
+      <c r="V86" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="W86" s="4">
+        <v>150</v>
+      </c>
+      <c r="X86" s="4">
+        <v>16.86</v>
+      </c>
+      <c r="Y86">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>56</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" t="s">
+        <v>27</v>
+      </c>
+      <c r="F87" t="s">
+        <v>50</v>
+      </c>
+      <c r="G87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>7774.25</v>
+      </c>
+      <c r="J87">
+        <v>7777.25</v>
+      </c>
+      <c r="K87" s="3">
+        <v>46316.449305555558</v>
+      </c>
+      <c r="L87" s="3">
+        <v>46316.45208333333</v>
+      </c>
+      <c r="M87" t="s">
+        <v>52</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" s="4">
+        <v>145.63999999999999</v>
+      </c>
+      <c r="P87" s="4">
+        <v>486.92</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R87" s="4">
+        <v>0</v>
+      </c>
+      <c r="S87" s="4">
+        <v>0</v>
+      </c>
+      <c r="T87" s="4">
+        <v>0</v>
+      </c>
+      <c r="U87" s="4">
+        <v>0</v>
+      </c>
+      <c r="V87" s="4">
+        <v>25</v>
+      </c>
+      <c r="W87" s="4">
+        <v>250</v>
+      </c>
+      <c r="X87" s="4">
+        <v>104.36</v>
+      </c>
+      <c r="Y87">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>56</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" t="s">
+        <v>50</v>
+      </c>
+      <c r="G88" t="s">
+        <v>29</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>7788.5</v>
+      </c>
+      <c r="J88">
+        <v>7791.75</v>
+      </c>
+      <c r="K88" s="3">
+        <v>46316.518750000003</v>
+      </c>
+      <c r="L88" s="3">
+        <v>46316.526388888888</v>
+      </c>
+      <c r="M88" t="s">
+        <v>51</v>
+      </c>
+      <c r="N88" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" s="4">
+        <v>-166.86</v>
+      </c>
+      <c r="P88" s="4">
+        <v>320.06</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R88" s="4">
+        <v>0</v>
+      </c>
+      <c r="S88" s="4">
+        <v>0</v>
+      </c>
+      <c r="T88" s="4">
+        <v>0</v>
+      </c>
+      <c r="U88" s="4">
+        <v>0</v>
+      </c>
+      <c r="V88" s="4">
+        <v>175</v>
+      </c>
+      <c r="W88" s="4">
+        <v>50</v>
+      </c>
+      <c r="X88" s="4">
+        <v>216.86</v>
+      </c>
+      <c r="Y88">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>56</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C89">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>26</v>
+      </c>
+      <c r="E89" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" t="s">
+        <v>50</v>
+      </c>
+      <c r="G89" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>7799.5</v>
+      </c>
+      <c r="J89">
+        <v>7798.75</v>
+      </c>
+      <c r="K89" s="3">
+        <v>46316.527083333334</v>
+      </c>
+      <c r="L89" s="3">
+        <v>46316.527777777781</v>
+      </c>
+      <c r="M89" t="s">
+        <v>52</v>
+      </c>
+      <c r="N89" t="s">
+        <v>31</v>
+      </c>
+      <c r="O89" s="4">
+        <v>-41.86</v>
+      </c>
+      <c r="P89" s="4">
+        <v>278.2</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R89" s="4">
+        <v>0</v>
+      </c>
+      <c r="S89" s="4">
+        <v>0</v>
+      </c>
+      <c r="T89" s="4">
+        <v>0</v>
+      </c>
+      <c r="U89" s="4">
+        <v>0</v>
+      </c>
+      <c r="V89" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="W89" s="4">
+        <v>350</v>
+      </c>
+      <c r="X89" s="4">
+        <v>391.86</v>
+      </c>
+      <c r="Y89">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>56</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C90">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" t="s">
+        <v>50</v>
+      </c>
+      <c r="G90" t="s">
+        <v>29</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>7805</v>
+      </c>
+      <c r="J90">
+        <v>7802.5</v>
+      </c>
+      <c r="K90" s="3">
+        <v>46316.615972222222</v>
+      </c>
+      <c r="L90" s="3">
+        <v>46316.616666666669</v>
+      </c>
+      <c r="M90" t="s">
+        <v>51</v>
+      </c>
+      <c r="N90" t="s">
+        <v>33</v>
+      </c>
+      <c r="O90" s="4">
+        <v>120.64</v>
+      </c>
+      <c r="P90" s="4">
+        <v>398.84</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R90" s="4">
+        <v>0</v>
+      </c>
+      <c r="S90" s="4">
+        <v>0</v>
+      </c>
+      <c r="T90" s="4">
+        <v>0</v>
+      </c>
+      <c r="U90" s="4">
+        <v>0</v>
+      </c>
+      <c r="V90" s="4">
+        <v>100</v>
+      </c>
+      <c r="W90" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="X90" s="4">
+        <v>41.86</v>
+      </c>
+      <c r="Y90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>56</v>
+      </c>
+      <c r="B91" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C91">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>26</v>
+      </c>
+      <c r="E91" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" t="s">
+        <v>50</v>
+      </c>
+      <c r="G91" t="s">
+        <v>29</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>7798.75</v>
+      </c>
+      <c r="J91">
+        <v>7797.5</v>
+      </c>
+      <c r="K91" s="3">
+        <v>46316.617361111108</v>
+      </c>
+      <c r="L91" s="3">
+        <v>46316.619444444441</v>
+      </c>
+      <c r="M91" t="s">
+        <v>53</v>
+      </c>
+      <c r="N91" t="s">
+        <v>31</v>
+      </c>
+      <c r="O91" s="4">
+        <v>58.14</v>
+      </c>
+      <c r="P91" s="4">
+        <v>456.98</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R91" s="4">
+        <v>0</v>
+      </c>
+      <c r="S91" s="4">
+        <v>0</v>
+      </c>
+      <c r="T91" s="4">
+        <v>0</v>
+      </c>
+      <c r="U91" s="4">
+        <v>0</v>
+      </c>
+      <c r="V91" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="W91" s="4">
+        <v>250</v>
+      </c>
+      <c r="X91" s="4">
+        <v>191.86</v>
+      </c>
+      <c r="Y91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>56</v>
+      </c>
+      <c r="B92" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F92" t="s">
+        <v>50</v>
+      </c>
+      <c r="G92" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>7786.5</v>
+      </c>
+      <c r="J92">
+        <v>7789.25</v>
+      </c>
+      <c r="K92" s="3">
+        <v>46316.636111111111</v>
+      </c>
+      <c r="L92" s="3">
+        <v>46316.636805555558</v>
+      </c>
+      <c r="M92" t="s">
+        <v>54</v>
+      </c>
+      <c r="N92" t="s">
+        <v>33</v>
+      </c>
+      <c r="O92" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P92" s="4">
+        <v>590.12</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R92" s="4">
+        <v>0</v>
+      </c>
+      <c r="S92" s="4">
+        <v>0</v>
+      </c>
+      <c r="T92" s="4">
+        <v>0</v>
+      </c>
+      <c r="U92" s="4">
+        <v>0</v>
+      </c>
+      <c r="V92" s="4">
+        <v>25</v>
+      </c>
+      <c r="W92" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="X92" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="Y92">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>57</v>
+      </c>
+      <c r="B93" s="2">
         <v>46317</v>
       </c>
-      <c r="C83">
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" t="s">
+        <v>27</v>
+      </c>
+      <c r="F93" t="s">
+        <v>50</v>
+      </c>
+      <c r="G93" t="s">
+        <v>29</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>7727.25</v>
+      </c>
+      <c r="J93">
+        <v>7718.5</v>
+      </c>
+      <c r="K93" s="3">
+        <v>46317.422222222223</v>
+      </c>
+      <c r="L93" s="3">
+        <v>46317.427083333336</v>
+      </c>
+      <c r="M93" t="s">
+        <v>53</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" s="4">
+        <v>433.14</v>
+      </c>
+      <c r="P93" s="4">
+        <v>433.14</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R93" s="4">
+        <v>0</v>
+      </c>
+      <c r="S93" s="4">
+        <v>0</v>
+      </c>
+      <c r="T93" s="4">
+        <v>0</v>
+      </c>
+      <c r="U93" s="4">
+        <v>0</v>
+      </c>
+      <c r="V93" s="4">
+        <v>100</v>
+      </c>
+      <c r="W93" s="4">
+        <v>462.5</v>
+      </c>
+      <c r="X93" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y93">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" t="s">
+        <v>27</v>
+      </c>
+      <c r="F94" t="s">
+        <v>50</v>
+      </c>
+      <c r="G94" t="s">
+        <v>34</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>7695</v>
+      </c>
+      <c r="J94">
+        <v>7689.75</v>
+      </c>
+      <c r="K94" s="3">
+        <v>46317.454861111109</v>
+      </c>
+      <c r="L94" s="3">
+        <v>46317.454861111109</v>
+      </c>
+      <c r="M94" t="s">
+        <v>54</v>
+      </c>
+      <c r="N94" t="s">
+        <v>31</v>
+      </c>
+      <c r="O94" s="4">
+        <v>-266.86</v>
+      </c>
+      <c r="P94" s="4">
+        <v>166.28</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R94" s="4">
+        <v>0</v>
+      </c>
+      <c r="S94" s="4">
+        <v>0</v>
+      </c>
+      <c r="T94" s="4">
+        <v>0</v>
+      </c>
+      <c r="U94" s="4">
+        <v>0</v>
+      </c>
+      <c r="V94" s="4">
+        <v>300</v>
+      </c>
+      <c r="W94" s="4">
+        <v>75</v>
+      </c>
+      <c r="X94" s="4">
+        <v>341.86</v>
+      </c>
+      <c r="Y94">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>57</v>
+      </c>
+      <c r="B95" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" t="s">
+        <v>27</v>
+      </c>
+      <c r="F95" t="s">
+        <v>50</v>
+      </c>
+      <c r="G95" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>7700.75</v>
+      </c>
+      <c r="J95">
+        <v>7712</v>
+      </c>
+      <c r="K95" s="3">
+        <v>46317.470833333333</v>
+      </c>
+      <c r="L95" s="3">
+        <v>46317.474999999999</v>
+      </c>
+      <c r="M95" t="s">
+        <v>52</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" s="4">
+        <v>558.14</v>
+      </c>
+      <c r="P95" s="4">
+        <v>724.42</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R95" s="4">
+        <v>0</v>
+      </c>
+      <c r="S95" s="4">
+        <v>0</v>
+      </c>
+      <c r="T95" s="4">
+        <v>0</v>
+      </c>
+      <c r="U95" s="4">
+        <v>0</v>
+      </c>
+      <c r="V95" s="4">
+        <v>100</v>
+      </c>
+      <c r="W95" s="4">
+        <v>587.5</v>
+      </c>
+      <c r="X95" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y95">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>57</v>
+      </c>
+      <c r="B96" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s">
+        <v>50</v>
+      </c>
+      <c r="G96" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>7711</v>
+      </c>
+      <c r="J96">
+        <v>7716.75</v>
+      </c>
+      <c r="K96" s="3">
+        <v>46317.49722222222</v>
+      </c>
+      <c r="L96" s="3">
+        <v>46317.5</v>
+      </c>
+      <c r="M96" t="s">
+        <v>52</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" s="4">
+        <v>283.14</v>
+      </c>
+      <c r="P96" s="4">
+        <v>1007.56</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R96" s="4">
+        <v>0</v>
+      </c>
+      <c r="S96" s="4">
+        <v>0</v>
+      </c>
+      <c r="T96" s="4">
+        <v>0</v>
+      </c>
+      <c r="U96" s="4">
+        <v>0</v>
+      </c>
+      <c r="V96" s="4">
+        <v>62.5</v>
+      </c>
+      <c r="W96" s="4">
+        <v>312.5</v>
+      </c>
+      <c r="X96" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y96">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>57</v>
+      </c>
+      <c r="B97" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C97">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>26</v>
+      </c>
+      <c r="E97" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" t="s">
+        <v>50</v>
+      </c>
+      <c r="G97" t="s">
+        <v>29</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>7711.5</v>
+      </c>
+      <c r="J97">
+        <v>7709</v>
+      </c>
+      <c r="K97" s="3">
+        <v>46317.522222222222</v>
+      </c>
+      <c r="L97" s="3">
+        <v>46317.522916666669</v>
+      </c>
+      <c r="M97" t="s">
+        <v>51</v>
+      </c>
+      <c r="N97" t="s">
+        <v>33</v>
+      </c>
+      <c r="O97" s="4">
+        <v>120.64</v>
+      </c>
+      <c r="P97" s="4">
+        <v>1128.2</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R97" s="4">
+        <v>0</v>
+      </c>
+      <c r="S97" s="4">
+        <v>0</v>
+      </c>
+      <c r="T97" s="4">
+        <v>0</v>
+      </c>
+      <c r="U97" s="4">
+        <v>0</v>
+      </c>
+      <c r="V97" s="4">
+        <v>50</v>
+      </c>
+      <c r="W97" s="4">
+        <v>137.5</v>
+      </c>
+      <c r="X97" s="4">
+        <v>16.86</v>
+      </c>
+      <c r="Y97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>57</v>
+      </c>
+      <c r="B98" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C98">
+        <v>6</v>
+      </c>
+      <c r="D98" t="s">
+        <v>26</v>
+      </c>
+      <c r="E98" t="s">
+        <v>27</v>
+      </c>
+      <c r="F98" t="s">
+        <v>50</v>
+      </c>
+      <c r="G98" t="s">
+        <v>29</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>7701</v>
+      </c>
+      <c r="J98">
+        <v>7698.25</v>
+      </c>
+      <c r="K98" s="3">
+        <v>46317.527083333334</v>
+      </c>
+      <c r="L98" s="3">
+        <v>46317.530555555553</v>
+      </c>
+      <c r="M98" t="s">
+        <v>53</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P98" s="4">
+        <v>1261.3399999999999</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R98" s="4">
+        <v>0</v>
+      </c>
+      <c r="S98" s="4">
+        <v>0</v>
+      </c>
+      <c r="T98" s="4">
+        <v>0</v>
+      </c>
+      <c r="U98" s="4">
+        <v>0</v>
+      </c>
+      <c r="V98" s="4">
+        <v>50</v>
+      </c>
+      <c r="W98" s="4">
+        <v>237.5</v>
+      </c>
+      <c r="X98" s="4">
+        <v>104.36</v>
+      </c>
+      <c r="Y98">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>57</v>
+      </c>
+      <c r="B99" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C99">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>26</v>
+      </c>
+      <c r="E99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" t="s">
+        <v>50</v>
+      </c>
+      <c r="G99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>7702.25</v>
+      </c>
+      <c r="J99">
+        <v>7697.5</v>
+      </c>
+      <c r="K99" s="3">
+        <v>46317.540277777778</v>
+      </c>
+      <c r="L99" s="3">
+        <v>46317.543055555558</v>
+      </c>
+      <c r="M99" t="s">
+        <v>54</v>
+      </c>
+      <c r="N99" t="s">
+        <v>31</v>
+      </c>
+      <c r="O99" s="4">
+        <v>-241.86</v>
+      </c>
+      <c r="P99" s="4">
+        <v>1019.48</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R99" s="4">
+        <v>0</v>
+      </c>
+      <c r="S99" s="4">
+        <v>0</v>
+      </c>
+      <c r="T99" s="4">
+        <v>0</v>
+      </c>
+      <c r="U99" s="4">
+        <v>0</v>
+      </c>
+      <c r="V99" s="4">
+        <v>250</v>
+      </c>
+      <c r="W99" s="4">
+        <v>87.5</v>
+      </c>
+      <c r="X99" s="4">
+        <v>329.36</v>
+      </c>
+      <c r="Y99">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>57</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C100">
+        <v>8</v>
+      </c>
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s">
+        <v>27</v>
+      </c>
+      <c r="F100" t="s">
+        <v>50</v>
+      </c>
+      <c r="G100" t="s">
+        <v>29</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>7690</v>
+      </c>
+      <c r="J100">
+        <v>7693</v>
+      </c>
+      <c r="K100" s="3">
+        <v>46317.547222222223</v>
+      </c>
+      <c r="L100" s="3">
+        <v>46317.551388888889</v>
+      </c>
+      <c r="M100" t="s">
+        <v>53</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" s="4">
+        <v>-154.36000000000001</v>
+      </c>
+      <c r="P100" s="4">
+        <v>865.12</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R100" s="4">
+        <v>0</v>
+      </c>
+      <c r="S100" s="4">
+        <v>0</v>
+      </c>
+      <c r="T100" s="4">
+        <v>0</v>
+      </c>
+      <c r="U100" s="4">
+        <v>0</v>
+      </c>
+      <c r="V100" s="4">
+        <v>150</v>
+      </c>
+      <c r="W100" s="4">
+        <v>175</v>
+      </c>
+      <c r="X100" s="4">
+        <v>329.36</v>
+      </c>
+      <c r="Y100">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>57</v>
+      </c>
+      <c r="B101" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C101">
+        <v>9</v>
+      </c>
+      <c r="D101" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" t="s">
+        <v>50</v>
+      </c>
+      <c r="G101" t="s">
+        <v>34</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>7704.75</v>
+      </c>
+      <c r="J101">
+        <v>7697.75</v>
+      </c>
+      <c r="K101" s="3">
+        <v>46317.56527777778</v>
+      </c>
+      <c r="L101" s="3">
+        <v>46317.573611111111</v>
+      </c>
+      <c r="M101" t="s">
+        <v>52</v>
+      </c>
+      <c r="N101" t="s">
+        <v>31</v>
+      </c>
+      <c r="O101" s="4">
+        <v>-354.36</v>
+      </c>
+      <c r="P101" s="4">
+        <v>510.76</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R101" s="4">
+        <v>0</v>
+      </c>
+      <c r="S101" s="4">
+        <v>0</v>
+      </c>
+      <c r="T101" s="4">
+        <v>0</v>
+      </c>
+      <c r="U101" s="4">
+        <v>0</v>
+      </c>
+      <c r="V101" s="4">
+        <v>362.5</v>
+      </c>
+      <c r="W101" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="X101" s="4">
+        <v>391.86</v>
+      </c>
+      <c r="Y101">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>57</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C102">
+        <v>10</v>
+      </c>
+      <c r="D102" t="s">
+        <v>26</v>
+      </c>
+      <c r="E102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F102" t="s">
+        <v>50</v>
+      </c>
+      <c r="G102" t="s">
+        <v>29</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>7687.75</v>
+      </c>
+      <c r="J102">
+        <v>7679.75</v>
+      </c>
+      <c r="K102" s="3">
+        <v>46317.584027777775</v>
+      </c>
+      <c r="L102" s="3">
+        <v>46317.586111111108</v>
+      </c>
+      <c r="M102" t="s">
+        <v>53</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" s="4">
+        <v>395.64</v>
+      </c>
+      <c r="P102" s="4">
+        <v>906.4</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R102" s="4">
+        <v>0</v>
+      </c>
+      <c r="S102" s="4">
+        <v>0</v>
+      </c>
+      <c r="T102" s="4">
+        <v>0</v>
+      </c>
+      <c r="U102" s="4">
+        <v>0</v>
+      </c>
+      <c r="V102" s="4">
+        <v>25</v>
+      </c>
+      <c r="W102" s="4">
+        <v>425</v>
+      </c>
+      <c r="X102" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y102">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C103">
+        <v>11</v>
+      </c>
+      <c r="D103" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" t="s">
+        <v>50</v>
+      </c>
+      <c r="G103" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>7699.75</v>
+      </c>
+      <c r="J103">
+        <v>7694</v>
+      </c>
+      <c r="K103" s="3">
+        <v>46317.59652777778</v>
+      </c>
+      <c r="L103" s="3">
+        <v>46317.602083333331</v>
+      </c>
+      <c r="M103" t="s">
+        <v>52</v>
+      </c>
+      <c r="N103" t="s">
+        <v>31</v>
+      </c>
+      <c r="O103" s="4">
+        <v>-291.86</v>
+      </c>
+      <c r="P103" s="4">
+        <v>614.54</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R103" s="4">
+        <v>0</v>
+      </c>
+      <c r="S103" s="4">
+        <v>0</v>
+      </c>
+      <c r="T103" s="4">
+        <v>0</v>
+      </c>
+      <c r="U103" s="4">
+        <v>0</v>
+      </c>
+      <c r="V103" s="4">
+        <v>300</v>
+      </c>
+      <c r="W103" s="4">
+        <v>175</v>
+      </c>
+      <c r="X103" s="4">
+        <v>466.86</v>
+      </c>
+      <c r="Y103">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>57</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C104">
+        <v>12</v>
+      </c>
+      <c r="D104" t="s">
+        <v>26</v>
+      </c>
+      <c r="E104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F104" t="s">
+        <v>50</v>
+      </c>
+      <c r="G104" t="s">
+        <v>29</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>7684</v>
+      </c>
+      <c r="J104">
+        <v>7682.5</v>
+      </c>
+      <c r="K104" s="3">
+        <v>46317.606249999997</v>
+      </c>
+      <c r="L104" s="3">
+        <v>46317.611805555556</v>
+      </c>
+      <c r="M104" t="s">
+        <v>53</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" s="4">
+        <v>70.64</v>
+      </c>
+      <c r="P104" s="4">
+        <v>685.18</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R104" s="4">
+        <v>0</v>
+      </c>
+      <c r="S104" s="4">
+        <v>0</v>
+      </c>
+      <c r="T104" s="4">
+        <v>0</v>
+      </c>
+      <c r="U104" s="4">
+        <v>0</v>
+      </c>
+      <c r="V104" s="4">
+        <v>200</v>
+      </c>
+      <c r="W104" s="4">
+        <v>112.5</v>
+      </c>
+      <c r="X104" s="4">
+        <v>41.86</v>
+      </c>
+      <c r="Y104">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C105">
+        <v>13</v>
+      </c>
+      <c r="D105" t="s">
+        <v>26</v>
+      </c>
+      <c r="E105" t="s">
+        <v>27</v>
+      </c>
+      <c r="F105" t="s">
+        <v>50</v>
+      </c>
+      <c r="G105" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>7687</v>
+      </c>
+      <c r="J105">
+        <v>7689.75</v>
+      </c>
+      <c r="K105" s="3">
+        <v>46317.629861111112</v>
+      </c>
+      <c r="L105" s="3">
+        <v>46317.633333333331</v>
+      </c>
+      <c r="M105" t="s">
+        <v>54</v>
+      </c>
+      <c r="N105" t="s">
+        <v>33</v>
+      </c>
+      <c r="O105" s="4">
+        <v>133.13999999999999</v>
+      </c>
+      <c r="P105" s="4">
+        <v>818.32</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R105" s="4">
+        <v>0</v>
+      </c>
+      <c r="S105" s="4">
+        <v>0</v>
+      </c>
+      <c r="T105" s="4">
+        <v>0</v>
+      </c>
+      <c r="U105" s="4">
+        <v>0</v>
+      </c>
+      <c r="V105" s="4">
+        <v>175</v>
+      </c>
+      <c r="W105" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="X105" s="4">
+        <v>29.36</v>
+      </c>
+      <c r="Y105">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>57</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C106">
         <v>14</v>
       </c>
-      <c r="D83" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83" t="s">
-        <v>27</v>
-      </c>
-      <c r="F83" t="s">
-        <v>48</v>
-      </c>
-      <c r="G83" t="s">
-        <v>32</v>
-      </c>
-      <c r="H83">
-        <v>1</v>
-      </c>
-      <c r="I83">
+      <c r="D106" t="s">
+        <v>26</v>
+      </c>
+      <c r="E106" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" t="s">
+        <v>50</v>
+      </c>
+      <c r="G106" t="s">
+        <v>29</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
         <v>7688.25</v>
       </c>
-      <c r="J83">
+      <c r="J106">
         <v>7685.25</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K106" s="3">
         <v>46317.649305555555</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L106" s="3">
         <v>46317.652777777781</v>
       </c>
-      <c r="M83" t="s">
-        <v>50</v>
-      </c>
-      <c r="N83" t="s">
-        <v>34</v>
-      </c>
-      <c r="O83" s="4">
+      <c r="M106" t="s">
+        <v>51</v>
+      </c>
+      <c r="N106" t="s">
+        <v>33</v>
+      </c>
+      <c r="O106" s="4">
         <v>145.63999999999999</v>
       </c>
-      <c r="P83" s="4">
+      <c r="P106" s="4">
         <v>963.96</v>
       </c>
-      <c r="Q83" s="4">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="R83" s="4">
-        <v>0</v>
-      </c>
-      <c r="S83" s="4">
-        <v>0</v>
-      </c>
-      <c r="T83" s="4">
-        <v>0</v>
-      </c>
-      <c r="U83" s="4">
-        <v>0</v>
-      </c>
-      <c r="V83" s="4">
+      <c r="Q106" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="R106" s="4">
+        <v>0</v>
+      </c>
+      <c r="S106" s="4">
+        <v>0</v>
+      </c>
+      <c r="T106" s="4">
+        <v>0</v>
+      </c>
+      <c r="U106" s="4">
+        <v>0</v>
+      </c>
+      <c r="V106" s="4">
         <v>100</v>
       </c>
-      <c r="W83" s="4">
+      <c r="W106" s="4">
         <v>175</v>
       </c>
-      <c r="X83" s="4">
+      <c r="X106" s="4">
         <v>29.36</v>
       </c>
-      <c r="Y83">
+      <c r="Y106">
         <v>21</v>
       </c>
     </row>
@@ -6713,8 +8493,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E6661C-AA91-4C8A-BCF8-86A021BC4B3F}">
-  <dimension ref="A1:E34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92FC62AB-D814-4E07-85FB-DEC1BBA76967}">
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -6729,21 +8509,21 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -6752,32 +8532,32 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>-221.22</v>
+        <v>136.91999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>133.13999999999999</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -6786,49 +8566,49 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>620.05999999999995</v>
+        <v>611.91999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>145.63999999999999</v>
+        <v>566.28</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>-33.72</v>
+        <v>-79.36</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -6837,10 +8617,10 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>-329.94</v>
+        <v>-141.86000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -6851,115 +8631,115 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>-16.86</v>
+        <v>-221.22</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>70.64</v>
+        <v>133.13999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>-204.36</v>
+        <v>620.05999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>266.27999999999997</v>
+        <v>145.63999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12">
-        <v>266.27999999999997</v>
+        <v>-33.72</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>103.78</v>
+        <v>-329.94</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>-46.22</v>
+        <v>-16.86</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6970,24 +8750,24 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>-79.36</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6998,58 +8778,58 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>-897.38</v>
+        <v>266.27999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>878.2</v>
+        <v>266.27999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>-375.58</v>
+        <v>103.78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -7058,27 +8838,27 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>195.06</v>
+        <v>-46.22</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>-238.08</v>
+        <v>-79.36</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -7089,109 +8869,109 @@
         <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>266.27999999999997</v>
+        <v>-204.36</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>-221.22</v>
+        <v>-897.38</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>133.13999999999999</v>
+        <v>878.2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>620.05999999999995</v>
+        <v>-375.58</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>145.63999999999999</v>
+        <v>195.06</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>266.27999999999997</v>
+        <v>-238.08</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -7202,103 +8982,273 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>103.78</v>
+        <v>136.91999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30">
-        <v>-46.22</v>
+        <v>566.28</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>878.2</v>
+        <v>-79.36</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>-375.58</v>
+        <v>-141.86000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>195.06</v>
+        <v>-221.22</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>133.13999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>620.05999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>145.63999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>266.27999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>266.27999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>103.78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>-46.22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>46317</v>
       </c>
-      <c r="B34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B41" t="s">
         <v>50</v>
       </c>
-      <c r="D34">
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>878.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>-375.58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>195.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44">
         <v>2</v>
       </c>
-      <c r="E34">
+      <c r="E44">
         <v>266.27999999999997</v>
       </c>
     </row>
